--- a/output/cta-violent-crime-full-year.xlsx
+++ b/output/cta-violent-crime-full-year.xlsx
@@ -13,10 +13,10 @@
     <sheet name="Englewood" sheetId="4" r:id="rId4"/>
     <sheet name="Avondale" sheetId="5" r:id="rId5"/>
     <sheet name="Douglas" sheetId="6" r:id="rId6"/>
-    <sheet name="Grand Crossing" sheetId="7" r:id="rId7"/>
+    <sheet name="Grand Boulevard" sheetId="7" r:id="rId7"/>
     <sheet name="Austin" sheetId="8" r:id="rId8"/>
-    <sheet name="Grand Boulevard" sheetId="9" r:id="rId9"/>
-    <sheet name="Mount Greenwood" sheetId="10" r:id="rId10"/>
+    <sheet name="Mount Greenwood" sheetId="9" r:id="rId9"/>
+    <sheet name="Grand Crossing" sheetId="10" r:id="rId10"/>
     <sheet name="Washington Park" sheetId="11" r:id="rId11"/>
     <sheet name="South Chicago" sheetId="12" r:id="rId12"/>
     <sheet name="Humboldt Park" sheetId="13" r:id="rId13"/>
@@ -34,11 +34,11 @@
     <sheet name="Armour Square" sheetId="25" r:id="rId25"/>
     <sheet name="Roseland" sheetId="26" r:id="rId26"/>
     <sheet name="Fuller Park" sheetId="27" r:id="rId27"/>
-    <sheet name="O'Hare" sheetId="28" r:id="rId28"/>
-    <sheet name="Little Italy, UIC" sheetId="29" r:id="rId29"/>
-    <sheet name="Hyde Park" sheetId="30" r:id="rId30"/>
-    <sheet name="Calumet Heights" sheetId="31" r:id="rId31"/>
-    <sheet name="Kenwood" sheetId="32" r:id="rId32"/>
+    <sheet name="Little Italy, UIC" sheetId="28" r:id="rId28"/>
+    <sheet name="Hyde Park" sheetId="29" r:id="rId29"/>
+    <sheet name="Calumet Heights" sheetId="30" r:id="rId30"/>
+    <sheet name="Kenwood" sheetId="31" r:id="rId31"/>
+    <sheet name="O'Hare" sheetId="32" r:id="rId32"/>
     <sheet name="Chicago Lawn" sheetId="33" r:id="rId33"/>
     <sheet name="Wrigleyville" sheetId="34" r:id="rId34"/>
     <sheet name="Auburn Gresham" sheetId="35" r:id="rId35"/>
@@ -1101,60 +1101,261 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
         <v>2016</v>
       </c>
-      <c r="C1" s="1">
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
         <v>2022</v>
       </c>
-      <c r="D1" s="1">
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
       <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>7</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>7</v>
+      </c>
+      <c r="K2">
+        <v>7</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>19</v>
+      </c>
+      <c r="G3">
+        <v>9</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
+      </c>
+      <c r="J3">
+        <v>12</v>
+      </c>
+      <c r="K3">
+        <v>17</v>
+      </c>
+      <c r="L3">
+        <v>13</v>
+      </c>
+      <c r="M3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>24</v>
+      </c>
+      <c r="C6">
+        <v>37</v>
+      </c>
+      <c r="D6">
+        <v>21</v>
+      </c>
+      <c r="E6">
+        <v>22</v>
+      </c>
+      <c r="F6">
+        <v>27</v>
+      </c>
+      <c r="G6">
+        <v>15</v>
+      </c>
+      <c r="H6">
+        <v>25</v>
+      </c>
+      <c r="I6">
+        <v>21</v>
+      </c>
+      <c r="J6">
+        <v>26</v>
+      </c>
+      <c r="K6">
+        <v>49</v>
+      </c>
+      <c r="L6">
+        <v>44</v>
+      </c>
+      <c r="M6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>42</v>
+      </c>
+      <c r="D7">
+        <v>36</v>
+      </c>
+      <c r="E7">
+        <v>38</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>28</v>
+      </c>
+      <c r="H7">
+        <v>39</v>
+      </c>
+      <c r="I7">
+        <v>39</v>
+      </c>
+      <c r="J7">
+        <v>47</v>
+      </c>
+      <c r="K7">
+        <v>74</v>
+      </c>
+      <c r="L7">
+        <v>63</v>
+      </c>
+      <c r="M7">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -8607,209 +8808,6 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>7</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>5</v>
-      </c>
-      <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -9039,6 +9037,174 @@
       </c>
       <c r="M6">
         <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>11</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>13</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -9277,174 +9443,6 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4">
-        <v>11</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="H5">
-        <v>13</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -9612,7 +9610,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9744,6 +9742,209 @@
       </c>
       <c r="J6">
         <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7">
+        <v>9</v>
+      </c>
+      <c r="L7">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -17266,10 +17467,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -17329,41 +17530,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>6</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17371,156 +17560,121 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>8</v>
-      </c>
-      <c r="E3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>9</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="M4">
+        <v>4</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="G6">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H6">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="I6">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="M6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>32</v>
-      </c>
-      <c r="C7">
-        <v>42</v>
-      </c>
-      <c r="D7">
-        <v>36</v>
-      </c>
-      <c r="E7">
-        <v>38</v>
-      </c>
-      <c r="F7">
-        <v>53</v>
-      </c>
-      <c r="G7">
-        <v>28</v>
-      </c>
-      <c r="H7">
-        <v>39</v>
-      </c>
-      <c r="I7">
-        <v>39</v>
-      </c>
-      <c r="J7">
-        <v>47</v>
-      </c>
-      <c r="K7">
-        <v>74</v>
-      </c>
-      <c r="L7">
-        <v>63</v>
-      </c>
-      <c r="M7">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -20275,214 +20429,60 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>4</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>8</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>13</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>8</v>
-      </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>6</v>
-      </c>
-      <c r="J6">
-        <v>8</v>
-      </c>
-      <c r="K6">
-        <v>9</v>
-      </c>
-      <c r="L6">
-        <v>12</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-full-year.xlsx
+++ b/output/cta-violent-crime-full-year.xlsx
@@ -13,10 +13,10 @@
     <sheet name="Englewood" sheetId="4" r:id="rId4"/>
     <sheet name="Avondale" sheetId="5" r:id="rId5"/>
     <sheet name="Douglas" sheetId="6" r:id="rId6"/>
-    <sheet name="Grand Boulevard" sheetId="7" r:id="rId7"/>
+    <sheet name="Grand Crossing" sheetId="7" r:id="rId7"/>
     <sheet name="Austin" sheetId="8" r:id="rId8"/>
-    <sheet name="Mount Greenwood" sheetId="9" r:id="rId9"/>
-    <sheet name="Grand Crossing" sheetId="10" r:id="rId10"/>
+    <sheet name="Grand Boulevard" sheetId="9" r:id="rId9"/>
+    <sheet name="Mount Greenwood" sheetId="10" r:id="rId10"/>
     <sheet name="Washington Park" sheetId="11" r:id="rId11"/>
     <sheet name="South Chicago" sheetId="12" r:id="rId12"/>
     <sheet name="Humboldt Park" sheetId="13" r:id="rId13"/>
@@ -34,11 +34,11 @@
     <sheet name="Armour Square" sheetId="25" r:id="rId25"/>
     <sheet name="Roseland" sheetId="26" r:id="rId26"/>
     <sheet name="Fuller Park" sheetId="27" r:id="rId27"/>
-    <sheet name="Little Italy, UIC" sheetId="28" r:id="rId28"/>
-    <sheet name="Hyde Park" sheetId="29" r:id="rId29"/>
-    <sheet name="Calumet Heights" sheetId="30" r:id="rId30"/>
-    <sheet name="Kenwood" sheetId="31" r:id="rId31"/>
-    <sheet name="O'Hare" sheetId="32" r:id="rId32"/>
+    <sheet name="O'Hare" sheetId="28" r:id="rId28"/>
+    <sheet name="Little Italy, UIC" sheetId="29" r:id="rId29"/>
+    <sheet name="Hyde Park" sheetId="30" r:id="rId30"/>
+    <sheet name="Calumet Heights" sheetId="31" r:id="rId31"/>
+    <sheet name="Kenwood" sheetId="32" r:id="rId32"/>
     <sheet name="Chicago Lawn" sheetId="33" r:id="rId33"/>
     <sheet name="Wrigleyville" sheetId="34" r:id="rId34"/>
     <sheet name="Auburn Gresham" sheetId="35" r:id="rId35"/>
@@ -1050,7 +1050,7 @@
         <v>467</v>
       </c>
       <c r="M6">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1091,7 +1091,7 @@
         <v>896</v>
       </c>
       <c r="M7">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
   </sheetData>
@@ -1101,261 +1101,60 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
       <c r="D2">
-        <v>7</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>6</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>7</v>
-      </c>
-      <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>8</v>
-      </c>
-      <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
-      </c>
-      <c r="G3">
-        <v>9</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
-      </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>12</v>
-      </c>
-      <c r="K3">
-        <v>17</v>
-      </c>
-      <c r="L3">
-        <v>13</v>
-      </c>
-      <c r="M3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>24</v>
-      </c>
-      <c r="C6">
-        <v>37</v>
-      </c>
-      <c r="D6">
-        <v>21</v>
-      </c>
-      <c r="E6">
-        <v>22</v>
-      </c>
-      <c r="F6">
-        <v>27</v>
-      </c>
-      <c r="G6">
-        <v>15</v>
-      </c>
-      <c r="H6">
-        <v>25</v>
-      </c>
-      <c r="I6">
-        <v>21</v>
-      </c>
-      <c r="J6">
-        <v>26</v>
-      </c>
-      <c r="K6">
-        <v>49</v>
-      </c>
-      <c r="L6">
-        <v>44</v>
-      </c>
-      <c r="M6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>32</v>
-      </c>
-      <c r="C7">
-        <v>42</v>
-      </c>
-      <c r="D7">
-        <v>36</v>
-      </c>
-      <c r="E7">
-        <v>38</v>
-      </c>
-      <c r="F7">
-        <v>53</v>
-      </c>
-      <c r="G7">
-        <v>28</v>
-      </c>
-      <c r="H7">
-        <v>39</v>
-      </c>
-      <c r="I7">
-        <v>39</v>
-      </c>
-      <c r="J7">
-        <v>47</v>
-      </c>
-      <c r="K7">
-        <v>74</v>
-      </c>
-      <c r="L7">
-        <v>63</v>
-      </c>
-      <c r="M7">
-        <v>25</v>
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2756,7 +2555,7 @@
         <v>44</v>
       </c>
       <c r="M6">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2797,7 +2596,7 @@
         <v>100</v>
       </c>
       <c r="M7">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -5256,7 +5055,7 @@
         <v>100</v>
       </c>
       <c r="M53">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -6822,7 +6621,7 @@
         <v>896</v>
       </c>
       <c r="M98">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
   </sheetData>
@@ -8808,6 +8607,209 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7">
+        <v>9</v>
+      </c>
+      <c r="L7">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -9037,174 +9039,6 @@
       </c>
       <c r="M6">
         <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4">
-        <v>11</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="H5">
-        <v>13</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -9443,6 +9277,174 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>11</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>13</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -9610,7 +9612,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9742,209 +9744,6 @@
       </c>
       <c r="J6">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>7</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>5</v>
-      </c>
-      <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -17467,10 +17266,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -17530,29 +17329,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17560,121 +17371,156 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C6">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="J6">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="L6">
+        <v>44</v>
+      </c>
+      <c r="M6">
         <v>12</v>
       </c>
-      <c r="M6">
-        <v>4</v>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>42</v>
+      </c>
+      <c r="D7">
+        <v>36</v>
+      </c>
+      <c r="E7">
+        <v>38</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>28</v>
+      </c>
+      <c r="H7">
+        <v>39</v>
+      </c>
+      <c r="I7">
+        <v>39</v>
+      </c>
+      <c r="J7">
+        <v>47</v>
+      </c>
+      <c r="K7">
+        <v>74</v>
+      </c>
+      <c r="L7">
+        <v>63</v>
+      </c>
+      <c r="M7">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -20429,60 +20275,214 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
         <v>2016</v>
       </c>
-      <c r="C1" s="1">
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
         <v>2022</v>
       </c>
-      <c r="D1" s="1">
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>9</v>
+      </c>
+      <c r="L6">
+        <v>12</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-full-year.xlsx
+++ b/output/cta-violent-crime-full-year.xlsx
@@ -13,10 +13,10 @@
     <sheet name="Englewood" sheetId="4" r:id="rId4"/>
     <sheet name="Avondale" sheetId="5" r:id="rId5"/>
     <sheet name="Douglas" sheetId="6" r:id="rId6"/>
-    <sheet name="Grand Boulevard" sheetId="7" r:id="rId7"/>
+    <sheet name="Grand Crossing" sheetId="7" r:id="rId7"/>
     <sheet name="Austin" sheetId="8" r:id="rId8"/>
-    <sheet name="Mount Greenwood" sheetId="9" r:id="rId9"/>
-    <sheet name="Grand Crossing" sheetId="10" r:id="rId10"/>
+    <sheet name="Grand Boulevard" sheetId="9" r:id="rId9"/>
+    <sheet name="Mount Greenwood" sheetId="10" r:id="rId10"/>
     <sheet name="Washington Park" sheetId="11" r:id="rId11"/>
     <sheet name="South Chicago" sheetId="12" r:id="rId12"/>
     <sheet name="Humboldt Park" sheetId="13" r:id="rId13"/>
@@ -34,11 +34,11 @@
     <sheet name="Armour Square" sheetId="25" r:id="rId25"/>
     <sheet name="Roseland" sheetId="26" r:id="rId26"/>
     <sheet name="Fuller Park" sheetId="27" r:id="rId27"/>
-    <sheet name="Little Italy, UIC" sheetId="28" r:id="rId28"/>
-    <sheet name="Hyde Park" sheetId="29" r:id="rId29"/>
-    <sheet name="Calumet Heights" sheetId="30" r:id="rId30"/>
-    <sheet name="Kenwood" sheetId="31" r:id="rId31"/>
-    <sheet name="O'Hare" sheetId="32" r:id="rId32"/>
+    <sheet name="O'Hare" sheetId="28" r:id="rId28"/>
+    <sheet name="Little Italy, UIC" sheetId="29" r:id="rId29"/>
+    <sheet name="Hyde Park" sheetId="30" r:id="rId30"/>
+    <sheet name="Calumet Heights" sheetId="31" r:id="rId31"/>
+    <sheet name="Kenwood" sheetId="32" r:id="rId32"/>
     <sheet name="Chicago Lawn" sheetId="33" r:id="rId33"/>
     <sheet name="Wrigleyville" sheetId="34" r:id="rId34"/>
     <sheet name="Auburn Gresham" sheetId="35" r:id="rId35"/>
@@ -1101,261 +1101,60 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
       <c r="D2">
-        <v>7</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>6</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>7</v>
-      </c>
-      <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>8</v>
-      </c>
-      <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
-      </c>
-      <c r="G3">
-        <v>9</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
-      </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>12</v>
-      </c>
-      <c r="K3">
-        <v>17</v>
-      </c>
-      <c r="L3">
-        <v>13</v>
-      </c>
-      <c r="M3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>24</v>
-      </c>
-      <c r="C6">
-        <v>37</v>
-      </c>
-      <c r="D6">
-        <v>21</v>
-      </c>
-      <c r="E6">
-        <v>22</v>
-      </c>
-      <c r="F6">
-        <v>27</v>
-      </c>
-      <c r="G6">
-        <v>15</v>
-      </c>
-      <c r="H6">
-        <v>25</v>
-      </c>
-      <c r="I6">
-        <v>21</v>
-      </c>
-      <c r="J6">
-        <v>26</v>
-      </c>
-      <c r="K6">
-        <v>49</v>
-      </c>
-      <c r="L6">
-        <v>44</v>
-      </c>
-      <c r="M6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>32</v>
-      </c>
-      <c r="C7">
-        <v>42</v>
-      </c>
-      <c r="D7">
-        <v>36</v>
-      </c>
-      <c r="E7">
-        <v>38</v>
-      </c>
-      <c r="F7">
-        <v>53</v>
-      </c>
-      <c r="G7">
-        <v>28</v>
-      </c>
-      <c r="H7">
-        <v>39</v>
-      </c>
-      <c r="I7">
-        <v>39</v>
-      </c>
-      <c r="J7">
-        <v>47</v>
-      </c>
-      <c r="K7">
-        <v>74</v>
-      </c>
-      <c r="L7">
-        <v>63</v>
-      </c>
-      <c r="M7">
-        <v>25</v>
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -8808,6 +8607,209 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7">
+        <v>9</v>
+      </c>
+      <c r="L7">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -9037,174 +9039,6 @@
       </c>
       <c r="M6">
         <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4">
-        <v>11</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="H5">
-        <v>13</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -9443,6 +9277,174 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>11</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>13</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -9610,7 +9612,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9742,209 +9744,6 @@
       </c>
       <c r="J6">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>7</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>5</v>
-      </c>
-      <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -17467,10 +17266,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -17530,29 +17329,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17560,121 +17371,156 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C6">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="J6">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="L6">
+        <v>44</v>
+      </c>
+      <c r="M6">
         <v>12</v>
       </c>
-      <c r="M6">
-        <v>4</v>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>42</v>
+      </c>
+      <c r="D7">
+        <v>36</v>
+      </c>
+      <c r="E7">
+        <v>38</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>28</v>
+      </c>
+      <c r="H7">
+        <v>39</v>
+      </c>
+      <c r="I7">
+        <v>39</v>
+      </c>
+      <c r="J7">
+        <v>47</v>
+      </c>
+      <c r="K7">
+        <v>74</v>
+      </c>
+      <c r="L7">
+        <v>63</v>
+      </c>
+      <c r="M7">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -20429,60 +20275,214 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
         <v>2016</v>
       </c>
-      <c r="C1" s="1">
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
         <v>2022</v>
       </c>
-      <c r="D1" s="1">
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>9</v>
+      </c>
+      <c r="L6">
+        <v>12</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-full-year.xlsx
+++ b/output/cta-violent-crime-full-year.xlsx
@@ -13,10 +13,10 @@
     <sheet name="Englewood" sheetId="4" r:id="rId4"/>
     <sheet name="Avondale" sheetId="5" r:id="rId5"/>
     <sheet name="Douglas" sheetId="6" r:id="rId6"/>
-    <sheet name="Grand Boulevard" sheetId="7" r:id="rId7"/>
+    <sheet name="Grand Crossing" sheetId="7" r:id="rId7"/>
     <sheet name="Austin" sheetId="8" r:id="rId8"/>
-    <sheet name="Mount Greenwood" sheetId="9" r:id="rId9"/>
-    <sheet name="Grand Crossing" sheetId="10" r:id="rId10"/>
+    <sheet name="Grand Boulevard" sheetId="9" r:id="rId9"/>
+    <sheet name="Mount Greenwood" sheetId="10" r:id="rId10"/>
     <sheet name="Washington Park" sheetId="11" r:id="rId11"/>
     <sheet name="South Chicago" sheetId="12" r:id="rId12"/>
     <sheet name="Humboldt Park" sheetId="13" r:id="rId13"/>
@@ -34,11 +34,11 @@
     <sheet name="Armour Square" sheetId="25" r:id="rId25"/>
     <sheet name="Roseland" sheetId="26" r:id="rId26"/>
     <sheet name="Fuller Park" sheetId="27" r:id="rId27"/>
-    <sheet name="Little Italy, UIC" sheetId="28" r:id="rId28"/>
-    <sheet name="Hyde Park" sheetId="29" r:id="rId29"/>
-    <sheet name="Calumet Heights" sheetId="30" r:id="rId30"/>
-    <sheet name="Kenwood" sheetId="31" r:id="rId31"/>
-    <sheet name="O'Hare" sheetId="32" r:id="rId32"/>
+    <sheet name="O'Hare" sheetId="28" r:id="rId28"/>
+    <sheet name="Little Italy, UIC" sheetId="29" r:id="rId29"/>
+    <sheet name="Hyde Park" sheetId="30" r:id="rId30"/>
+    <sheet name="Calumet Heights" sheetId="31" r:id="rId31"/>
+    <sheet name="Kenwood" sheetId="32" r:id="rId32"/>
     <sheet name="Chicago Lawn" sheetId="33" r:id="rId33"/>
     <sheet name="Wrigleyville" sheetId="34" r:id="rId34"/>
     <sheet name="Auburn Gresham" sheetId="35" r:id="rId35"/>
@@ -50,18 +50,18 @@
     <sheet name="Chinatown" sheetId="41" r:id="rId41"/>
     <sheet name="Edgewater" sheetId="42" r:id="rId42"/>
     <sheet name="Lower West Side" sheetId="43" r:id="rId43"/>
-    <sheet name="Washington Heights" sheetId="44" r:id="rId44"/>
-    <sheet name="Brighton Park" sheetId="45" r:id="rId45"/>
-    <sheet name="Greektown" sheetId="46" r:id="rId46"/>
-    <sheet name="North Lawndale" sheetId="47" r:id="rId47"/>
-    <sheet name="West Loop" sheetId="48" r:id="rId48"/>
-    <sheet name="West Pullman" sheetId="49" r:id="rId49"/>
-    <sheet name="Belmont Cragin" sheetId="50" r:id="rId50"/>
-    <sheet name="Bucktown" sheetId="51" r:id="rId51"/>
-    <sheet name="Little Village" sheetId="52" r:id="rId52"/>
-    <sheet name="Archer Heights" sheetId="53" r:id="rId53"/>
-    <sheet name="Albany Park" sheetId="54" r:id="rId54"/>
-    <sheet name="Woodlawn" sheetId="55" r:id="rId55"/>
+    <sheet name="Brighton Park" sheetId="44" r:id="rId44"/>
+    <sheet name="Greektown" sheetId="45" r:id="rId45"/>
+    <sheet name="North Lawndale" sheetId="46" r:id="rId46"/>
+    <sheet name="West Loop" sheetId="47" r:id="rId47"/>
+    <sheet name="Belmont Cragin" sheetId="48" r:id="rId48"/>
+    <sheet name="New City" sheetId="49" r:id="rId49"/>
+    <sheet name="Woodlawn" sheetId="50" r:id="rId50"/>
+    <sheet name="West Pullman" sheetId="51" r:id="rId51"/>
+    <sheet name="Bucktown" sheetId="52" r:id="rId52"/>
+    <sheet name="Little Village" sheetId="53" r:id="rId53"/>
+    <sheet name="Archer Heights" sheetId="54" r:id="rId54"/>
+    <sheet name="Albany Park" sheetId="55" r:id="rId55"/>
     <sheet name="East Side" sheetId="56" r:id="rId56"/>
     <sheet name="South Deering" sheetId="57" r:id="rId57"/>
     <sheet name="West Elsdon" sheetId="58" r:id="rId58"/>
@@ -69,16 +69,16 @@
     <sheet name="Lincoln Park" sheetId="60" r:id="rId60"/>
     <sheet name="Avalon Park" sheetId="61" r:id="rId61"/>
     <sheet name="Streeterville" sheetId="62" r:id="rId62"/>
-    <sheet name="New City" sheetId="63" r:id="rId63"/>
-    <sheet name="Portage Park" sheetId="64" r:id="rId64"/>
-    <sheet name="Lincoln Square" sheetId="65" r:id="rId65"/>
-    <sheet name="Irving Park" sheetId="66" r:id="rId66"/>
-    <sheet name="North Park" sheetId="67" r:id="rId67"/>
-    <sheet name="Printers Row" sheetId="68" r:id="rId68"/>
-    <sheet name="Jefferson Park" sheetId="69" r:id="rId69"/>
-    <sheet name="Logan Square" sheetId="70" r:id="rId70"/>
-    <sheet name="Mckinley Park" sheetId="71" r:id="rId71"/>
-    <sheet name="Old Town" sheetId="72" r:id="rId72"/>
+    <sheet name="Portage Park" sheetId="63" r:id="rId63"/>
+    <sheet name="Lincoln Square" sheetId="64" r:id="rId64"/>
+    <sheet name="Irving Park" sheetId="65" r:id="rId65"/>
+    <sheet name="North Park" sheetId="66" r:id="rId66"/>
+    <sheet name="Printers Row" sheetId="67" r:id="rId67"/>
+    <sheet name="Jefferson Park" sheetId="68" r:id="rId68"/>
+    <sheet name="Logan Square" sheetId="69" r:id="rId69"/>
+    <sheet name="Mckinley Park" sheetId="70" r:id="rId70"/>
+    <sheet name="Old Town" sheetId="71" r:id="rId71"/>
+    <sheet name="Washington Heights" sheetId="72" r:id="rId72"/>
     <sheet name="Riverdale" sheetId="73" r:id="rId73"/>
     <sheet name="Montclare" sheetId="74" r:id="rId74"/>
     <sheet name="Garfield Ridge" sheetId="75" r:id="rId75"/>
@@ -889,7 +889,7 @@
         <v>137</v>
       </c>
       <c r="M2">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1050,7 +1050,7 @@
         <v>467</v>
       </c>
       <c r="M6">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1091,7 +1091,7 @@
         <v>896</v>
       </c>
       <c r="M7">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
   </sheetData>
@@ -1101,261 +1101,60 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
       <c r="D2">
-        <v>7</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>6</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>7</v>
-      </c>
-      <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>8</v>
-      </c>
-      <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
-      </c>
-      <c r="G3">
-        <v>9</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
-      </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>12</v>
-      </c>
-      <c r="K3">
-        <v>17</v>
-      </c>
-      <c r="L3">
-        <v>13</v>
-      </c>
-      <c r="M3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>24</v>
-      </c>
-      <c r="C6">
-        <v>37</v>
-      </c>
-      <c r="D6">
-        <v>21</v>
-      </c>
-      <c r="E6">
-        <v>22</v>
-      </c>
-      <c r="F6">
-        <v>27</v>
-      </c>
-      <c r="G6">
-        <v>15</v>
-      </c>
-      <c r="H6">
-        <v>25</v>
-      </c>
-      <c r="I6">
-        <v>21</v>
-      </c>
-      <c r="J6">
-        <v>26</v>
-      </c>
-      <c r="K6">
-        <v>49</v>
-      </c>
-      <c r="L6">
-        <v>44</v>
-      </c>
-      <c r="M6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>32</v>
-      </c>
-      <c r="C7">
-        <v>42</v>
-      </c>
-      <c r="D7">
-        <v>36</v>
-      </c>
-      <c r="E7">
-        <v>38</v>
-      </c>
-      <c r="F7">
-        <v>53</v>
-      </c>
-      <c r="G7">
-        <v>28</v>
-      </c>
-      <c r="H7">
-        <v>39</v>
-      </c>
-      <c r="I7">
-        <v>39</v>
-      </c>
-      <c r="J7">
-        <v>47</v>
-      </c>
-      <c r="K7">
-        <v>74</v>
-      </c>
-      <c r="L7">
-        <v>63</v>
-      </c>
-      <c r="M7">
-        <v>25</v>
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3867,7 +3666,7 @@
         <v>1</v>
       </c>
       <c r="M11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -5569,6 +5368,9 @@
       <c r="L63">
         <v>2</v>
       </c>
+      <c r="M63">
+        <v>1</v>
+      </c>
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="2" t="s">
@@ -6425,7 +6227,7 @@
         <v>1</v>
       </c>
       <c r="M87">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -6559,7 +6361,7 @@
         <v>15</v>
       </c>
       <c r="M91">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -6740,7 +6542,7 @@
         <v>5</v>
       </c>
       <c r="M96">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -6822,7 +6624,7 @@
         <v>896</v>
       </c>
       <c r="M98">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
   </sheetData>
@@ -8808,6 +8610,209 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7">
+        <v>9</v>
+      </c>
+      <c r="L7">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -9037,174 +9042,6 @@
       </c>
       <c r="M6">
         <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4">
-        <v>11</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="H5">
-        <v>13</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -9443,6 +9280,174 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>11</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>13</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -9610,7 +9615,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9742,209 +9747,6 @@
       </c>
       <c r="J6">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>7</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>5</v>
-      </c>
-      <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -12602,181 +12404,6 @@
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>8</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>7</v>
-      </c>
-      <c r="F4">
-        <v>4</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -12948,7 +12575,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13125,7 +12752,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13363,7 +12990,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13551,7 +13178,7 @@
         <v>5</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -13592,7 +13219,165 @@
         <v>15</v>
       </c>
       <c r="M7">
-        <v>8</v>
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -13602,7 +13387,7 @@
 
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -13617,10 +13402,9 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13640,144 +13424,144 @@
         <v>2019</v>
       </c>
       <c r="G1" s="1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H1" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I1" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J1" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K1" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
       <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
       <c r="J2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
         <v>2</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
         <v>8</v>
       </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>4</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>5</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
+      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5">
         <v>10</v>
       </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
       <c r="K5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -13998,7 +13782,7 @@
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -14012,9 +13796,11 @@
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14031,72 +13817,117 @@
         <v>2018</v>
       </c>
       <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
         <v>2020</v>
       </c>
-      <c r="G1" s="1">
+      <c r="H1" s="1">
         <v>2021</v>
       </c>
-      <c r="H1" s="1">
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="I1" s="1">
+      <c r="K1" s="1">
         <v>2024</v>
       </c>
-      <c r="J1" s="1">
+      <c r="L1" s="1">
         <v>2025</v>
       </c>
-      <c r="K1" s="1">
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E3">
-        <v>2</v>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>5</v>
       </c>
       <c r="J3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>12</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -14105,45 +13936,60 @@
         <v>4</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>7</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
         <v>7</v>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
       <c r="G6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -14152,6 +13998,191 @@
 </file>
 
 <file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>5</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14272,7 +14303,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14474,7 +14505,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14581,7 +14612,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14775,223 +14806,6 @@
       </c>
       <c r="L6">
         <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>5</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>11</v>
-      </c>
-      <c r="C5">
-        <v>12</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>7</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>16</v>
-      </c>
-      <c r="C6">
-        <v>13</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>11</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>11</v>
-      </c>
-      <c r="J6">
-        <v>11</v>
-      </c>
-      <c r="K6">
-        <v>12</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -16225,180 +16039,6 @@
 
 <file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>6</v>
-      </c>
-      <c r="C4">
-        <v>6</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-      <c r="F4">
-        <v>4</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>8</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>10</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -16538,7 +16178,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16718,7 +16358,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16944,7 +16584,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17057,7 +16697,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17238,6 +16878,226 @@
       </c>
       <c r="M5">
         <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>9</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>8</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -17310,60 +17170,57 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
         <v>3</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
         <v>1</v>
       </c>
     </row>
@@ -17374,7 +17231,13 @@
       <c r="D4">
         <v>1</v>
       </c>
-      <c r="I4">
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -17386,37 +17249,37 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -17424,40 +17287,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
+      </c>
+      <c r="I6">
         <v>7</v>
       </c>
-      <c r="H6">
-        <v>9</v>
-      </c>
-      <c r="I6">
-        <v>6</v>
-      </c>
       <c r="J6">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -17467,10 +17330,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -17530,29 +17393,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17560,121 +17435,156 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C6">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="J6">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="L6">
+        <v>44</v>
+      </c>
+      <c r="M6">
         <v>12</v>
       </c>
-      <c r="M6">
-        <v>4</v>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>42</v>
+      </c>
+      <c r="D7">
+        <v>36</v>
+      </c>
+      <c r="E7">
+        <v>38</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>28</v>
+      </c>
+      <c r="H7">
+        <v>39</v>
+      </c>
+      <c r="I7">
+        <v>39</v>
+      </c>
+      <c r="J7">
+        <v>47</v>
+      </c>
+      <c r="K7">
+        <v>74</v>
+      </c>
+      <c r="L7">
+        <v>63</v>
+      </c>
+      <c r="M7">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -17748,28 +17658,22 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="F2">
         <v>1</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17779,22 +17683,13 @@
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
       <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="K3">
         <v>1</v>
       </c>
       <c r="L3">
@@ -17805,15 +17700,6 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
       <c r="L4">
         <v>1</v>
       </c>
@@ -17823,39 +17709,27 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="H5">
-        <v>8</v>
-      </c>
-      <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>7</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -17864,37 +17738,37 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="M6">
         <v>1</v>
@@ -17970,50 +17844,68 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>2</v>
       </c>
       <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
       </c>
       <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L4">
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
@@ -18025,25 +17917,37 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>12</v>
+      </c>
+      <c r="I5">
+        <v>17</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -18051,40 +17955,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -18094,10 +17998,10 @@
 
 <file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -18109,10 +18013,9 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -18135,173 +18038,132 @@
         <v>2020</v>
       </c>
       <c r="H1" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I1" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J1" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K1" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="E2">
         <v>2</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
       <c r="K2">
-        <v>4</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>6</v>
-      </c>
-      <c r="K3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>11</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>11</v>
-      </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
-      <c r="E6">
-        <v>19</v>
-      </c>
-      <c r="F6">
-        <v>24</v>
-      </c>
-      <c r="G6">
-        <v>15</v>
-      </c>
-      <c r="H6">
-        <v>17</v>
-      </c>
-      <c r="I6">
-        <v>19</v>
-      </c>
-      <c r="J6">
-        <v>14</v>
-      </c>
-      <c r="K6">
-        <v>24</v>
-      </c>
-      <c r="L6">
-        <v>10</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -20429,60 +20291,214 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
         <v>2016</v>
       </c>
-      <c r="C1" s="1">
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
         <v>2022</v>
       </c>
-      <c r="D1" s="1">
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>9</v>
+      </c>
+      <c r="L6">
+        <v>12</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-full-year.xlsx
+++ b/output/cta-violent-crime-full-year.xlsx
@@ -13,10 +13,10 @@
     <sheet name="Englewood" sheetId="4" r:id="rId4"/>
     <sheet name="Avondale" sheetId="5" r:id="rId5"/>
     <sheet name="Douglas" sheetId="6" r:id="rId6"/>
-    <sheet name="Grand Crossing" sheetId="7" r:id="rId7"/>
+    <sheet name="Grand Boulevard" sheetId="7" r:id="rId7"/>
     <sheet name="Austin" sheetId="8" r:id="rId8"/>
-    <sheet name="Grand Boulevard" sheetId="9" r:id="rId9"/>
-    <sheet name="Mount Greenwood" sheetId="10" r:id="rId10"/>
+    <sheet name="Mount Greenwood" sheetId="9" r:id="rId9"/>
+    <sheet name="Grand Crossing" sheetId="10" r:id="rId10"/>
     <sheet name="Washington Park" sheetId="11" r:id="rId11"/>
     <sheet name="South Chicago" sheetId="12" r:id="rId12"/>
     <sheet name="Humboldt Park" sheetId="13" r:id="rId13"/>
@@ -34,11 +34,11 @@
     <sheet name="Armour Square" sheetId="25" r:id="rId25"/>
     <sheet name="Roseland" sheetId="26" r:id="rId26"/>
     <sheet name="Fuller Park" sheetId="27" r:id="rId27"/>
-    <sheet name="O'Hare" sheetId="28" r:id="rId28"/>
-    <sheet name="Little Italy, UIC" sheetId="29" r:id="rId29"/>
-    <sheet name="Hyde Park" sheetId="30" r:id="rId30"/>
-    <sheet name="Calumet Heights" sheetId="31" r:id="rId31"/>
-    <sheet name="Kenwood" sheetId="32" r:id="rId32"/>
+    <sheet name="Little Italy, UIC" sheetId="28" r:id="rId28"/>
+    <sheet name="Hyde Park" sheetId="29" r:id="rId29"/>
+    <sheet name="Calumet Heights" sheetId="30" r:id="rId30"/>
+    <sheet name="Kenwood" sheetId="31" r:id="rId31"/>
+    <sheet name="O'Hare" sheetId="32" r:id="rId32"/>
     <sheet name="Chicago Lawn" sheetId="33" r:id="rId33"/>
     <sheet name="Wrigleyville" sheetId="34" r:id="rId34"/>
     <sheet name="Auburn Gresham" sheetId="35" r:id="rId35"/>
@@ -1101,60 +1101,261 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
         <v>2016</v>
       </c>
-      <c r="C1" s="1">
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
         <v>2022</v>
       </c>
-      <c r="D1" s="1">
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
       <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>7</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>7</v>
+      </c>
+      <c r="K2">
+        <v>7</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>19</v>
+      </c>
+      <c r="G3">
+        <v>9</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
+      </c>
+      <c r="J3">
+        <v>12</v>
+      </c>
+      <c r="K3">
+        <v>17</v>
+      </c>
+      <c r="L3">
+        <v>13</v>
+      </c>
+      <c r="M3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>24</v>
+      </c>
+      <c r="C6">
+        <v>37</v>
+      </c>
+      <c r="D6">
+        <v>21</v>
+      </c>
+      <c r="E6">
+        <v>22</v>
+      </c>
+      <c r="F6">
+        <v>27</v>
+      </c>
+      <c r="G6">
+        <v>15</v>
+      </c>
+      <c r="H6">
+        <v>25</v>
+      </c>
+      <c r="I6">
+        <v>21</v>
+      </c>
+      <c r="J6">
+        <v>26</v>
+      </c>
+      <c r="K6">
+        <v>49</v>
+      </c>
+      <c r="L6">
+        <v>44</v>
+      </c>
+      <c r="M6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>42</v>
+      </c>
+      <c r="D7">
+        <v>36</v>
+      </c>
+      <c r="E7">
+        <v>38</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>28</v>
+      </c>
+      <c r="H7">
+        <v>39</v>
+      </c>
+      <c r="I7">
+        <v>39</v>
+      </c>
+      <c r="J7">
+        <v>47</v>
+      </c>
+      <c r="K7">
+        <v>74</v>
+      </c>
+      <c r="L7">
+        <v>63</v>
+      </c>
+      <c r="M7">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -8610,209 +8811,6 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>7</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>5</v>
-      </c>
-      <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -9042,6 +9040,174 @@
       </c>
       <c r="M6">
         <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>11</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>13</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -9280,174 +9446,6 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4">
-        <v>11</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="H5">
-        <v>13</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -9615,7 +9613,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9747,6 +9745,209 @@
       </c>
       <c r="J6">
         <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7">
+        <v>9</v>
+      </c>
+      <c r="L7">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -17330,10 +17531,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -17393,41 +17594,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>6</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17435,156 +17624,121 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>8</v>
-      </c>
-      <c r="E3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>9</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="M4">
+        <v>4</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="G6">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H6">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="I6">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="M6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>32</v>
-      </c>
-      <c r="C7">
-        <v>42</v>
-      </c>
-      <c r="D7">
-        <v>36</v>
-      </c>
-      <c r="E7">
-        <v>38</v>
-      </c>
-      <c r="F7">
-        <v>53</v>
-      </c>
-      <c r="G7">
-        <v>28</v>
-      </c>
-      <c r="H7">
-        <v>39</v>
-      </c>
-      <c r="I7">
-        <v>39</v>
-      </c>
-      <c r="J7">
-        <v>47</v>
-      </c>
-      <c r="K7">
-        <v>74</v>
-      </c>
-      <c r="L7">
-        <v>63</v>
-      </c>
-      <c r="M7">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -20291,214 +20445,60 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>4</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>8</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>13</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>8</v>
-      </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>6</v>
-      </c>
-      <c r="J6">
-        <v>8</v>
-      </c>
-      <c r="K6">
-        <v>9</v>
-      </c>
-      <c r="L6">
-        <v>12</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-full-year.xlsx
+++ b/output/cta-violent-crime-full-year.xlsx
@@ -930,7 +930,7 @@
         <v>262</v>
       </c>
       <c r="M3">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1050,7 +1050,7 @@
         <v>467</v>
       </c>
       <c r="M6">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1091,7 +1091,7 @@
         <v>896</v>
       </c>
       <c r="M7">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -3231,7 +3231,7 @@
         <v>19</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3272,7 +3272,7 @@
         <v>27</v>
       </c>
       <c r="M7">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -3762,7 +3762,7 @@
         <v>33</v>
       </c>
       <c r="M8">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -4093,7 +4093,7 @@
         <v>27</v>
       </c>
       <c r="M19">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -6825,7 +6825,7 @@
         <v>896</v>
       </c>
       <c r="M98">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -19317,7 +19317,7 @@
         <v>14</v>
       </c>
       <c r="M3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -19430,7 +19430,7 @@
         <v>33</v>
       </c>
       <c r="M7">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-full-year.xlsx
+++ b/output/cta-violent-crime-full-year.xlsx
@@ -13,10 +13,10 @@
     <sheet name="Englewood" sheetId="4" r:id="rId4"/>
     <sheet name="Avondale" sheetId="5" r:id="rId5"/>
     <sheet name="Douglas" sheetId="6" r:id="rId6"/>
-    <sheet name="Grand Boulevard" sheetId="7" r:id="rId7"/>
+    <sheet name="Grand Crossing" sheetId="7" r:id="rId7"/>
     <sheet name="Austin" sheetId="8" r:id="rId8"/>
-    <sheet name="Mount Greenwood" sheetId="9" r:id="rId9"/>
-    <sheet name="Grand Crossing" sheetId="10" r:id="rId10"/>
+    <sheet name="Grand Boulevard" sheetId="9" r:id="rId9"/>
+    <sheet name="Mount Greenwood" sheetId="10" r:id="rId10"/>
     <sheet name="Washington Park" sheetId="11" r:id="rId11"/>
     <sheet name="South Chicago" sheetId="12" r:id="rId12"/>
     <sheet name="Humboldt Park" sheetId="13" r:id="rId13"/>
@@ -34,11 +34,11 @@
     <sheet name="Armour Square" sheetId="25" r:id="rId25"/>
     <sheet name="Roseland" sheetId="26" r:id="rId26"/>
     <sheet name="Fuller Park" sheetId="27" r:id="rId27"/>
-    <sheet name="Little Italy, UIC" sheetId="28" r:id="rId28"/>
-    <sheet name="Hyde Park" sheetId="29" r:id="rId29"/>
-    <sheet name="Calumet Heights" sheetId="30" r:id="rId30"/>
-    <sheet name="Kenwood" sheetId="31" r:id="rId31"/>
-    <sheet name="O'Hare" sheetId="32" r:id="rId32"/>
+    <sheet name="O'Hare" sheetId="28" r:id="rId28"/>
+    <sheet name="Little Italy, UIC" sheetId="29" r:id="rId29"/>
+    <sheet name="Hyde Park" sheetId="30" r:id="rId30"/>
+    <sheet name="Calumet Heights" sheetId="31" r:id="rId31"/>
+    <sheet name="Kenwood" sheetId="32" r:id="rId32"/>
     <sheet name="Chicago Lawn" sheetId="33" r:id="rId33"/>
     <sheet name="Wrigleyville" sheetId="34" r:id="rId34"/>
     <sheet name="Auburn Gresham" sheetId="35" r:id="rId35"/>
@@ -1101,261 +1101,60 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
       <c r="D2">
-        <v>7</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>6</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>7</v>
-      </c>
-      <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>8</v>
-      </c>
-      <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
-      </c>
-      <c r="G3">
-        <v>9</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
-      </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>12</v>
-      </c>
-      <c r="K3">
-        <v>17</v>
-      </c>
-      <c r="L3">
-        <v>13</v>
-      </c>
-      <c r="M3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>24</v>
-      </c>
-      <c r="C6">
-        <v>37</v>
-      </c>
-      <c r="D6">
-        <v>21</v>
-      </c>
-      <c r="E6">
-        <v>22</v>
-      </c>
-      <c r="F6">
-        <v>27</v>
-      </c>
-      <c r="G6">
-        <v>15</v>
-      </c>
-      <c r="H6">
-        <v>25</v>
-      </c>
-      <c r="I6">
-        <v>21</v>
-      </c>
-      <c r="J6">
-        <v>26</v>
-      </c>
-      <c r="K6">
-        <v>49</v>
-      </c>
-      <c r="L6">
-        <v>44</v>
-      </c>
-      <c r="M6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>32</v>
-      </c>
-      <c r="C7">
-        <v>42</v>
-      </c>
-      <c r="D7">
-        <v>36</v>
-      </c>
-      <c r="E7">
-        <v>38</v>
-      </c>
-      <c r="F7">
-        <v>53</v>
-      </c>
-      <c r="G7">
-        <v>28</v>
-      </c>
-      <c r="H7">
-        <v>39</v>
-      </c>
-      <c r="I7">
-        <v>39</v>
-      </c>
-      <c r="J7">
-        <v>47</v>
-      </c>
-      <c r="K7">
-        <v>74</v>
-      </c>
-      <c r="L7">
-        <v>63</v>
-      </c>
-      <c r="M7">
-        <v>25</v>
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -8811,6 +8610,209 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7">
+        <v>9</v>
+      </c>
+      <c r="L7">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -9040,174 +9042,6 @@
       </c>
       <c r="M6">
         <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4">
-        <v>11</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="H5">
-        <v>13</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -9446,6 +9280,174 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>11</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>13</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -9613,7 +9615,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9745,209 +9747,6 @@
       </c>
       <c r="J6">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>7</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>5</v>
-      </c>
-      <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -17531,10 +17330,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -17594,29 +17393,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17624,121 +17435,156 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C6">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="J6">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="L6">
+        <v>44</v>
+      </c>
+      <c r="M6">
         <v>12</v>
       </c>
-      <c r="M6">
-        <v>4</v>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>42</v>
+      </c>
+      <c r="D7">
+        <v>36</v>
+      </c>
+      <c r="E7">
+        <v>38</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>28</v>
+      </c>
+      <c r="H7">
+        <v>39</v>
+      </c>
+      <c r="I7">
+        <v>39</v>
+      </c>
+      <c r="J7">
+        <v>47</v>
+      </c>
+      <c r="K7">
+        <v>74</v>
+      </c>
+      <c r="L7">
+        <v>63</v>
+      </c>
+      <c r="M7">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -20445,60 +20291,214 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
         <v>2016</v>
       </c>
-      <c r="C1" s="1">
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
         <v>2022</v>
       </c>
-      <c r="D1" s="1">
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>9</v>
+      </c>
+      <c r="L6">
+        <v>12</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-full-year.xlsx
+++ b/output/cta-violent-crime-full-year.xlsx
@@ -1009,7 +1009,7 @@
         <v>5</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1091,7 +1091,7 @@
         <v>896</v>
       </c>
       <c r="M7">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
   </sheetData>
@@ -4572,7 +4572,7 @@
         <v>63</v>
       </c>
       <c r="M36">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -6748,7 +6748,7 @@
         <v>896</v>
       </c>
       <c r="M98">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
   </sheetData>
@@ -7491,6 +7491,9 @@
       <c r="L5">
         <v>1</v>
       </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
@@ -7571,7 +7574,7 @@
         <v>63</v>
       </c>
       <c r="M7">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-full-year.xlsx
+++ b/output/cta-violent-crime-full-year.xlsx
@@ -9,29 +9,29 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Austin" sheetId="3" r:id="rId3"/>
-    <sheet name="Avondale" sheetId="4" r:id="rId4"/>
-    <sheet name="Rush &amp; Division" sheetId="5" r:id="rId5"/>
-    <sheet name="Oakland" sheetId="6" r:id="rId6"/>
-    <sheet name="Chatham" sheetId="7" r:id="rId7"/>
-    <sheet name="New City" sheetId="8" r:id="rId8"/>
-    <sheet name="Belmont Cragin" sheetId="9" r:id="rId9"/>
-    <sheet name="Woodlawn" sheetId="10" r:id="rId10"/>
-    <sheet name="West Loop" sheetId="11" r:id="rId11"/>
-    <sheet name="Loop" sheetId="12" r:id="rId12"/>
-    <sheet name="Uptown" sheetId="13" r:id="rId13"/>
-    <sheet name="Lake View" sheetId="14" r:id="rId14"/>
-    <sheet name="North Lawndale" sheetId="15" r:id="rId15"/>
-    <sheet name="Grand Boulevard" sheetId="16" r:id="rId16"/>
-    <sheet name="West Town" sheetId="17" r:id="rId17"/>
-    <sheet name="South Shore" sheetId="18" r:id="rId18"/>
-    <sheet name="Englewood" sheetId="19" r:id="rId19"/>
-    <sheet name="Greektown" sheetId="20" r:id="rId20"/>
-    <sheet name="Edgewater" sheetId="21" r:id="rId21"/>
-    <sheet name="Little Italy, UIC" sheetId="22" r:id="rId22"/>
-    <sheet name="Gage Park" sheetId="23" r:id="rId23"/>
-    <sheet name="Humboldt Park" sheetId="24" r:id="rId24"/>
-    <sheet name="Grand Crossing" sheetId="25" r:id="rId25"/>
+    <sheet name="Grand Crossing" sheetId="3" r:id="rId3"/>
+    <sheet name="South Shore" sheetId="4" r:id="rId4"/>
+    <sheet name="Austin" sheetId="5" r:id="rId5"/>
+    <sheet name="Avondale" sheetId="6" r:id="rId6"/>
+    <sheet name="Rush &amp; Division" sheetId="7" r:id="rId7"/>
+    <sheet name="Oakland" sheetId="8" r:id="rId8"/>
+    <sheet name="Chatham" sheetId="9" r:id="rId9"/>
+    <sheet name="New City" sheetId="10" r:id="rId10"/>
+    <sheet name="Belmont Cragin" sheetId="11" r:id="rId11"/>
+    <sheet name="Woodlawn" sheetId="12" r:id="rId12"/>
+    <sheet name="West Loop" sheetId="13" r:id="rId13"/>
+    <sheet name="Loop" sheetId="14" r:id="rId14"/>
+    <sheet name="Uptown" sheetId="15" r:id="rId15"/>
+    <sheet name="Lake View" sheetId="16" r:id="rId16"/>
+    <sheet name="North Lawndale" sheetId="17" r:id="rId17"/>
+    <sheet name="Grand Boulevard" sheetId="18" r:id="rId18"/>
+    <sheet name="West Town" sheetId="19" r:id="rId19"/>
+    <sheet name="Englewood" sheetId="20" r:id="rId20"/>
+    <sheet name="Greektown" sheetId="21" r:id="rId21"/>
+    <sheet name="Edgewater" sheetId="22" r:id="rId22"/>
+    <sheet name="Little Italy, UIC" sheetId="23" r:id="rId23"/>
+    <sheet name="Gage Park" sheetId="24" r:id="rId24"/>
+    <sheet name="Humboldt Park" sheetId="25" r:id="rId25"/>
     <sheet name="Lower West Side" sheetId="26" r:id="rId26"/>
     <sheet name="Near South Side" sheetId="27" r:id="rId27"/>
     <sheet name="Sheffield &amp; DePaul" sheetId="28" r:id="rId28"/>
@@ -889,7 +889,7 @@
         <v>137</v>
       </c>
       <c r="M2">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -930,7 +930,7 @@
         <v>262</v>
       </c>
       <c r="M3">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1050,7 +1050,7 @@
         <v>467</v>
       </c>
       <c r="M6">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1091,7 +1091,7 @@
         <v>896</v>
       </c>
       <c r="M7">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
   </sheetData>
@@ -1100,6 +1100,348 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>10</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1316,7 +1658,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1553,7 +1895,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1693,7 +2035,7 @@
         <v>34</v>
       </c>
       <c r="M3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1830,489 +2172,7 @@
         <v>100</v>
       </c>
       <c r="M7">
-        <v>43</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>4</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>6</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
-      </c>
-      <c r="K3">
-        <v>7</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>9</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>14</v>
-      </c>
-      <c r="H5">
-        <v>7</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>11</v>
-      </c>
-      <c r="L5">
-        <v>8</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>14</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>11</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>22</v>
-      </c>
-      <c r="H6">
-        <v>14</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>16</v>
-      </c>
-      <c r="K6">
-        <v>23</v>
-      </c>
-      <c r="L6">
-        <v>13</v>
-      </c>
-      <c r="M6">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>6</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>11</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>14</v>
-      </c>
-      <c r="D5">
-        <v>12</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-      <c r="F5">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>11</v>
-      </c>
-      <c r="H5">
-        <v>17</v>
-      </c>
-      <c r="I5">
-        <v>20</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>10</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>23</v>
-      </c>
-      <c r="D6">
-        <v>14</v>
-      </c>
-      <c r="E6">
-        <v>18</v>
-      </c>
-      <c r="F6">
-        <v>18</v>
-      </c>
-      <c r="G6">
-        <v>19</v>
-      </c>
-      <c r="H6">
-        <v>27</v>
-      </c>
-      <c r="I6">
-        <v>26</v>
-      </c>
-      <c r="J6">
-        <v>16</v>
-      </c>
-      <c r="K6">
-        <v>24</v>
-      </c>
-      <c r="L6">
-        <v>20</v>
-      </c>
-      <c r="M6">
-        <v>12</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -2386,22 +2246,22 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2">
         <v>5</v>
@@ -2410,36 +2270,36 @@
         <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
       <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
         <v>2</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -2448,26 +2308,23 @@
         <v>4</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
@@ -2476,40 +2333,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J5">
         <v>5</v>
       </c>
       <c r="K5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2517,40 +2374,40 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
         <v>14</v>
       </c>
-      <c r="C6">
-        <v>26</v>
-      </c>
       <c r="D6">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H6">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I6">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K6">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L6">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2563,7 +2420,7 @@
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -2624,28 +2481,37 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2">
         <v>2</v>
       </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2656,77 +2522,98 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
       <c r="F3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
       </c>
       <c r="H4">
         <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>7</v>
-      </c>
       <c r="C5">
+        <v>14</v>
+      </c>
+      <c r="D5">
+        <v>12</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
         <v>11</v>
       </c>
-      <c r="D5">
-        <v>8</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
       <c r="G5">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2734,40 +2621,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="J6">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="L6">
+        <v>20</v>
+      </c>
+      <c r="M6">
         <v>12</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2843,77 +2730,86 @@
       <c r="B2">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
       <c r="D2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
       <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L3">
         <v>7</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
       <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -2922,40 +2818,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F5">
+        <v>35</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>15</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>9</v>
+      </c>
+      <c r="L5">
         <v>7</v>
       </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>6</v>
-      </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
       <c r="M5">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2963,40 +2859,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D6">
+        <v>29</v>
+      </c>
+      <c r="E6">
+        <v>24</v>
+      </c>
+      <c r="F6">
+        <v>42</v>
+      </c>
+      <c r="G6">
+        <v>18</v>
+      </c>
+      <c r="H6">
+        <v>18</v>
+      </c>
+      <c r="I6">
+        <v>21</v>
+      </c>
+      <c r="J6">
         <v>12</v>
       </c>
-      <c r="E6">
-        <v>12</v>
-      </c>
-      <c r="F6">
-        <v>8</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
       <c r="K6">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="L6">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M6">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3006,7 +2902,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -3069,9 +2965,6 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
       <c r="C2">
         <v>1</v>
       </c>
@@ -3081,23 +2974,14 @@
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
       <c r="H2">
         <v>2</v>
       </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
         <v>2</v>
@@ -3114,13 +2998,10 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>3</v>
@@ -3128,20 +3009,17 @@
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="H3">
-        <v>6</v>
-      </c>
       <c r="I3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3">
         <v>2</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -3149,84 +3027,89 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>11</v>
-      </c>
-      <c r="C4">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <v>6</v>
-      </c>
-      <c r="E4">
-        <v>7</v>
-      </c>
-      <c r="F4">
-        <v>7</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>8</v>
-      </c>
-      <c r="J4">
-        <v>12</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>9</v>
+      </c>
+      <c r="L6">
         <v>12</v>
       </c>
-      <c r="E5">
-        <v>11</v>
-      </c>
-      <c r="F5">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>9</v>
-      </c>
-      <c r="H5">
-        <v>11</v>
-      </c>
-      <c r="I5">
-        <v>12</v>
-      </c>
-      <c r="J5">
-        <v>15</v>
-      </c>
-      <c r="K5">
-        <v>9</v>
-      </c>
-      <c r="L5">
-        <v>9</v>
-      </c>
-      <c r="M5">
-        <v>6</v>
+      <c r="M6">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3236,7 +3119,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -3299,35 +3182,32 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
+      <c r="B2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M2">
         <v>4</v>
@@ -3337,160 +3217,128 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>5</v>
-      </c>
       <c r="C3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
         <v>7</v>
       </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>12</v>
-      </c>
-      <c r="K3">
-        <v>20</v>
-      </c>
-      <c r="L3">
-        <v>20</v>
-      </c>
       <c r="M3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
       <c r="J4">
         <v>1</v>
       </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
       <c r="L4">
         <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>7</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="G6">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>9</v>
+      </c>
+      <c r="L6">
         <v>15</v>
       </c>
-      <c r="K6">
-        <v>44</v>
-      </c>
-      <c r="L6">
-        <v>44</v>
-      </c>
       <c r="M6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>40</v>
-      </c>
-      <c r="C7">
-        <v>51</v>
-      </c>
-      <c r="D7">
-        <v>50</v>
-      </c>
-      <c r="E7">
-        <v>33</v>
-      </c>
-      <c r="F7">
-        <v>63</v>
-      </c>
-      <c r="G7">
-        <v>50</v>
-      </c>
-      <c r="H7">
-        <v>47</v>
-      </c>
-      <c r="I7">
-        <v>45</v>
-      </c>
-      <c r="J7">
-        <v>37</v>
-      </c>
-      <c r="K7">
-        <v>68</v>
-      </c>
-      <c r="L7">
-        <v>71</v>
-      </c>
-      <c r="M7">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -4676,7 +4524,7 @@
         <v>63</v>
       </c>
       <c r="M36">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -5283,7 +5131,7 @@
         <v>100</v>
       </c>
       <c r="M53">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -6286,7 +6134,7 @@
         <v>9</v>
       </c>
       <c r="M82">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -6855,7 +6703,7 @@
         <v>896</v>
       </c>
       <c r="M98">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
   </sheetData>
@@ -6964,6 +6812,270 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>7</v>
+      </c>
+      <c r="H2">
+        <v>11</v>
+      </c>
+      <c r="I2">
+        <v>10</v>
+      </c>
+      <c r="J2">
+        <v>9</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>6</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>18</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>12</v>
+      </c>
+      <c r="G3">
+        <v>11</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
+      </c>
+      <c r="J3">
+        <v>12</v>
+      </c>
+      <c r="K3">
+        <v>20</v>
+      </c>
+      <c r="L3">
+        <v>20</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>34</v>
+      </c>
+      <c r="C6">
+        <v>45</v>
+      </c>
+      <c r="D6">
+        <v>25</v>
+      </c>
+      <c r="E6">
+        <v>22</v>
+      </c>
+      <c r="F6">
+        <v>42</v>
+      </c>
+      <c r="G6">
+        <v>32</v>
+      </c>
+      <c r="H6">
+        <v>26</v>
+      </c>
+      <c r="I6">
+        <v>21</v>
+      </c>
+      <c r="J6">
+        <v>15</v>
+      </c>
+      <c r="K6">
+        <v>44</v>
+      </c>
+      <c r="L6">
+        <v>44</v>
+      </c>
+      <c r="M6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>40</v>
+      </c>
+      <c r="C7">
+        <v>51</v>
+      </c>
+      <c r="D7">
+        <v>50</v>
+      </c>
+      <c r="E7">
+        <v>33</v>
+      </c>
+      <c r="F7">
+        <v>63</v>
+      </c>
+      <c r="G7">
+        <v>50</v>
+      </c>
+      <c r="H7">
+        <v>47</v>
+      </c>
+      <c r="I7">
+        <v>45</v>
+      </c>
+      <c r="J7">
+        <v>37</v>
+      </c>
+      <c r="K7">
+        <v>68</v>
+      </c>
+      <c r="L7">
+        <v>71</v>
+      </c>
+      <c r="M7">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -7132,226 +7244,6 @@
       </c>
       <c r="L6">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>12</v>
-      </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>16</v>
-      </c>
-      <c r="L5">
-        <v>8</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>13</v>
-      </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
-      </c>
-      <c r="K6">
-        <v>21</v>
-      </c>
-      <c r="L6">
-        <v>13</v>
-      </c>
-      <c r="M6">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -7425,19 +7317,19 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -7446,66 +7338,48 @@
         <v>5</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
       <c r="M4">
         <v>1</v>
       </c>
@@ -7515,40 +7389,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>12</v>
+      </c>
+      <c r="I5">
         <v>7</v>
       </c>
-      <c r="D5">
-        <v>11</v>
-      </c>
-      <c r="E5">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>25</v>
-      </c>
-      <c r="G5">
-        <v>15</v>
-      </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>9</v>
-      </c>
       <c r="J5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -7556,40 +7430,40 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
         <v>10</v>
       </c>
-      <c r="C6">
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>13</v>
+      </c>
+      <c r="I6">
+        <v>12</v>
+      </c>
+      <c r="J6">
         <v>10</v>
       </c>
-      <c r="D6">
-        <v>14</v>
-      </c>
-      <c r="E6">
-        <v>23</v>
-      </c>
-      <c r="F6">
-        <v>28</v>
-      </c>
-      <c r="G6">
-        <v>16</v>
-      </c>
-      <c r="H6">
-        <v>14</v>
-      </c>
-      <c r="I6">
-        <v>17</v>
-      </c>
-      <c r="J6">
-        <v>16</v>
-      </c>
       <c r="K6">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="L6">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -7598,6 +7472,244 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>11</v>
+      </c>
+      <c r="E5">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>25</v>
+      </c>
+      <c r="G5">
+        <v>15</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5">
+        <v>11</v>
+      </c>
+      <c r="K5">
+        <v>18</v>
+      </c>
+      <c r="L5">
+        <v>11</v>
+      </c>
+      <c r="M5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>14</v>
+      </c>
+      <c r="E6">
+        <v>23</v>
+      </c>
+      <c r="F6">
+        <v>28</v>
+      </c>
+      <c r="G6">
+        <v>16</v>
+      </c>
+      <c r="H6">
+        <v>14</v>
+      </c>
+      <c r="I6">
+        <v>17</v>
+      </c>
+      <c r="J6">
+        <v>16</v>
+      </c>
+      <c r="K6">
+        <v>31</v>
+      </c>
+      <c r="L6">
+        <v>22</v>
+      </c>
+      <c r="M6">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7822,7 +7934,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8050,273 +8162,6 @@
       </c>
       <c r="M6">
         <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>7</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>6</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>7</v>
-      </c>
-      <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>8</v>
-      </c>
-      <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
-      </c>
-      <c r="G3">
-        <v>9</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
-      </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>12</v>
-      </c>
-      <c r="K3">
-        <v>17</v>
-      </c>
-      <c r="L3">
-        <v>13</v>
-      </c>
-      <c r="M3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>24</v>
-      </c>
-      <c r="C6">
-        <v>37</v>
-      </c>
-      <c r="D6">
-        <v>21</v>
-      </c>
-      <c r="E6">
-        <v>22</v>
-      </c>
-      <c r="F6">
-        <v>27</v>
-      </c>
-      <c r="G6">
-        <v>15</v>
-      </c>
-      <c r="H6">
-        <v>25</v>
-      </c>
-      <c r="I6">
-        <v>21</v>
-      </c>
-      <c r="J6">
-        <v>26</v>
-      </c>
-      <c r="K6">
-        <v>49</v>
-      </c>
-      <c r="L6">
-        <v>44</v>
-      </c>
-      <c r="M6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>32</v>
-      </c>
-      <c r="C7">
-        <v>42</v>
-      </c>
-      <c r="D7">
-        <v>36</v>
-      </c>
-      <c r="E7">
-        <v>38</v>
-      </c>
-      <c r="F7">
-        <v>53</v>
-      </c>
-      <c r="G7">
-        <v>28</v>
-      </c>
-      <c r="H7">
-        <v>39</v>
-      </c>
-      <c r="I7">
-        <v>39</v>
-      </c>
-      <c r="J7">
-        <v>47</v>
-      </c>
-      <c r="K7">
-        <v>74</v>
-      </c>
-      <c r="L7">
-        <v>63</v>
-      </c>
-      <c r="M7">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -9302,31 +9147,31 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>4</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K2">
         <v>7</v>
@@ -9335,7 +9180,7 @@
         <v>5</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9343,59 +9188,53 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H3">
         <v>8</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
       <c r="E4">
         <v>1</v>
       </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
       <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
         <v>2</v>
       </c>
       <c r="M4">
@@ -9406,7 +9245,19 @@
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
       <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -9415,40 +9266,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D6">
+        <v>21</v>
+      </c>
+      <c r="E6">
         <v>22</v>
       </c>
-      <c r="E6">
-        <v>44</v>
-      </c>
       <c r="F6">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H6">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I6">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J6">
         <v>26</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="L6">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="M6">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9459,37 +9310,37 @@
         <v>32</v>
       </c>
       <c r="C7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E7">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F7">
         <v>53</v>
       </c>
       <c r="G7">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H7">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="I7">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="J7">
         <v>47</v>
       </c>
       <c r="K7">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="L7">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="M7">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -11599,10 +11450,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -11663,7 +11514,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -11672,10 +11523,16 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -11684,123 +11541,136 @@
         <v>1</v>
       </c>
       <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
         <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
+      <c r="H3">
+        <v>6</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
       <c r="J3">
         <v>2</v>
       </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
       <c r="L3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4">
+        <v>7</v>
+      </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>8</v>
+      </c>
+      <c r="J4">
+        <v>12</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
         <v>9</v>
       </c>
-      <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>6</v>
+      <c r="M5">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -13614,7 +13484,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -13678,25 +13548,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -13704,124 +13589,153 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="J3">
+        <v>10</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
       <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-      <c r="F5">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>14</v>
-      </c>
-      <c r="H5">
-        <v>7</v>
-      </c>
-      <c r="I5">
-        <v>9</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="G6">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H6">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I6">
+        <v>34</v>
+      </c>
+      <c r="J6">
+        <v>26</v>
+      </c>
+      <c r="K6">
+        <v>24</v>
+      </c>
+      <c r="L6">
         <v>14</v>
       </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>7</v>
-      </c>
       <c r="M6">
-        <v>3</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>40</v>
+      </c>
+      <c r="D7">
+        <v>32</v>
+      </c>
+      <c r="E7">
+        <v>57</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>34</v>
+      </c>
+      <c r="H7">
+        <v>63</v>
+      </c>
+      <c r="I7">
+        <v>44</v>
+      </c>
+      <c r="J7">
+        <v>47</v>
+      </c>
+      <c r="K7">
+        <v>46</v>
+      </c>
+      <c r="L7">
+        <v>33</v>
+      </c>
+      <c r="M7">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -15477,79 +15391,137 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
     <col min="5" max="5" width="4.7109375" customWidth="1"/>
     <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
         <v>2017</v>
       </c>
-      <c r="C1" s="1">
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
         <v>2019</v>
       </c>
-      <c r="D1" s="1">
+      <c r="G1" s="1">
         <v>2020</v>
       </c>
-      <c r="E1" s="1">
+      <c r="H1" s="1">
         <v>2021</v>
       </c>
-      <c r="F1" s="1">
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
       <c r="E2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
       <c r="E3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -15558,10 +15530,69 @@
         <v>3</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>9</v>
+      </c>
+      <c r="K6">
+        <v>6</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -17328,7 +17359,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -17391,38 +17422,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
+      <c r="B2">
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
       <c r="H2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>8</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17430,13 +17449,10 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -17445,132 +17461,112 @@
         <v>4</v>
       </c>
       <c r="G3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>6</v>
-      </c>
-      <c r="J3">
         <v>4</v>
       </c>
       <c r="K3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="K4">
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>9</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
         <v>13</v>
       </c>
-      <c r="F6">
-        <v>19</v>
-      </c>
       <c r="G6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J6">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>8</v>
-      </c>
-      <c r="C7">
-        <v>11</v>
-      </c>
-      <c r="D7">
-        <v>29</v>
-      </c>
-      <c r="E7">
-        <v>17</v>
-      </c>
-      <c r="F7">
-        <v>26</v>
-      </c>
-      <c r="G7">
-        <v>25</v>
-      </c>
-      <c r="H7">
-        <v>13</v>
-      </c>
-      <c r="I7">
-        <v>24</v>
-      </c>
-      <c r="J7">
-        <v>21</v>
-      </c>
-      <c r="K7">
-        <v>37</v>
-      </c>
-      <c r="L7">
-        <v>27</v>
-      </c>
-      <c r="M7">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -19168,7 +19164,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -19177,80 +19173,41 @@
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
     <col min="5" max="5" width="4.7109375" customWidth="1"/>
     <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="D1" s="1">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="E1" s="1">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
@@ -19259,90 +19216,39 @@
       <c r="E3">
         <v>2</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B4">
-        <v>6</v>
-      </c>
-      <c r="C4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
       <c r="F4">
-        <v>4</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>10</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -20431,7 +20337,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -20445,9 +20351,11 @@
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -20464,122 +20372,214 @@
         <v>2018</v>
       </c>
       <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
         <v>2020</v>
       </c>
-      <c r="G1" s="1">
+      <c r="H1" s="1">
         <v>2021</v>
       </c>
-      <c r="H1" s="1">
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="I1" s="1">
+      <c r="K1" s="1">
         <v>2024</v>
       </c>
-      <c r="J1" s="1">
+      <c r="L1" s="1">
         <v>2025</v>
       </c>
-      <c r="K1" s="1">
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>5</v>
       </c>
       <c r="K2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>8</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>7</v>
+      </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>8</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="I3">
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
         <v>5</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K6">
-        <v>2</v>
+        <v>18</v>
+      </c>
+      <c r="L6">
+        <v>19</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>11</v>
+      </c>
+      <c r="D7">
+        <v>29</v>
+      </c>
+      <c r="E7">
+        <v>17</v>
+      </c>
+      <c r="F7">
+        <v>26</v>
+      </c>
+      <c r="G7">
+        <v>25</v>
+      </c>
+      <c r="H7">
+        <v>13</v>
+      </c>
+      <c r="I7">
+        <v>24</v>
+      </c>
+      <c r="J7">
+        <v>21</v>
+      </c>
+      <c r="K7">
+        <v>37</v>
+      </c>
+      <c r="L7">
+        <v>27</v>
+      </c>
+      <c r="M7">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-full-year.xlsx
+++ b/output/cta-violent-crime-full-year.xlsx
@@ -9,31 +9,31 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Grand Crossing" sheetId="3" r:id="rId3"/>
-    <sheet name="South Shore" sheetId="4" r:id="rId4"/>
-    <sheet name="Austin" sheetId="5" r:id="rId5"/>
-    <sheet name="Avondale" sheetId="6" r:id="rId6"/>
-    <sheet name="Rush &amp; Division" sheetId="7" r:id="rId7"/>
-    <sheet name="Oakland" sheetId="8" r:id="rId8"/>
-    <sheet name="Chatham" sheetId="9" r:id="rId9"/>
-    <sheet name="New City" sheetId="10" r:id="rId10"/>
-    <sheet name="Belmont Cragin" sheetId="11" r:id="rId11"/>
-    <sheet name="Woodlawn" sheetId="12" r:id="rId12"/>
-    <sheet name="West Loop" sheetId="13" r:id="rId13"/>
-    <sheet name="Loop" sheetId="14" r:id="rId14"/>
-    <sheet name="Uptown" sheetId="15" r:id="rId15"/>
-    <sheet name="Lake View" sheetId="16" r:id="rId16"/>
-    <sheet name="North Lawndale" sheetId="17" r:id="rId17"/>
-    <sheet name="Grand Boulevard" sheetId="18" r:id="rId18"/>
-    <sheet name="West Town" sheetId="19" r:id="rId19"/>
-    <sheet name="Englewood" sheetId="20" r:id="rId20"/>
-    <sheet name="Greektown" sheetId="21" r:id="rId21"/>
-    <sheet name="Edgewater" sheetId="22" r:id="rId22"/>
-    <sheet name="Little Italy, UIC" sheetId="23" r:id="rId23"/>
-    <sheet name="Gage Park" sheetId="24" r:id="rId24"/>
-    <sheet name="Humboldt Park" sheetId="25" r:id="rId25"/>
-    <sheet name="Lower West Side" sheetId="26" r:id="rId26"/>
-    <sheet name="Near South Side" sheetId="27" r:id="rId27"/>
+    <sheet name="Near South Side" sheetId="3" r:id="rId3"/>
+    <sheet name="Grand Crossing" sheetId="4" r:id="rId4"/>
+    <sheet name="South Shore" sheetId="5" r:id="rId5"/>
+    <sheet name="Austin" sheetId="6" r:id="rId6"/>
+    <sheet name="Avondale" sheetId="7" r:id="rId7"/>
+    <sheet name="Rush &amp; Division" sheetId="8" r:id="rId8"/>
+    <sheet name="Oakland" sheetId="9" r:id="rId9"/>
+    <sheet name="Chatham" sheetId="10" r:id="rId10"/>
+    <sheet name="New City" sheetId="11" r:id="rId11"/>
+    <sheet name="Belmont Cragin" sheetId="12" r:id="rId12"/>
+    <sheet name="Woodlawn" sheetId="13" r:id="rId13"/>
+    <sheet name="West Loop" sheetId="14" r:id="rId14"/>
+    <sheet name="Loop" sheetId="15" r:id="rId15"/>
+    <sheet name="Uptown" sheetId="16" r:id="rId16"/>
+    <sheet name="Lake View" sheetId="17" r:id="rId17"/>
+    <sheet name="North Lawndale" sheetId="18" r:id="rId18"/>
+    <sheet name="Grand Boulevard" sheetId="19" r:id="rId19"/>
+    <sheet name="West Town" sheetId="20" r:id="rId20"/>
+    <sheet name="Englewood" sheetId="21" r:id="rId21"/>
+    <sheet name="Greektown" sheetId="22" r:id="rId22"/>
+    <sheet name="Edgewater" sheetId="23" r:id="rId23"/>
+    <sheet name="Little Italy, UIC" sheetId="24" r:id="rId24"/>
+    <sheet name="Gage Park" sheetId="25" r:id="rId25"/>
+    <sheet name="Humboldt Park" sheetId="26" r:id="rId26"/>
+    <sheet name="Lower West Side" sheetId="27" r:id="rId27"/>
     <sheet name="Sheffield &amp; DePaul" sheetId="28" r:id="rId28"/>
     <sheet name="Roseland" sheetId="29" r:id="rId29"/>
     <sheet name="Norwood Park" sheetId="30" r:id="rId30"/>
@@ -1050,7 +1050,7 @@
         <v>467</v>
       </c>
       <c r="M6">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1091,7 +1091,7 @@
         <v>896</v>
       </c>
       <c r="M7">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
   </sheetData>
@@ -1100,6 +1100,258 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>5</v>
+      </c>
+      <c r="K2">
+        <v>8</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>7</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>8</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
+      </c>
+      <c r="I3">
+        <v>6</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>9</v>
+      </c>
+      <c r="D6">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>13</v>
+      </c>
+      <c r="F6">
+        <v>19</v>
+      </c>
+      <c r="G6">
+        <v>15</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>15</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+      <c r="K6">
+        <v>18</v>
+      </c>
+      <c r="L6">
+        <v>19</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>11</v>
+      </c>
+      <c r="D7">
+        <v>29</v>
+      </c>
+      <c r="E7">
+        <v>17</v>
+      </c>
+      <c r="F7">
+        <v>26</v>
+      </c>
+      <c r="G7">
+        <v>25</v>
+      </c>
+      <c r="H7">
+        <v>13</v>
+      </c>
+      <c r="I7">
+        <v>24</v>
+      </c>
+      <c r="J7">
+        <v>21</v>
+      </c>
+      <c r="K7">
+        <v>37</v>
+      </c>
+      <c r="L7">
+        <v>27</v>
+      </c>
+      <c r="M7">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1283,7 +1535,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1441,7 +1693,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1651,243 +1903,6 @@
       </c>
       <c r="M6">
         <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>4</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>9</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>7</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>7</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>8</v>
-      </c>
-      <c r="E7">
-        <v>9</v>
-      </c>
-      <c r="F7">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>12</v>
-      </c>
-      <c r="H7">
-        <v>16</v>
-      </c>
-      <c r="I7">
-        <v>13</v>
-      </c>
-      <c r="J7">
-        <v>8</v>
-      </c>
-      <c r="K7">
-        <v>14</v>
-      </c>
-      <c r="L7">
-        <v>15</v>
-      </c>
-      <c r="M7">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1961,37 +1976,28 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>12</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I2">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="M2">
         <v>2</v>
@@ -2002,94 +2008,55 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>13</v>
-      </c>
-      <c r="C3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>34</v>
-      </c>
-      <c r="M3">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
       <c r="F4">
         <v>1</v>
       </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>4</v>
-      </c>
       <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>5</v>
-      </c>
-      <c r="M4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
+      <c r="I5">
         <v>1</v>
       </c>
     </row>
@@ -2098,40 +2065,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="H6">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="I6">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2139,40 +2106,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>79</v>
+        <v>8</v>
       </c>
       <c r="E7">
-        <v>92</v>
+        <v>9</v>
       </c>
       <c r="F7">
-        <v>92</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>88</v>
+        <v>12</v>
       </c>
       <c r="H7">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="I7">
-        <v>130</v>
+        <v>13</v>
       </c>
       <c r="J7">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="M7">
-        <v>44</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -2182,7 +2149,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -2246,37 +2213,37 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="M2">
         <v>2</v>
@@ -2286,84 +2253,93 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>13</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>4</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>5</v>
+      </c>
+      <c r="M4">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>9</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>7</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -2371,43 +2347,84 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="G6">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="H6">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="J6">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="K6">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="L6">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="M6">
-        <v>8</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>49</v>
+      </c>
+      <c r="C7">
+        <v>62</v>
+      </c>
+      <c r="D7">
+        <v>79</v>
+      </c>
+      <c r="E7">
+        <v>92</v>
+      </c>
+      <c r="F7">
+        <v>92</v>
+      </c>
+      <c r="G7">
+        <v>88</v>
+      </c>
+      <c r="H7">
+        <v>120</v>
+      </c>
+      <c r="I7">
+        <v>130</v>
+      </c>
+      <c r="J7">
+        <v>131</v>
+      </c>
+      <c r="K7">
+        <v>91</v>
+      </c>
+      <c r="L7">
+        <v>100</v>
+      </c>
+      <c r="M7">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -2480,6 +2497,9 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
       <c r="C2">
         <v>4</v>
       </c>
@@ -2487,133 +2507,118 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
         <v>7</v>
       </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>11</v>
-      </c>
       <c r="K3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+      <c r="B4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
       <c r="C5">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
         <v>14</v>
       </c>
-      <c r="D5">
-        <v>12</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-      <c r="F5">
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
         <v>11</v>
       </c>
-      <c r="G5">
-        <v>11</v>
-      </c>
-      <c r="H5">
-        <v>17</v>
-      </c>
-      <c r="I5">
-        <v>20</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>10</v>
-      </c>
       <c r="L5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2621,40 +2626,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>22</v>
+      </c>
+      <c r="H6">
         <v>14</v>
       </c>
-      <c r="E6">
-        <v>18</v>
-      </c>
-      <c r="F6">
-        <v>18</v>
-      </c>
-      <c r="G6">
-        <v>19</v>
-      </c>
-      <c r="H6">
-        <v>27</v>
-      </c>
       <c r="I6">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>16</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L6">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2727,41 +2732,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2769,89 +2771,101 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3">
         <v>5</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L3">
         <v>7</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
       <c r="H4">
         <v>1</v>
       </c>
-      <c r="J4">
-        <v>1</v>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
+      <c r="C5">
+        <v>14</v>
+      </c>
+      <c r="D5">
         <v>12</v>
       </c>
-      <c r="C5">
-        <v>21</v>
-      </c>
-      <c r="D5">
-        <v>28</v>
-      </c>
       <c r="E5">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H5">
+        <v>17</v>
+      </c>
+      <c r="I5">
+        <v>20</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
         <v>10</v>
       </c>
-      <c r="I5">
-        <v>15</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>9</v>
-      </c>
       <c r="L5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2859,40 +2873,40 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>23</v>
+      </c>
+      <c r="D6">
         <v>14</v>
       </c>
-      <c r="C6">
+      <c r="E6">
+        <v>18</v>
+      </c>
+      <c r="F6">
+        <v>18</v>
+      </c>
+      <c r="G6">
+        <v>19</v>
+      </c>
+      <c r="H6">
+        <v>27</v>
+      </c>
+      <c r="I6">
         <v>26</v>
       </c>
-      <c r="D6">
-        <v>29</v>
-      </c>
-      <c r="E6">
+      <c r="J6">
+        <v>16</v>
+      </c>
+      <c r="K6">
         <v>24</v>
       </c>
-      <c r="F6">
-        <v>42</v>
-      </c>
-      <c r="G6">
-        <v>18</v>
-      </c>
-      <c r="H6">
-        <v>18</v>
-      </c>
-      <c r="I6">
-        <v>21</v>
-      </c>
-      <c r="J6">
+      <c r="L6">
+        <v>20</v>
+      </c>
+      <c r="M6">
         <v>12</v>
-      </c>
-      <c r="K6">
-        <v>18</v>
-      </c>
-      <c r="L6">
-        <v>18</v>
-      </c>
-      <c r="M6">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2901,6 +2915,244 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>6</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>21</v>
+      </c>
+      <c r="D5">
+        <v>28</v>
+      </c>
+      <c r="E5">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>35</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>15</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>9</v>
+      </c>
+      <c r="L5">
+        <v>7</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>14</v>
+      </c>
+      <c r="C6">
+        <v>26</v>
+      </c>
+      <c r="D6">
+        <v>29</v>
+      </c>
+      <c r="E6">
+        <v>24</v>
+      </c>
+      <c r="F6">
+        <v>42</v>
+      </c>
+      <c r="G6">
+        <v>18</v>
+      </c>
+      <c r="H6">
+        <v>18</v>
+      </c>
+      <c r="I6">
+        <v>21</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+      <c r="K6">
+        <v>18</v>
+      </c>
+      <c r="L6">
+        <v>18</v>
+      </c>
+      <c r="M6">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3110,235 +3362,6 @@
       </c>
       <c r="M6">
         <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>8</v>
-      </c>
-      <c r="E5">
-        <v>8</v>
-      </c>
-      <c r="F5">
-        <v>7</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>6</v>
-      </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>12</v>
-      </c>
-      <c r="E6">
-        <v>12</v>
-      </c>
-      <c r="F6">
-        <v>8</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>9</v>
-      </c>
-      <c r="L6">
-        <v>15</v>
-      </c>
-      <c r="M6">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -5407,7 +5430,7 @@
         <v>4</v>
       </c>
       <c r="M62">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -6703,7 +6726,7 @@
         <v>896</v>
       </c>
       <c r="M98">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
   </sheetData>
@@ -6812,6 +6835,235 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>7</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="I5">
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>12</v>
+      </c>
+      <c r="E6">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>9</v>
+      </c>
+      <c r="L6">
+        <v>15</v>
+      </c>
+      <c r="M6">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -7074,7 +7326,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7244,226 +7496,6 @@
       </c>
       <c r="L6">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>12</v>
-      </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>16</v>
-      </c>
-      <c r="L5">
-        <v>8</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>13</v>
-      </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
-      </c>
-      <c r="K6">
-        <v>21</v>
-      </c>
-      <c r="L6">
-        <v>13</v>
-      </c>
-      <c r="M6">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -7537,19 +7569,19 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -7558,66 +7590,48 @@
         <v>5</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
       <c r="M4">
         <v>1</v>
       </c>
@@ -7627,40 +7641,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>12</v>
+      </c>
+      <c r="I5">
         <v>7</v>
       </c>
-      <c r="D5">
-        <v>11</v>
-      </c>
-      <c r="E5">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>25</v>
-      </c>
-      <c r="G5">
-        <v>15</v>
-      </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>9</v>
-      </c>
       <c r="J5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -7668,40 +7682,40 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
         <v>10</v>
       </c>
-      <c r="C6">
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>13</v>
+      </c>
+      <c r="I6">
+        <v>12</v>
+      </c>
+      <c r="J6">
         <v>10</v>
       </c>
-      <c r="D6">
-        <v>14</v>
-      </c>
-      <c r="E6">
-        <v>23</v>
-      </c>
-      <c r="F6">
-        <v>28</v>
-      </c>
-      <c r="G6">
-        <v>16</v>
-      </c>
-      <c r="H6">
-        <v>14</v>
-      </c>
-      <c r="I6">
-        <v>17</v>
-      </c>
-      <c r="J6">
-        <v>16</v>
-      </c>
       <c r="K6">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="L6">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -7710,6 +7724,244 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>11</v>
+      </c>
+      <c r="E5">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>25</v>
+      </c>
+      <c r="G5">
+        <v>15</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5">
+        <v>11</v>
+      </c>
+      <c r="K5">
+        <v>18</v>
+      </c>
+      <c r="L5">
+        <v>11</v>
+      </c>
+      <c r="M5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>14</v>
+      </c>
+      <c r="E6">
+        <v>23</v>
+      </c>
+      <c r="F6">
+        <v>28</v>
+      </c>
+      <c r="G6">
+        <v>16</v>
+      </c>
+      <c r="H6">
+        <v>14</v>
+      </c>
+      <c r="I6">
+        <v>17</v>
+      </c>
+      <c r="J6">
+        <v>16</v>
+      </c>
+      <c r="K6">
+        <v>31</v>
+      </c>
+      <c r="L6">
+        <v>22</v>
+      </c>
+      <c r="M6">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7934,7 +8186,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8169,7 +8421,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8362,231 +8614,6 @@
       </c>
       <c r="M5">
         <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>7</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>6</v>
-      </c>
-      <c r="E7">
-        <v>7</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="G7">
-        <v>8</v>
-      </c>
-      <c r="H7">
-        <v>9</v>
-      </c>
-      <c r="I7">
-        <v>13</v>
-      </c>
-      <c r="J7">
-        <v>8</v>
-      </c>
-      <c r="K7">
-        <v>8</v>
-      </c>
-      <c r="L7">
-        <v>4</v>
-      </c>
-      <c r="M7">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -9146,41 +9173,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>7</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
       <c r="F2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9188,56 +9200,41 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>17</v>
-      </c>
-      <c r="L3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
       <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -9245,19 +9242,7 @@
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
       <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -9266,40 +9251,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9307,40 +9292,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F7">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="G7">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="H7">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="J7">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="M7">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -11450,10 +11435,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -11514,40 +11499,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -11555,122 +11540,159 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>11</v>
-      </c>
-      <c r="C4">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>7</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>12</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>24</v>
+      </c>
+      <c r="C6">
+        <v>37</v>
+      </c>
+      <c r="D6">
+        <v>21</v>
+      </c>
+      <c r="E6">
+        <v>22</v>
+      </c>
+      <c r="F6">
+        <v>27</v>
+      </c>
+      <c r="G6">
         <v>15</v>
       </c>
-      <c r="C5">
-        <v>15</v>
-      </c>
-      <c r="D5">
-        <v>12</v>
-      </c>
-      <c r="E5">
-        <v>11</v>
-      </c>
-      <c r="F5">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>9</v>
-      </c>
-      <c r="H5">
-        <v>11</v>
-      </c>
-      <c r="I5">
-        <v>12</v>
-      </c>
-      <c r="J5">
-        <v>15</v>
-      </c>
-      <c r="K5">
-        <v>9</v>
-      </c>
-      <c r="L5">
-        <v>9</v>
-      </c>
-      <c r="M5">
-        <v>7</v>
+      <c r="H6">
+        <v>25</v>
+      </c>
+      <c r="I6">
+        <v>21</v>
+      </c>
+      <c r="J6">
+        <v>26</v>
+      </c>
+      <c r="K6">
+        <v>49</v>
+      </c>
+      <c r="L6">
+        <v>44</v>
+      </c>
+      <c r="M6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>42</v>
+      </c>
+      <c r="D7">
+        <v>36</v>
+      </c>
+      <c r="E7">
+        <v>38</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>28</v>
+      </c>
+      <c r="H7">
+        <v>39</v>
+      </c>
+      <c r="I7">
+        <v>39</v>
+      </c>
+      <c r="J7">
+        <v>47</v>
+      </c>
+      <c r="K7">
+        <v>74</v>
+      </c>
+      <c r="L7">
+        <v>63</v>
+      </c>
+      <c r="M7">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -13484,10 +13506,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -13548,40 +13570,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -13589,153 +13611,122 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="F4">
+        <v>7</v>
+      </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>15</v>
+      </c>
+      <c r="D5">
+        <v>12</v>
+      </c>
+      <c r="E5">
+        <v>11</v>
+      </c>
+      <c r="F5">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5">
+        <v>11</v>
+      </c>
+      <c r="I5">
+        <v>12</v>
+      </c>
+      <c r="J5">
+        <v>15</v>
       </c>
       <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>23</v>
-      </c>
-      <c r="C6">
-        <v>31</v>
-      </c>
-      <c r="D6">
-        <v>22</v>
-      </c>
-      <c r="E6">
-        <v>44</v>
-      </c>
-      <c r="F6">
-        <v>38</v>
-      </c>
-      <c r="G6">
-        <v>24</v>
-      </c>
-      <c r="H6">
-        <v>50</v>
-      </c>
-      <c r="I6">
-        <v>34</v>
-      </c>
-      <c r="J6">
-        <v>26</v>
-      </c>
-      <c r="K6">
-        <v>24</v>
-      </c>
-      <c r="L6">
-        <v>14</v>
-      </c>
-      <c r="M6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>32</v>
-      </c>
-      <c r="C7">
-        <v>40</v>
-      </c>
-      <c r="D7">
-        <v>32</v>
-      </c>
-      <c r="E7">
-        <v>57</v>
-      </c>
-      <c r="F7">
-        <v>53</v>
-      </c>
-      <c r="G7">
-        <v>34</v>
-      </c>
-      <c r="H7">
-        <v>63</v>
-      </c>
-      <c r="I7">
-        <v>44</v>
-      </c>
-      <c r="J7">
-        <v>47</v>
-      </c>
-      <c r="K7">
-        <v>46</v>
-      </c>
-      <c r="L7">
-        <v>33</v>
-      </c>
-      <c r="M7">
-        <v>36</v>
+        <v>9</v>
+      </c>
+      <c r="L5">
+        <v>9</v>
+      </c>
+      <c r="M5">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -15391,7 +15382,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -15455,54 +15446,81 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
       <c r="E3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="K3">
+        <v>12</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -15512,87 +15530,110 @@
       <c r="B4">
         <v>1</v>
       </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
       <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>40</v>
+      </c>
+      <c r="D7">
+        <v>32</v>
+      </c>
+      <c r="E7">
+        <v>57</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>34</v>
+      </c>
+      <c r="H7">
+        <v>63</v>
+      </c>
+      <c r="I7">
+        <v>44</v>
+      </c>
+      <c r="J7">
+        <v>47</v>
+      </c>
+      <c r="K7">
+        <v>46</v>
+      </c>
+      <c r="L7">
+        <v>33</v>
+      </c>
+      <c r="M7">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -17423,67 +17464,64 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
       </c>
       <c r="L3">
         <v>2</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M4">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -17492,40 +17530,37 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5">
         <v>3</v>
       </c>
       <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -17533,40 +17568,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -19164,91 +19199,214 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
     <col min="5" max="5" width="4.7109375" customWidth="1"/>
     <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
         <v>2017</v>
       </c>
-      <c r="C1" s="1">
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
         <v>2019</v>
       </c>
-      <c r="D1" s="1">
+      <c r="G1" s="1">
         <v>2020</v>
       </c>
-      <c r="E1" s="1">
+      <c r="H1" s="1">
         <v>2021</v>
       </c>
-      <c r="F1" s="1">
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
       <c r="E2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
+      <c r="B3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>14</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>16</v>
+      </c>
+      <c r="H6">
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <v>14</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>7</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -20337,249 +20495,91 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
     <col min="5" max="5" width="4.7109375" customWidth="1"/>
     <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="D1" s="1">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="E1" s="1">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
-      </c>
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>5</v>
-      </c>
-      <c r="K2">
-        <v>8</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3">
-        <v>8</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>6</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>10</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>9</v>
-      </c>
-      <c r="D6">
-        <v>17</v>
-      </c>
-      <c r="E6">
-        <v>13</v>
-      </c>
-      <c r="F6">
-        <v>19</v>
-      </c>
-      <c r="G6">
-        <v>15</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>15</v>
-      </c>
-      <c r="J6">
-        <v>12</v>
-      </c>
-      <c r="K6">
-        <v>18</v>
-      </c>
-      <c r="L6">
-        <v>19</v>
-      </c>
-      <c r="M6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>8</v>
-      </c>
-      <c r="C7">
-        <v>11</v>
-      </c>
-      <c r="D7">
-        <v>29</v>
-      </c>
-      <c r="E7">
-        <v>17</v>
-      </c>
-      <c r="F7">
-        <v>26</v>
-      </c>
-      <c r="G7">
-        <v>25</v>
-      </c>
-      <c r="H7">
-        <v>13</v>
-      </c>
-      <c r="I7">
-        <v>24</v>
-      </c>
-      <c r="J7">
-        <v>21</v>
-      </c>
-      <c r="K7">
-        <v>37</v>
-      </c>
-      <c r="L7">
-        <v>27</v>
-      </c>
-      <c r="M7">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-full-year.xlsx
+++ b/output/cta-violent-crime-full-year.xlsx
@@ -9,41 +9,41 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Near South Side" sheetId="3" r:id="rId3"/>
-    <sheet name="Grand Crossing" sheetId="4" r:id="rId4"/>
-    <sheet name="South Shore" sheetId="5" r:id="rId5"/>
-    <sheet name="Austin" sheetId="6" r:id="rId6"/>
-    <sheet name="Avondale" sheetId="7" r:id="rId7"/>
-    <sheet name="Rush &amp; Division" sheetId="8" r:id="rId8"/>
-    <sheet name="Oakland" sheetId="9" r:id="rId9"/>
-    <sheet name="Chatham" sheetId="10" r:id="rId10"/>
-    <sheet name="New City" sheetId="11" r:id="rId11"/>
-    <sheet name="Belmont Cragin" sheetId="12" r:id="rId12"/>
-    <sheet name="Woodlawn" sheetId="13" r:id="rId13"/>
-    <sheet name="West Loop" sheetId="14" r:id="rId14"/>
-    <sheet name="Loop" sheetId="15" r:id="rId15"/>
-    <sheet name="Uptown" sheetId="16" r:id="rId16"/>
-    <sheet name="Lake View" sheetId="17" r:id="rId17"/>
-    <sheet name="North Lawndale" sheetId="18" r:id="rId18"/>
-    <sheet name="Grand Boulevard" sheetId="19" r:id="rId19"/>
-    <sheet name="West Town" sheetId="20" r:id="rId20"/>
-    <sheet name="Englewood" sheetId="21" r:id="rId21"/>
-    <sheet name="Greektown" sheetId="22" r:id="rId22"/>
-    <sheet name="Edgewater" sheetId="23" r:id="rId23"/>
-    <sheet name="Little Italy, UIC" sheetId="24" r:id="rId24"/>
-    <sheet name="Gage Park" sheetId="25" r:id="rId25"/>
-    <sheet name="Humboldt Park" sheetId="26" r:id="rId26"/>
-    <sheet name="Lower West Side" sheetId="27" r:id="rId27"/>
-    <sheet name="Sheffield &amp; DePaul" sheetId="28" r:id="rId28"/>
-    <sheet name="Roseland" sheetId="29" r:id="rId29"/>
-    <sheet name="Norwood Park" sheetId="30" r:id="rId30"/>
-    <sheet name="Garfield Park" sheetId="31" r:id="rId31"/>
-    <sheet name="Wrigleyville" sheetId="32" r:id="rId32"/>
-    <sheet name="Auburn Gresham" sheetId="33" r:id="rId33"/>
-    <sheet name="Rogers Park" sheetId="34" r:id="rId34"/>
-    <sheet name="Washington Park" sheetId="35" r:id="rId35"/>
-    <sheet name="Chicago Lawn" sheetId="36" r:id="rId36"/>
-    <sheet name="O'Hare" sheetId="37" r:id="rId37"/>
+    <sheet name="Loop" sheetId="3" r:id="rId3"/>
+    <sheet name="O'Hare" sheetId="4" r:id="rId4"/>
+    <sheet name="Near South Side" sheetId="5" r:id="rId5"/>
+    <sheet name="Grand Crossing" sheetId="6" r:id="rId6"/>
+    <sheet name="South Shore" sheetId="7" r:id="rId7"/>
+    <sheet name="Austin" sheetId="8" r:id="rId8"/>
+    <sheet name="Avondale" sheetId="9" r:id="rId9"/>
+    <sheet name="Rush &amp; Division" sheetId="10" r:id="rId10"/>
+    <sheet name="Oakland" sheetId="11" r:id="rId11"/>
+    <sheet name="Chatham" sheetId="12" r:id="rId12"/>
+    <sheet name="New City" sheetId="13" r:id="rId13"/>
+    <sheet name="Belmont Cragin" sheetId="14" r:id="rId14"/>
+    <sheet name="Woodlawn" sheetId="15" r:id="rId15"/>
+    <sheet name="West Loop" sheetId="16" r:id="rId16"/>
+    <sheet name="Uptown" sheetId="17" r:id="rId17"/>
+    <sheet name="Lake View" sheetId="18" r:id="rId18"/>
+    <sheet name="North Lawndale" sheetId="19" r:id="rId19"/>
+    <sheet name="Grand Boulevard" sheetId="20" r:id="rId20"/>
+    <sheet name="West Town" sheetId="21" r:id="rId21"/>
+    <sheet name="Englewood" sheetId="22" r:id="rId22"/>
+    <sheet name="Greektown" sheetId="23" r:id="rId23"/>
+    <sheet name="Edgewater" sheetId="24" r:id="rId24"/>
+    <sheet name="Little Italy, UIC" sheetId="25" r:id="rId25"/>
+    <sheet name="Gage Park" sheetId="26" r:id="rId26"/>
+    <sheet name="Humboldt Park" sheetId="27" r:id="rId27"/>
+    <sheet name="Lower West Side" sheetId="28" r:id="rId28"/>
+    <sheet name="Sheffield &amp; DePaul" sheetId="29" r:id="rId29"/>
+    <sheet name="Roseland" sheetId="30" r:id="rId30"/>
+    <sheet name="Norwood Park" sheetId="31" r:id="rId31"/>
+    <sheet name="Garfield Park" sheetId="32" r:id="rId32"/>
+    <sheet name="Wrigleyville" sheetId="33" r:id="rId33"/>
+    <sheet name="Auburn Gresham" sheetId="34" r:id="rId34"/>
+    <sheet name="Rogers Park" sheetId="35" r:id="rId35"/>
+    <sheet name="Washington Park" sheetId="36" r:id="rId36"/>
+    <sheet name="Chicago Lawn" sheetId="37" r:id="rId37"/>
     <sheet name="Kenwood" sheetId="38" r:id="rId38"/>
     <sheet name="Calumet Heights" sheetId="39" r:id="rId39"/>
     <sheet name="Hyde Park" sheetId="40" r:id="rId40"/>
@@ -889,7 +889,7 @@
         <v>137</v>
       </c>
       <c r="M2">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1050,7 +1050,7 @@
         <v>467</v>
       </c>
       <c r="M6">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1091,7 +1091,7 @@
         <v>896</v>
       </c>
       <c r="M7">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
   </sheetData>
@@ -1100,6 +1100,317 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>14</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>16</v>
+      </c>
+      <c r="H6">
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <v>14</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>7</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1351,7 +1662,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1535,7 +1846,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1693,7 +2004,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1910,7 +2221,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2140,526 +2451,6 @@
       </c>
       <c r="M7">
         <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>6</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>12</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>8</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>13</v>
-      </c>
-      <c r="I2">
-        <v>14</v>
-      </c>
-      <c r="J2">
-        <v>22</v>
-      </c>
-      <c r="K2">
-        <v>15</v>
-      </c>
-      <c r="L2">
-        <v>15</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>13</v>
-      </c>
-      <c r="C3">
-        <v>13</v>
-      </c>
-      <c r="D3">
-        <v>17</v>
-      </c>
-      <c r="E3">
-        <v>18</v>
-      </c>
-      <c r="F3">
-        <v>14</v>
-      </c>
-      <c r="G3">
-        <v>26</v>
-      </c>
-      <c r="H3">
-        <v>23</v>
-      </c>
-      <c r="I3">
-        <v>32</v>
-      </c>
-      <c r="J3">
-        <v>40</v>
-      </c>
-      <c r="K3">
-        <v>26</v>
-      </c>
-      <c r="L3">
-        <v>34</v>
-      </c>
-      <c r="M3">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>4</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>5</v>
-      </c>
-      <c r="M4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>30</v>
-      </c>
-      <c r="C6">
-        <v>44</v>
-      </c>
-      <c r="D6">
-        <v>49</v>
-      </c>
-      <c r="E6">
-        <v>67</v>
-      </c>
-      <c r="F6">
-        <v>69</v>
-      </c>
-      <c r="G6">
-        <v>57</v>
-      </c>
-      <c r="H6">
-        <v>80</v>
-      </c>
-      <c r="I6">
-        <v>80</v>
-      </c>
-      <c r="J6">
-        <v>64</v>
-      </c>
-      <c r="K6">
-        <v>48</v>
-      </c>
-      <c r="L6">
-        <v>44</v>
-      </c>
-      <c r="M6">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>49</v>
-      </c>
-      <c r="C7">
-        <v>62</v>
-      </c>
-      <c r="D7">
-        <v>79</v>
-      </c>
-      <c r="E7">
-        <v>92</v>
-      </c>
-      <c r="F7">
-        <v>92</v>
-      </c>
-      <c r="G7">
-        <v>88</v>
-      </c>
-      <c r="H7">
-        <v>120</v>
-      </c>
-      <c r="I7">
-        <v>130</v>
-      </c>
-      <c r="J7">
-        <v>131</v>
-      </c>
-      <c r="K7">
-        <v>91</v>
-      </c>
-      <c r="L7">
-        <v>100</v>
-      </c>
-      <c r="M7">
-        <v>44</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>4</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>6</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
-      </c>
-      <c r="K3">
-        <v>7</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>9</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>14</v>
-      </c>
-      <c r="H5">
-        <v>7</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>11</v>
-      </c>
-      <c r="L5">
-        <v>8</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>14</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>11</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>22</v>
-      </c>
-      <c r="H6">
-        <v>14</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>16</v>
-      </c>
-      <c r="K6">
-        <v>23</v>
-      </c>
-      <c r="L6">
-        <v>13</v>
-      </c>
-      <c r="M6">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2732,6 +2523,9 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
       <c r="C2">
         <v>4</v>
       </c>
@@ -2739,133 +2533,118 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
         <v>7</v>
       </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>11</v>
-      </c>
       <c r="K3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+      <c r="B4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
       <c r="C5">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
         <v>14</v>
       </c>
-      <c r="D5">
-        <v>12</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-      <c r="F5">
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
         <v>11</v>
       </c>
-      <c r="G5">
-        <v>11</v>
-      </c>
-      <c r="H5">
-        <v>17</v>
-      </c>
-      <c r="I5">
-        <v>20</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>10</v>
-      </c>
       <c r="L5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2873,40 +2652,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>22</v>
+      </c>
+      <c r="H6">
         <v>14</v>
       </c>
-      <c r="E6">
-        <v>18</v>
-      </c>
-      <c r="F6">
-        <v>18</v>
-      </c>
-      <c r="G6">
-        <v>19</v>
-      </c>
-      <c r="H6">
-        <v>27</v>
-      </c>
       <c r="I6">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>16</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L6">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2979,41 +2758,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3021,89 +2797,101 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3">
         <v>5</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L3">
         <v>7</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
       <c r="H4">
         <v>1</v>
       </c>
-      <c r="J4">
-        <v>1</v>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
+      <c r="C5">
+        <v>14</v>
+      </c>
+      <c r="D5">
         <v>12</v>
       </c>
-      <c r="C5">
-        <v>21</v>
-      </c>
-      <c r="D5">
-        <v>28</v>
-      </c>
       <c r="E5">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H5">
+        <v>17</v>
+      </c>
+      <c r="I5">
+        <v>20</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
         <v>10</v>
       </c>
-      <c r="I5">
-        <v>15</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>9</v>
-      </c>
       <c r="L5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -3111,40 +2899,40 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>23</v>
+      </c>
+      <c r="D6">
         <v>14</v>
       </c>
-      <c r="C6">
+      <c r="E6">
+        <v>18</v>
+      </c>
+      <c r="F6">
+        <v>18</v>
+      </c>
+      <c r="G6">
+        <v>19</v>
+      </c>
+      <c r="H6">
+        <v>27</v>
+      </c>
+      <c r="I6">
         <v>26</v>
       </c>
-      <c r="D6">
-        <v>29</v>
-      </c>
-      <c r="E6">
+      <c r="J6">
+        <v>16</v>
+      </c>
+      <c r="K6">
         <v>24</v>
       </c>
-      <c r="F6">
-        <v>42</v>
-      </c>
-      <c r="G6">
-        <v>18</v>
-      </c>
-      <c r="H6">
-        <v>18</v>
-      </c>
-      <c r="I6">
-        <v>21</v>
-      </c>
-      <c r="J6">
+      <c r="L6">
+        <v>20</v>
+      </c>
+      <c r="M6">
         <v>12</v>
-      </c>
-      <c r="K6">
-        <v>18</v>
-      </c>
-      <c r="L6">
-        <v>18</v>
-      </c>
-      <c r="M6">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3157,7 +2945,7 @@
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -3217,8 +3005,11 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -3226,20 +3017,29 @@
       <c r="E2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
       <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
         <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3247,41 +3047,47 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
       </c>
       <c r="I3">
         <v>4</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
@@ -3290,37 +3096,40 @@
         <v>5</v>
       </c>
       <c r="B5">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>21</v>
+      </c>
+      <c r="D5">
+        <v>28</v>
+      </c>
+      <c r="E5">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>35</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>15</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>9</v>
+      </c>
+      <c r="L5">
         <v>7</v>
       </c>
-      <c r="C5">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>8</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>6</v>
+      <c r="M5">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -3328,40 +3137,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="G6">
+        <v>18</v>
+      </c>
+      <c r="H6">
+        <v>18</v>
+      </c>
+      <c r="I6">
+        <v>21</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+      <c r="K6">
+        <v>18</v>
+      </c>
+      <c r="L6">
+        <v>18</v>
+      </c>
+      <c r="M6">
         <v>7</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>6</v>
-      </c>
-      <c r="J6">
-        <v>8</v>
-      </c>
-      <c r="K6">
-        <v>9</v>
-      </c>
-      <c r="L6">
-        <v>12</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5154,7 +4963,7 @@
         <v>100</v>
       </c>
       <c r="M53">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -5643,7 +5452,7 @@
         <v>9</v>
       </c>
       <c r="M68">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -6726,7 +6535,7 @@
         <v>896</v>
       </c>
       <c r="M98">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
   </sheetData>
@@ -6838,6 +6647,223 @@
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>9</v>
+      </c>
+      <c r="L6">
+        <v>12</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
@@ -7062,7 +7088,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7326,7 +7352,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7496,226 +7522,6 @@
       </c>
       <c r="L6">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>12</v>
-      </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>16</v>
-      </c>
-      <c r="L5">
-        <v>8</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>13</v>
-      </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
-      </c>
-      <c r="K6">
-        <v>21</v>
-      </c>
-      <c r="L6">
-        <v>13</v>
-      </c>
-      <c r="M6">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -7789,19 +7595,19 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -7810,66 +7616,48 @@
         <v>5</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
       <c r="M4">
         <v>1</v>
       </c>
@@ -7879,40 +7667,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>12</v>
+      </c>
+      <c r="I5">
         <v>7</v>
       </c>
-      <c r="D5">
-        <v>11</v>
-      </c>
-      <c r="E5">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>25</v>
-      </c>
-      <c r="G5">
-        <v>15</v>
-      </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>9</v>
-      </c>
       <c r="J5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -7920,40 +7708,40 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
         <v>10</v>
       </c>
-      <c r="C6">
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>13</v>
+      </c>
+      <c r="I6">
+        <v>12</v>
+      </c>
+      <c r="J6">
         <v>10</v>
       </c>
-      <c r="D6">
-        <v>14</v>
-      </c>
-      <c r="E6">
-        <v>23</v>
-      </c>
-      <c r="F6">
-        <v>28</v>
-      </c>
-      <c r="G6">
-        <v>16</v>
-      </c>
-      <c r="H6">
-        <v>14</v>
-      </c>
-      <c r="I6">
-        <v>17</v>
-      </c>
-      <c r="J6">
-        <v>16</v>
-      </c>
       <c r="K6">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="L6">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -7962,6 +7750,244 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>11</v>
+      </c>
+      <c r="E5">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>25</v>
+      </c>
+      <c r="G5">
+        <v>15</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5">
+        <v>11</v>
+      </c>
+      <c r="K5">
+        <v>18</v>
+      </c>
+      <c r="L5">
+        <v>11</v>
+      </c>
+      <c r="M5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>14</v>
+      </c>
+      <c r="E6">
+        <v>23</v>
+      </c>
+      <c r="F6">
+        <v>28</v>
+      </c>
+      <c r="G6">
+        <v>16</v>
+      </c>
+      <c r="H6">
+        <v>14</v>
+      </c>
+      <c r="I6">
+        <v>17</v>
+      </c>
+      <c r="J6">
+        <v>16</v>
+      </c>
+      <c r="K6">
+        <v>31</v>
+      </c>
+      <c r="L6">
+        <v>22</v>
+      </c>
+      <c r="M6">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8186,7 +8212,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8421,7 +8447,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8621,7 +8647,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8837,270 +8863,6 @@
       </c>
       <c r="M6">
         <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2">
-        <v>4</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
-        <v>6</v>
-      </c>
-      <c r="I2">
-        <v>7</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>5</v>
-      </c>
-      <c r="F3">
-        <v>7</v>
-      </c>
-      <c r="G3">
-        <v>6</v>
-      </c>
-      <c r="H3">
-        <v>6</v>
-      </c>
-      <c r="I3">
-        <v>9</v>
-      </c>
-      <c r="J3">
-        <v>14</v>
-      </c>
-      <c r="K3">
-        <v>7</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>19</v>
-      </c>
-      <c r="C6">
-        <v>16</v>
-      </c>
-      <c r="D6">
-        <v>11</v>
-      </c>
-      <c r="E6">
-        <v>14</v>
-      </c>
-      <c r="F6">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>14</v>
-      </c>
-      <c r="H6">
-        <v>19</v>
-      </c>
-      <c r="I6">
-        <v>29</v>
-      </c>
-      <c r="J6">
-        <v>19</v>
-      </c>
-      <c r="K6">
-        <v>20</v>
-      </c>
-      <c r="L6">
-        <v>26</v>
-      </c>
-      <c r="M6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>26</v>
-      </c>
-      <c r="C7">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>16</v>
-      </c>
-      <c r="E7">
-        <v>23</v>
-      </c>
-      <c r="F7">
-        <v>23</v>
-      </c>
-      <c r="G7">
-        <v>24</v>
-      </c>
-      <c r="H7">
-        <v>31</v>
-      </c>
-      <c r="I7">
-        <v>47</v>
-      </c>
-      <c r="J7">
-        <v>35</v>
-      </c>
-      <c r="K7">
-        <v>31</v>
-      </c>
-      <c r="L7">
-        <v>37</v>
-      </c>
-      <c r="M7">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -9173,23 +8935,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
       <c r="F2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>15</v>
+      </c>
+      <c r="L2">
+        <v>15</v>
       </c>
       <c r="M2">
         <v>2</v>
@@ -9200,49 +8977,94 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>26</v>
+      </c>
+      <c r="L3">
+        <v>34</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>4</v>
+      </c>
       <c r="J4">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>5</v>
+      </c>
+      <c r="M4">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K5">
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -9251,40 +9073,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9292,40 +9114,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>92</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="G7">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>120</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>130</v>
       </c>
       <c r="J7">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="K7">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="L7">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -9334,190 +9156,6 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>6</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>4</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>7</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9583,40 +9221,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>4</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
+      </c>
+      <c r="I2">
         <v>7</v>
       </c>
-      <c r="E2">
-        <v>8</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>5</v>
-      </c>
       <c r="J2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9624,25 +9262,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G3">
         <v>6</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I3">
         <v>9</v>
@@ -9651,36 +9289,36 @@
         <v>14</v>
       </c>
       <c r="K3">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
       <c r="I4">
         <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
       </c>
       <c r="M4">
         <v>1</v>
@@ -9690,7 +9328,7 @@
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I5">
+      <c r="D5">
         <v>1</v>
       </c>
     </row>
@@ -9699,40 +9337,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C6">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="E6">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="H6">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="I6">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J6">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="K6">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="L6">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9740,40 +9378,224 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C7">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D7">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="E7">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="F7">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="G7">
+        <v>24</v>
+      </c>
+      <c r="H7">
+        <v>31</v>
+      </c>
+      <c r="I7">
         <v>47</v>
       </c>
+      <c r="J7">
+        <v>35</v>
+      </c>
+      <c r="K7">
+        <v>31</v>
+      </c>
+      <c r="L7">
+        <v>37</v>
+      </c>
+      <c r="M7">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>6</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>7</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
       <c r="H7">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="K7">
-        <v>48</v>
-      </c>
-      <c r="L7">
-        <v>44</v>
-      </c>
-      <c r="M7">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -9783,7 +9605,7 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -9847,22 +9669,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>5</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9872,29 +9712,38 @@
       <c r="B3">
         <v>1</v>
       </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
       <c r="D3">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>16</v>
+      </c>
+      <c r="L3">
+        <v>8</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9902,86 +9751,115 @@
         <v>3</v>
       </c>
       <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
       <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>3</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>19</v>
+      </c>
+      <c r="C7">
+        <v>40</v>
+      </c>
+      <c r="D7">
+        <v>51</v>
+      </c>
+      <c r="E7">
+        <v>69</v>
+      </c>
+      <c r="F7">
+        <v>65</v>
+      </c>
+      <c r="G7">
+        <v>47</v>
+      </c>
+      <c r="H7">
+        <v>50</v>
+      </c>
+      <c r="I7">
+        <v>49</v>
+      </c>
+      <c r="J7">
+        <v>51</v>
+      </c>
+      <c r="K7">
+        <v>48</v>
+      </c>
+      <c r="L7">
+        <v>44</v>
+      </c>
+      <c r="M7">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -10057,11 +9935,8 @@
       <c r="B2">
         <v>2</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>2</v>
@@ -10072,20 +9947,8 @@
       <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
       <c r="J2">
         <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10095,42 +9958,39 @@
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
       <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
     </row>
@@ -10138,41 +9998,35 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>19</v>
-      </c>
       <c r="C5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -10180,40 +10034,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -10222,6 +10076,238 @@
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>19</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>12</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>7</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>16</v>
+      </c>
+      <c r="F6">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>10</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <v>9</v>
+      </c>
+      <c r="K6">
+        <v>10</v>
+      </c>
+      <c r="L6">
+        <v>6</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10469,235 +10555,6 @@
       </c>
       <c r="M7">
         <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>7</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>8</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>7</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <v>11</v>
-      </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>10</v>
-      </c>
-      <c r="H6">
-        <v>7</v>
-      </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
-      <c r="J6">
-        <v>12</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>8</v>
-      </c>
-      <c r="M6">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -10770,71 +10627,80 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
         <v>2</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -10843,37 +10709,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>1</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -10881,40 +10750,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>10</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
+      </c>
+      <c r="I6">
+        <v>12</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
         <v>8</v>
       </c>
-      <c r="G6">
-        <v>13</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>6</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
       <c r="M6">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -10924,7 +10793,7 @@
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10939,9 +10808,10 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10961,163 +10831,176 @@
         <v>2019</v>
       </c>
       <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
         <v>2021</v>
       </c>
-      <c r="H1" s="1">
+      <c r="I1" s="1">
         <v>2022</v>
       </c>
-      <c r="I1" s="1">
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="J1" s="1">
+      <c r="K1" s="1">
         <v>2024</v>
       </c>
-      <c r="K1" s="1">
+      <c r="L1" s="1">
         <v>2025</v>
       </c>
-      <c r="L1" s="1">
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
       <c r="C3">
         <v>1</v>
       </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
       <c r="E3">
         <v>1</v>
       </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>11</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>11</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
       </c>
       <c r="K5">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>16</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>7</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>5</v>
-      </c>
-      <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -11435,7 +11318,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -11450,10 +11333,9 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11473,226 +11355,163 @@
         <v>2019</v>
       </c>
       <c r="G1" s="1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H1" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I1" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J1" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K1" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
         <v>7</v>
       </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>6</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>7</v>
-      </c>
-      <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>8</v>
-      </c>
-      <c r="E3">
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7">
         <v>9</v>
       </c>
-      <c r="F3">
-        <v>19</v>
-      </c>
-      <c r="G3">
+      <c r="L7">
         <v>9</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
-      </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>12</v>
-      </c>
-      <c r="K3">
-        <v>17</v>
-      </c>
-      <c r="L3">
-        <v>13</v>
-      </c>
-      <c r="M3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>24</v>
-      </c>
-      <c r="C6">
-        <v>37</v>
-      </c>
-      <c r="D6">
-        <v>21</v>
-      </c>
-      <c r="E6">
-        <v>22</v>
-      </c>
-      <c r="F6">
-        <v>27</v>
-      </c>
-      <c r="G6">
-        <v>15</v>
-      </c>
-      <c r="H6">
-        <v>25</v>
-      </c>
-      <c r="I6">
-        <v>21</v>
-      </c>
-      <c r="J6">
-        <v>26</v>
-      </c>
-      <c r="K6">
-        <v>49</v>
-      </c>
-      <c r="L6">
-        <v>44</v>
-      </c>
-      <c r="M6">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>32</v>
-      </c>
-      <c r="C7">
-        <v>42</v>
-      </c>
-      <c r="D7">
-        <v>36</v>
-      </c>
-      <c r="E7">
-        <v>38</v>
-      </c>
-      <c r="F7">
-        <v>53</v>
-      </c>
-      <c r="G7">
-        <v>28</v>
-      </c>
-      <c r="H7">
-        <v>39</v>
-      </c>
-      <c r="I7">
-        <v>39</v>
-      </c>
-      <c r="J7">
-        <v>47</v>
-      </c>
-      <c r="K7">
-        <v>74</v>
-      </c>
-      <c r="L7">
-        <v>63</v>
-      </c>
-      <c r="M7">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -13506,10 +13325,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -13569,41 +13388,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -13611,121 +13415,131 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>4</v>
-      </c>
-      <c r="L3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>11</v>
-      </c>
-      <c r="C4">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <v>6</v>
-      </c>
-      <c r="E4">
-        <v>7</v>
-      </c>
-      <c r="F4">
-        <v>7</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J4">
-        <v>12</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>15</v>
-      </c>
-      <c r="C5">
-        <v>15</v>
-      </c>
-      <c r="D5">
-        <v>12</v>
-      </c>
-      <c r="E5">
-        <v>11</v>
-      </c>
-      <c r="F5">
-        <v>12</v>
-      </c>
-      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>7</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7">
+        <v>7</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7">
         <v>9</v>
       </c>
-      <c r="H5">
-        <v>11</v>
-      </c>
-      <c r="I5">
-        <v>12</v>
-      </c>
-      <c r="J5">
-        <v>15</v>
-      </c>
-      <c r="K5">
-        <v>9</v>
-      </c>
-      <c r="L5">
-        <v>9</v>
-      </c>
-      <c r="M5">
+      <c r="I7">
+        <v>13</v>
+      </c>
+      <c r="J7">
+        <v>8</v>
+      </c>
+      <c r="K7">
+        <v>8</v>
+      </c>
+      <c r="L7">
+        <v>4</v>
+      </c>
+      <c r="M7">
         <v>7</v>
       </c>
     </row>
@@ -15446,31 +15260,31 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>4</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K2">
         <v>7</v>
@@ -15479,7 +15293,7 @@
         <v>5</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15487,59 +15301,53 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H3">
         <v>8</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
       <c r="E4">
         <v>1</v>
       </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
       <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
         <v>2</v>
       </c>
       <c r="M4">
@@ -15550,7 +15358,19 @@
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
       <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -15559,40 +15379,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D6">
+        <v>21</v>
+      </c>
+      <c r="E6">
         <v>22</v>
       </c>
-      <c r="E6">
-        <v>44</v>
-      </c>
       <c r="F6">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H6">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I6">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J6">
         <v>26</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="L6">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="M6">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -15603,37 +15423,37 @@
         <v>32</v>
       </c>
       <c r="C7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E7">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F7">
         <v>53</v>
       </c>
       <c r="G7">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H7">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="I7">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="J7">
         <v>47</v>
       </c>
       <c r="K7">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="L7">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="M7">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -17400,10 +17220,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -17464,7 +17284,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -17473,10 +17293,16 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -17485,123 +17311,136 @@
         <v>1</v>
       </c>
       <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
         <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
+      <c r="H3">
+        <v>6</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
       <c r="J3">
         <v>2</v>
       </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
       <c r="L3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4">
+        <v>7</v>
+      </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>8</v>
+      </c>
+      <c r="J4">
+        <v>12</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
         <v>9</v>
       </c>
-      <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>6</v>
+      <c r="M5">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -19199,7 +19038,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -19263,25 +19102,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -19289,124 +19143,153 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="J3">
+        <v>10</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
       <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-      <c r="F5">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>14</v>
-      </c>
-      <c r="H5">
-        <v>7</v>
-      </c>
-      <c r="I5">
-        <v>9</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="G6">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H6">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="I6">
+        <v>34</v>
+      </c>
+      <c r="J6">
+        <v>26</v>
+      </c>
+      <c r="K6">
+        <v>24</v>
+      </c>
+      <c r="L6">
         <v>14</v>
       </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>7</v>
-      </c>
       <c r="M6">
-        <v>3</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>40</v>
+      </c>
+      <c r="D7">
+        <v>32</v>
+      </c>
+      <c r="E7">
+        <v>57</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>34</v>
+      </c>
+      <c r="H7">
+        <v>63</v>
+      </c>
+      <c r="I7">
+        <v>44</v>
+      </c>
+      <c r="J7">
+        <v>47</v>
+      </c>
+      <c r="K7">
+        <v>46</v>
+      </c>
+      <c r="L7">
+        <v>33</v>
+      </c>
+      <c r="M7">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -20495,79 +20378,137 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
     <col min="5" max="5" width="4.7109375" customWidth="1"/>
     <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
         <v>2017</v>
       </c>
-      <c r="C1" s="1">
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
         <v>2019</v>
       </c>
-      <c r="D1" s="1">
+      <c r="G1" s="1">
         <v>2020</v>
       </c>
-      <c r="E1" s="1">
+      <c r="H1" s="1">
         <v>2021</v>
       </c>
-      <c r="F1" s="1">
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
       <c r="E2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
       <c r="E3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -20576,10 +20517,69 @@
         <v>3</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>9</v>
+      </c>
+      <c r="K6">
+        <v>6</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-full-year.xlsx
+++ b/output/cta-violent-crime-full-year.xlsx
@@ -9,25 +9,25 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="South Shore" sheetId="3" r:id="rId3"/>
-    <sheet name="Albany Park" sheetId="4" r:id="rId4"/>
-    <sheet name="Old Town" sheetId="5" r:id="rId5"/>
-    <sheet name="Loop" sheetId="6" r:id="rId6"/>
-    <sheet name="O'Hare" sheetId="7" r:id="rId7"/>
-    <sheet name="Near South Side" sheetId="8" r:id="rId8"/>
-    <sheet name="Grand Crossing" sheetId="9" r:id="rId9"/>
-    <sheet name="Austin" sheetId="10" r:id="rId10"/>
-    <sheet name="Avondale" sheetId="11" r:id="rId11"/>
-    <sheet name="Rush &amp; Division" sheetId="12" r:id="rId12"/>
-    <sheet name="Oakland" sheetId="13" r:id="rId13"/>
-    <sheet name="Chatham" sheetId="14" r:id="rId14"/>
-    <sheet name="New City" sheetId="15" r:id="rId15"/>
-    <sheet name="Belmont Cragin" sheetId="16" r:id="rId16"/>
-    <sheet name="Woodlawn" sheetId="17" r:id="rId17"/>
-    <sheet name="West Loop" sheetId="18" r:id="rId18"/>
-    <sheet name="Uptown" sheetId="19" r:id="rId19"/>
-    <sheet name="Lake View" sheetId="20" r:id="rId20"/>
-    <sheet name="North Lawndale" sheetId="21" r:id="rId21"/>
+    <sheet name="Albany Park" sheetId="3" r:id="rId3"/>
+    <sheet name="Woodlawn" sheetId="4" r:id="rId4"/>
+    <sheet name="North Lawndale" sheetId="5" r:id="rId5"/>
+    <sheet name="South Shore" sheetId="6" r:id="rId6"/>
+    <sheet name="Old Town" sheetId="7" r:id="rId7"/>
+    <sheet name="Loop" sheetId="8" r:id="rId8"/>
+    <sheet name="O'Hare" sheetId="9" r:id="rId9"/>
+    <sheet name="Near South Side" sheetId="10" r:id="rId10"/>
+    <sheet name="Grand Crossing" sheetId="11" r:id="rId11"/>
+    <sheet name="Austin" sheetId="12" r:id="rId12"/>
+    <sheet name="Avondale" sheetId="13" r:id="rId13"/>
+    <sheet name="Rush &amp; Division" sheetId="14" r:id="rId14"/>
+    <sheet name="Oakland" sheetId="15" r:id="rId15"/>
+    <sheet name="Chatham" sheetId="16" r:id="rId16"/>
+    <sheet name="New City" sheetId="17" r:id="rId17"/>
+    <sheet name="Belmont Cragin" sheetId="18" r:id="rId18"/>
+    <sheet name="West Loop" sheetId="19" r:id="rId19"/>
+    <sheet name="Uptown" sheetId="20" r:id="rId20"/>
+    <sheet name="Lake View" sheetId="21" r:id="rId21"/>
     <sheet name="Grand Boulevard" sheetId="22" r:id="rId22"/>
     <sheet name="West Town" sheetId="23" r:id="rId23"/>
     <sheet name="Englewood" sheetId="24" r:id="rId24"/>
@@ -889,7 +889,7 @@
         <v>137</v>
       </c>
       <c r="M2">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1050,7 +1050,7 @@
         <v>467</v>
       </c>
       <c r="M6">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1091,7 +1091,7 @@
         <v>896</v>
       </c>
       <c r="M7">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -1164,41 +1164,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
       <c r="F2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1206,62 +1191,41 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>12</v>
-      </c>
-      <c r="L3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
       <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -1278,40 +1242,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1319,40 +1283,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="F7">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="G7">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="H7">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="J7">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="M7">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1361,6 +1325,534 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>7</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>7</v>
+      </c>
+      <c r="K2">
+        <v>7</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>19</v>
+      </c>
+      <c r="G3">
+        <v>9</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
+      </c>
+      <c r="J3">
+        <v>12</v>
+      </c>
+      <c r="K3">
+        <v>17</v>
+      </c>
+      <c r="L3">
+        <v>13</v>
+      </c>
+      <c r="M3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>24</v>
+      </c>
+      <c r="C6">
+        <v>37</v>
+      </c>
+      <c r="D6">
+        <v>21</v>
+      </c>
+      <c r="E6">
+        <v>22</v>
+      </c>
+      <c r="F6">
+        <v>27</v>
+      </c>
+      <c r="G6">
+        <v>15</v>
+      </c>
+      <c r="H6">
+        <v>25</v>
+      </c>
+      <c r="I6">
+        <v>21</v>
+      </c>
+      <c r="J6">
+        <v>26</v>
+      </c>
+      <c r="K6">
+        <v>49</v>
+      </c>
+      <c r="L6">
+        <v>44</v>
+      </c>
+      <c r="M6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>42</v>
+      </c>
+      <c r="D7">
+        <v>36</v>
+      </c>
+      <c r="E7">
+        <v>38</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>28</v>
+      </c>
+      <c r="H7">
+        <v>39</v>
+      </c>
+      <c r="I7">
+        <v>39</v>
+      </c>
+      <c r="J7">
+        <v>47</v>
+      </c>
+      <c r="K7">
+        <v>74</v>
+      </c>
+      <c r="L7">
+        <v>63</v>
+      </c>
+      <c r="M7">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>8</v>
+      </c>
+      <c r="K2">
+        <v>7</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>7</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>6</v>
+      </c>
+      <c r="J3">
+        <v>10</v>
+      </c>
+      <c r="K3">
+        <v>12</v>
+      </c>
+      <c r="L3">
+        <v>14</v>
+      </c>
+      <c r="M3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>23</v>
+      </c>
+      <c r="C6">
+        <v>31</v>
+      </c>
+      <c r="D6">
+        <v>22</v>
+      </c>
+      <c r="E6">
+        <v>44</v>
+      </c>
+      <c r="F6">
+        <v>38</v>
+      </c>
+      <c r="G6">
+        <v>24</v>
+      </c>
+      <c r="H6">
+        <v>50</v>
+      </c>
+      <c r="I6">
+        <v>34</v>
+      </c>
+      <c r="J6">
+        <v>26</v>
+      </c>
+      <c r="K6">
+        <v>24</v>
+      </c>
+      <c r="L6">
+        <v>14</v>
+      </c>
+      <c r="M6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>40</v>
+      </c>
+      <c r="D7">
+        <v>32</v>
+      </c>
+      <c r="E7">
+        <v>57</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>34</v>
+      </c>
+      <c r="H7">
+        <v>63</v>
+      </c>
+      <c r="I7">
+        <v>44</v>
+      </c>
+      <c r="J7">
+        <v>47</v>
+      </c>
+      <c r="K7">
+        <v>46</v>
+      </c>
+      <c r="L7">
+        <v>33</v>
+      </c>
+      <c r="M7">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1571,7 +2063,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1788,7 +2280,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1882,7 +2374,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2134,7 +2626,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2318,7 +2810,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2476,224 +2968,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>5</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>11</v>
-      </c>
-      <c r="C5">
-        <v>12</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>7</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>16</v>
-      </c>
-      <c r="C6">
-        <v>13</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>11</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>11</v>
-      </c>
-      <c r="J6">
-        <v>11</v>
-      </c>
-      <c r="K6">
-        <v>12</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2923,241 +3198,6 @@
       </c>
       <c r="M7">
         <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>4</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>6</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
-      </c>
-      <c r="K3">
-        <v>7</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>9</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>14</v>
-      </c>
-      <c r="H5">
-        <v>7</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>11</v>
-      </c>
-      <c r="L5">
-        <v>8</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>14</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>11</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>22</v>
-      </c>
-      <c r="H6">
-        <v>14</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>16</v>
-      </c>
-      <c r="K6">
-        <v>23</v>
-      </c>
-      <c r="L6">
-        <v>13</v>
-      </c>
-      <c r="M6">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3261,7 +3301,7 @@
         <v>3</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -5337,7 +5377,7 @@
         <v>18</v>
       </c>
       <c r="M65">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -6440,7 +6480,7 @@
         <v>5</v>
       </c>
       <c r="M96">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -6522,7 +6562,7 @@
         <v>896</v>
       </c>
       <c r="M98">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -6694,6 +6734,9 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
       <c r="C2">
         <v>4</v>
       </c>
@@ -6701,133 +6744,118 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
         <v>7</v>
       </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>11</v>
-      </c>
       <c r="K3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+      <c r="B4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
       <c r="C5">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
         <v>14</v>
       </c>
-      <c r="D5">
-        <v>12</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-      <c r="F5">
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
         <v>11</v>
       </c>
-      <c r="G5">
-        <v>11</v>
-      </c>
-      <c r="H5">
-        <v>17</v>
-      </c>
-      <c r="I5">
-        <v>20</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>10</v>
-      </c>
       <c r="L5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -6835,40 +6863,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>22</v>
+      </c>
+      <c r="H6">
         <v>14</v>
       </c>
-      <c r="E6">
-        <v>18</v>
-      </c>
-      <c r="F6">
-        <v>18</v>
-      </c>
-      <c r="G6">
-        <v>19</v>
-      </c>
-      <c r="H6">
-        <v>27</v>
-      </c>
       <c r="I6">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>16</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L6">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -6941,41 +6969,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -6983,89 +7008,101 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3">
         <v>5</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L3">
         <v>7</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
       <c r="H4">
         <v>1</v>
       </c>
-      <c r="J4">
-        <v>1</v>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
+      <c r="C5">
+        <v>14</v>
+      </c>
+      <c r="D5">
         <v>12</v>
       </c>
-      <c r="C5">
-        <v>21</v>
-      </c>
-      <c r="D5">
-        <v>28</v>
-      </c>
       <c r="E5">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H5">
+        <v>17</v>
+      </c>
+      <c r="I5">
+        <v>20</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
         <v>10</v>
       </c>
-      <c r="I5">
-        <v>15</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>9</v>
-      </c>
       <c r="L5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -7073,40 +7110,40 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>23</v>
+      </c>
+      <c r="D6">
         <v>14</v>
       </c>
-      <c r="C6">
+      <c r="E6">
+        <v>18</v>
+      </c>
+      <c r="F6">
+        <v>18</v>
+      </c>
+      <c r="G6">
+        <v>19</v>
+      </c>
+      <c r="H6">
+        <v>27</v>
+      </c>
+      <c r="I6">
         <v>26</v>
       </c>
-      <c r="D6">
-        <v>29</v>
-      </c>
-      <c r="E6">
+      <c r="J6">
+        <v>16</v>
+      </c>
+      <c r="K6">
         <v>24</v>
       </c>
-      <c r="F6">
-        <v>42</v>
-      </c>
-      <c r="G6">
-        <v>18</v>
-      </c>
-      <c r="H6">
-        <v>18</v>
-      </c>
-      <c r="I6">
-        <v>21</v>
-      </c>
-      <c r="J6">
+      <c r="L6">
+        <v>20</v>
+      </c>
+      <c r="M6">
         <v>12</v>
-      </c>
-      <c r="K6">
-        <v>18</v>
-      </c>
-      <c r="L6">
-        <v>18</v>
-      </c>
-      <c r="M6">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -8921,10 +8958,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -8936,10 +8973,9 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8962,42 +8998,30 @@
         <v>2020</v>
       </c>
       <c r="H1" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I1" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J1" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K1" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -9006,142 +9030,126 @@
         <v>2</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
         <v>2</v>
       </c>
-      <c r="M2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>6</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>11</v>
-      </c>
-      <c r="C4">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>9</v>
+      </c>
+      <c r="J6">
         <v>7</v>
       </c>
-      <c r="F4">
-        <v>7</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>8</v>
-      </c>
-      <c r="J4">
-        <v>12</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>15</v>
-      </c>
-      <c r="C5">
-        <v>15</v>
-      </c>
-      <c r="D5">
-        <v>12</v>
-      </c>
-      <c r="E5">
-        <v>11</v>
-      </c>
-      <c r="F5">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>9</v>
-      </c>
-      <c r="H5">
-        <v>11</v>
-      </c>
-      <c r="I5">
-        <v>12</v>
-      </c>
-      <c r="J5">
-        <v>15</v>
-      </c>
-      <c r="K5">
-        <v>9</v>
-      </c>
-      <c r="L5">
-        <v>9</v>
-      </c>
-      <c r="M5">
-        <v>8</v>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -11427,7 +11435,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -11442,9 +11450,10 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11467,157 +11476,172 @@
         <v>2020</v>
       </c>
       <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
         <v>2022</v>
       </c>
-      <c r="I1" s="1">
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="J1" s="1">
+      <c r="K1" s="1">
         <v>2024</v>
       </c>
-      <c r="K1" s="1">
+      <c r="L1" s="1">
         <v>2025</v>
       </c>
-      <c r="L1" s="1">
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>1</v>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
         <v>2</v>
       </c>
       <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
         <v>4</v>
       </c>
     </row>
@@ -13581,25 +13605,40 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
         <v>2</v>
       </c>
     </row>
@@ -13610,31 +13649,34 @@
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>3</v>
+      <c r="C3">
+        <v>2</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
         <v>3</v>
       </c>
     </row>
@@ -13642,6 +13684,9 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
       <c r="J4">
         <v>1</v>
       </c>
@@ -13651,40 +13696,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G5">
         <v>12</v>
       </c>
       <c r="H5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -13692,40 +13737,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="G6">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L6">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -15200,10 +15245,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -15264,40 +15309,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15305,177 +15350,122 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="L3">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>11</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="G4">
+        <v>7</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>15</v>
+      </c>
+      <c r="D5">
+        <v>12</v>
+      </c>
+      <c r="E5">
+        <v>11</v>
+      </c>
+      <c r="F5">
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="I5">
+        <v>12</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="K5">
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>30</v>
-      </c>
-      <c r="C6">
-        <v>44</v>
-      </c>
-      <c r="D6">
-        <v>49</v>
-      </c>
-      <c r="E6">
-        <v>67</v>
-      </c>
-      <c r="F6">
-        <v>69</v>
-      </c>
-      <c r="G6">
-        <v>57</v>
-      </c>
-      <c r="H6">
-        <v>80</v>
-      </c>
-      <c r="I6">
-        <v>80</v>
-      </c>
-      <c r="J6">
-        <v>64</v>
-      </c>
-      <c r="K6">
-        <v>48</v>
-      </c>
-      <c r="L6">
-        <v>44</v>
-      </c>
-      <c r="M6">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>49</v>
-      </c>
-      <c r="C7">
-        <v>62</v>
-      </c>
-      <c r="D7">
-        <v>79</v>
-      </c>
-      <c r="E7">
-        <v>92</v>
-      </c>
-      <c r="F7">
-        <v>92</v>
-      </c>
-      <c r="G7">
-        <v>88</v>
-      </c>
-      <c r="H7">
-        <v>120</v>
-      </c>
-      <c r="I7">
-        <v>130</v>
-      </c>
-      <c r="J7">
-        <v>131</v>
-      </c>
-      <c r="K7">
-        <v>91</v>
-      </c>
-      <c r="L7">
-        <v>100</v>
-      </c>
-      <c r="M7">
-        <v>45</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -17227,7 +17217,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -17242,9 +17232,10 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -17264,163 +17255,176 @@
         <v>2019</v>
       </c>
       <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
         <v>2021</v>
       </c>
-      <c r="H1" s="1">
+      <c r="I1" s="1">
         <v>2022</v>
       </c>
-      <c r="I1" s="1">
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="J1" s="1">
+      <c r="K1" s="1">
         <v>2024</v>
       </c>
-      <c r="K1" s="1">
+      <c r="L1" s="1">
         <v>2025</v>
       </c>
-      <c r="L1" s="1">
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="D2">
         <v>2</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
       <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L2">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
       <c r="J4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>17</v>
+      </c>
+      <c r="F5">
+        <v>18</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>12</v>
+      </c>
+      <c r="I5">
+        <v>17</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>17</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>19</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="I6">
+        <v>19</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="K6">
+        <v>24</v>
       </c>
       <c r="L6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>7</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>5</v>
-      </c>
-      <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -19081,23 +19085,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
       <c r="F2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>15</v>
+      </c>
+      <c r="L2">
+        <v>15</v>
       </c>
       <c r="M2">
         <v>2</v>
@@ -19108,49 +19127,94 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>26</v>
+      </c>
+      <c r="L3">
+        <v>34</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>4</v>
+      </c>
       <c r="J4">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>5</v>
+      </c>
+      <c r="M4">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K5">
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -19159,40 +19223,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -19200,40 +19264,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>92</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="G7">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>120</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>130</v>
       </c>
       <c r="J7">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="K7">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="L7">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -20322,7 +20386,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -20337,10 +20401,9 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -20360,226 +20423,163 @@
         <v>2019</v>
       </c>
       <c r="G1" s="1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H1" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I1" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J1" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K1" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
         <v>7</v>
       </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>6</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>7</v>
-      </c>
-      <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>8</v>
-      </c>
-      <c r="E3">
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7">
         <v>9</v>
       </c>
-      <c r="F3">
-        <v>19</v>
-      </c>
-      <c r="G3">
+      <c r="L7">
         <v>9</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
-      </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>12</v>
-      </c>
-      <c r="K3">
-        <v>17</v>
-      </c>
-      <c r="L3">
-        <v>13</v>
-      </c>
-      <c r="M3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>24</v>
-      </c>
-      <c r="C6">
-        <v>37</v>
-      </c>
-      <c r="D6">
-        <v>21</v>
-      </c>
-      <c r="E6">
-        <v>22</v>
-      </c>
-      <c r="F6">
-        <v>27</v>
-      </c>
-      <c r="G6">
-        <v>15</v>
-      </c>
-      <c r="H6">
-        <v>25</v>
-      </c>
-      <c r="I6">
-        <v>21</v>
-      </c>
-      <c r="J6">
-        <v>26</v>
-      </c>
-      <c r="K6">
-        <v>49</v>
-      </c>
-      <c r="L6">
-        <v>44</v>
-      </c>
-      <c r="M6">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>32</v>
-      </c>
-      <c r="C7">
-        <v>42</v>
-      </c>
-      <c r="D7">
-        <v>36</v>
-      </c>
-      <c r="E7">
-        <v>38</v>
-      </c>
-      <c r="F7">
-        <v>53</v>
-      </c>
-      <c r="G7">
-        <v>28</v>
-      </c>
-      <c r="H7">
-        <v>39</v>
-      </c>
-      <c r="I7">
-        <v>39</v>
-      </c>
-      <c r="J7">
-        <v>47</v>
-      </c>
-      <c r="K7">
-        <v>74</v>
-      </c>
-      <c r="L7">
-        <v>63</v>
-      </c>
-      <c r="M7">
-        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-full-year.xlsx
+++ b/output/cta-violent-crime-full-year.xlsx
@@ -9,36 +9,36 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Albany Park" sheetId="3" r:id="rId3"/>
-    <sheet name="Woodlawn" sheetId="4" r:id="rId4"/>
-    <sheet name="North Lawndale" sheetId="5" r:id="rId5"/>
-    <sheet name="South Shore" sheetId="6" r:id="rId6"/>
-    <sheet name="Old Town" sheetId="7" r:id="rId7"/>
-    <sheet name="Loop" sheetId="8" r:id="rId8"/>
-    <sheet name="O'Hare" sheetId="9" r:id="rId9"/>
-    <sheet name="Near South Side" sheetId="10" r:id="rId10"/>
-    <sheet name="Grand Crossing" sheetId="11" r:id="rId11"/>
-    <sheet name="Austin" sheetId="12" r:id="rId12"/>
-    <sheet name="Avondale" sheetId="13" r:id="rId13"/>
-    <sheet name="Rush &amp; Division" sheetId="14" r:id="rId14"/>
-    <sheet name="Oakland" sheetId="15" r:id="rId15"/>
-    <sheet name="Chatham" sheetId="16" r:id="rId16"/>
-    <sheet name="New City" sheetId="17" r:id="rId17"/>
-    <sheet name="Belmont Cragin" sheetId="18" r:id="rId18"/>
-    <sheet name="West Loop" sheetId="19" r:id="rId19"/>
-    <sheet name="Uptown" sheetId="20" r:id="rId20"/>
-    <sheet name="Lake View" sheetId="21" r:id="rId21"/>
-    <sheet name="Grand Boulevard" sheetId="22" r:id="rId22"/>
-    <sheet name="West Town" sheetId="23" r:id="rId23"/>
-    <sheet name="Englewood" sheetId="24" r:id="rId24"/>
-    <sheet name="Greektown" sheetId="25" r:id="rId25"/>
-    <sheet name="Edgewater" sheetId="26" r:id="rId26"/>
-    <sheet name="Little Italy, UIC" sheetId="27" r:id="rId27"/>
-    <sheet name="Gage Park" sheetId="28" r:id="rId28"/>
-    <sheet name="Humboldt Park" sheetId="29" r:id="rId29"/>
-    <sheet name="Lower West Side" sheetId="30" r:id="rId30"/>
-    <sheet name="Sheffield &amp; DePaul" sheetId="31" r:id="rId31"/>
-    <sheet name="Roseland" sheetId="32" r:id="rId32"/>
+    <sheet name="Austin" sheetId="3" r:id="rId3"/>
+    <sheet name="Roseland" sheetId="4" r:id="rId4"/>
+    <sheet name="Albany Park" sheetId="5" r:id="rId5"/>
+    <sheet name="Woodlawn" sheetId="6" r:id="rId6"/>
+    <sheet name="North Lawndale" sheetId="7" r:id="rId7"/>
+    <sheet name="South Shore" sheetId="8" r:id="rId8"/>
+    <sheet name="Old Town" sheetId="9" r:id="rId9"/>
+    <sheet name="Loop" sheetId="10" r:id="rId10"/>
+    <sheet name="O'Hare" sheetId="11" r:id="rId11"/>
+    <sheet name="Near South Side" sheetId="12" r:id="rId12"/>
+    <sheet name="Grand Crossing" sheetId="13" r:id="rId13"/>
+    <sheet name="Avondale" sheetId="14" r:id="rId14"/>
+    <sheet name="Rush &amp; Division" sheetId="15" r:id="rId15"/>
+    <sheet name="Oakland" sheetId="16" r:id="rId16"/>
+    <sheet name="Chatham" sheetId="17" r:id="rId17"/>
+    <sheet name="New City" sheetId="18" r:id="rId18"/>
+    <sheet name="Belmont Cragin" sheetId="19" r:id="rId19"/>
+    <sheet name="West Loop" sheetId="20" r:id="rId20"/>
+    <sheet name="Uptown" sheetId="21" r:id="rId21"/>
+    <sheet name="Lake View" sheetId="22" r:id="rId22"/>
+    <sheet name="Grand Boulevard" sheetId="23" r:id="rId23"/>
+    <sheet name="West Town" sheetId="24" r:id="rId24"/>
+    <sheet name="Englewood" sheetId="25" r:id="rId25"/>
+    <sheet name="Greektown" sheetId="26" r:id="rId26"/>
+    <sheet name="Edgewater" sheetId="27" r:id="rId27"/>
+    <sheet name="Little Italy, UIC" sheetId="28" r:id="rId28"/>
+    <sheet name="Gage Park" sheetId="29" r:id="rId29"/>
+    <sheet name="Humboldt Park" sheetId="30" r:id="rId30"/>
+    <sheet name="Lower West Side" sheetId="31" r:id="rId31"/>
+    <sheet name="Sheffield &amp; DePaul" sheetId="32" r:id="rId32"/>
     <sheet name="Norwood Park" sheetId="33" r:id="rId33"/>
     <sheet name="Garfield Park" sheetId="34" r:id="rId34"/>
     <sheet name="Wrigleyville" sheetId="35" r:id="rId35"/>
@@ -930,7 +930,7 @@
         <v>262</v>
       </c>
       <c r="M3">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -971,7 +971,7 @@
         <v>25</v>
       </c>
       <c r="M4">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1091,7 +1091,7 @@
         <v>896</v>
       </c>
       <c r="M7">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>
@@ -1164,23 +1164,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
       <c r="F2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>15</v>
+      </c>
+      <c r="L2">
+        <v>15</v>
       </c>
       <c r="M2">
         <v>2</v>
@@ -1191,49 +1206,94 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>26</v>
+      </c>
+      <c r="L3">
+        <v>34</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>4</v>
+      </c>
       <c r="J4">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>5</v>
+      </c>
+      <c r="M4">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K5">
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -1242,40 +1302,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1283,40 +1343,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>92</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="G7">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>120</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>130</v>
       </c>
       <c r="J7">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="K7">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="L7">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1326,7 +1386,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -1341,10 +1401,9 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1364,226 +1423,163 @@
         <v>2019</v>
       </c>
       <c r="G1" s="1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H1" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I1" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J1" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K1" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
         <v>7</v>
       </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>6</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>7</v>
-      </c>
-      <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>8</v>
-      </c>
-      <c r="E3">
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7">
         <v>9</v>
       </c>
-      <c r="F3">
-        <v>19</v>
-      </c>
-      <c r="G3">
+      <c r="L7">
         <v>9</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
-      </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>12</v>
-      </c>
-      <c r="K3">
-        <v>17</v>
-      </c>
-      <c r="L3">
-        <v>13</v>
-      </c>
-      <c r="M3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>24</v>
-      </c>
-      <c r="C6">
-        <v>37</v>
-      </c>
-      <c r="D6">
-        <v>21</v>
-      </c>
-      <c r="E6">
-        <v>22</v>
-      </c>
-      <c r="F6">
-        <v>27</v>
-      </c>
-      <c r="G6">
-        <v>15</v>
-      </c>
-      <c r="H6">
-        <v>25</v>
-      </c>
-      <c r="I6">
-        <v>21</v>
-      </c>
-      <c r="J6">
-        <v>26</v>
-      </c>
-      <c r="K6">
-        <v>49</v>
-      </c>
-      <c r="L6">
-        <v>44</v>
-      </c>
-      <c r="M6">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>32</v>
-      </c>
-      <c r="C7">
-        <v>42</v>
-      </c>
-      <c r="D7">
-        <v>36</v>
-      </c>
-      <c r="E7">
-        <v>38</v>
-      </c>
-      <c r="F7">
-        <v>53</v>
-      </c>
-      <c r="G7">
-        <v>28</v>
-      </c>
-      <c r="H7">
-        <v>39</v>
-      </c>
-      <c r="I7">
-        <v>39</v>
-      </c>
-      <c r="J7">
-        <v>47</v>
-      </c>
-      <c r="K7">
-        <v>74</v>
-      </c>
-      <c r="L7">
-        <v>63</v>
-      </c>
-      <c r="M7">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1656,41 +1652,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
       <c r="F2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1698,62 +1679,41 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>12</v>
-      </c>
-      <c r="L3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
       <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -1770,40 +1730,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1811,40 +1771,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="F7">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="G7">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="H7">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="J7">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="M7">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1854,7 +1814,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -1918,144 +1878,200 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
       <c r="E3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="K3">
+        <v>17</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="K4">
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
       <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>42</v>
+      </c>
+      <c r="D7">
+        <v>36</v>
+      </c>
+      <c r="E7">
+        <v>38</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>28</v>
+      </c>
+      <c r="H7">
+        <v>39</v>
+      </c>
+      <c r="I7">
+        <v>39</v>
+      </c>
+      <c r="J7">
+        <v>47</v>
+      </c>
+      <c r="K7">
+        <v>74</v>
+      </c>
+      <c r="L7">
+        <v>63</v>
+      </c>
+      <c r="M7">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -2129,67 +2145,64 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
       </c>
       <c r="L3">
         <v>2</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M4">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -2198,40 +2211,37 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5">
         <v>3</v>
       </c>
       <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2239,40 +2249,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2281,6 +2291,223 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>14</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>16</v>
+      </c>
+      <c r="H6">
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <v>14</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>7</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2374,7 +2601,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2626,7 +2853,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2810,7 +3037,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2961,243 +3188,6 @@
       </c>
       <c r="K6">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>4</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>8</v>
-      </c>
-      <c r="H6">
-        <v>9</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>7</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>7</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>8</v>
-      </c>
-      <c r="E7">
-        <v>9</v>
-      </c>
-      <c r="F7">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>12</v>
-      </c>
-      <c r="H7">
-        <v>16</v>
-      </c>
-      <c r="I7">
-        <v>13</v>
-      </c>
-      <c r="J7">
-        <v>8</v>
-      </c>
-      <c r="K7">
-        <v>14</v>
-      </c>
-      <c r="L7">
-        <v>15</v>
-      </c>
-      <c r="M7">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3496,7 +3486,7 @@
         <v>33</v>
       </c>
       <c r="M8">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -5794,7 +5784,7 @@
         <v>37</v>
       </c>
       <c r="M77">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -6562,7 +6552,7 @@
         <v>896</v>
       </c>
       <c r="M98">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>
@@ -6671,7 +6661,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -6735,37 +6725,28 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>2</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2">
         <v>2</v>
@@ -6775,128 +6756,139 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
+      <c r="B3">
         <v>1</v>
       </c>
       <c r="D3">
         <v>2</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>9</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>14</v>
-      </c>
-      <c r="H5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>11</v>
-      </c>
-      <c r="L5">
-        <v>8</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
         <v>8</v>
-      </c>
-      <c r="C6">
-        <v>14</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>11</v>
       </c>
       <c r="F6">
         <v>10</v>
       </c>
       <c r="G6">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H6">
+        <v>9</v>
+      </c>
+      <c r="I6">
+        <v>7</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>7</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>7</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>9</v>
+      </c>
+      <c r="F7">
+        <v>12</v>
+      </c>
+      <c r="G7">
+        <v>12</v>
+      </c>
+      <c r="H7">
+        <v>16</v>
+      </c>
+      <c r="I7">
+        <v>13</v>
+      </c>
+      <c r="J7">
+        <v>8</v>
+      </c>
+      <c r="K7">
         <v>14</v>
       </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>16</v>
-      </c>
-      <c r="K6">
-        <v>23</v>
-      </c>
-      <c r="L6">
-        <v>13</v>
-      </c>
-      <c r="M6">
-        <v>8</v>
+      <c r="L7">
+        <v>15</v>
+      </c>
+      <c r="M7">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -6969,6 +6961,9 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
       <c r="C2">
         <v>4</v>
       </c>
@@ -6976,133 +6971,118 @@
         <v>1</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
         <v>7</v>
       </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>11</v>
-      </c>
       <c r="K3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+      <c r="B4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
       <c r="C5">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
         <v>14</v>
       </c>
-      <c r="D5">
-        <v>12</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-      <c r="F5">
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
         <v>11</v>
       </c>
-      <c r="G5">
-        <v>11</v>
-      </c>
-      <c r="H5">
-        <v>17</v>
-      </c>
-      <c r="I5">
-        <v>20</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>10</v>
-      </c>
       <c r="L5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -7110,40 +7090,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>22</v>
+      </c>
+      <c r="H6">
         <v>14</v>
       </c>
-      <c r="E6">
-        <v>18</v>
-      </c>
-      <c r="F6">
-        <v>18</v>
-      </c>
-      <c r="G6">
-        <v>19</v>
-      </c>
-      <c r="H6">
-        <v>27</v>
-      </c>
       <c r="I6">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>16</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L6">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -7152,6 +7132,253 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>6</v>
+      </c>
+      <c r="L2">
+        <v>6</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>11</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>14</v>
+      </c>
+      <c r="D5">
+        <v>12</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>11</v>
+      </c>
+      <c r="H5">
+        <v>17</v>
+      </c>
+      <c r="I5">
+        <v>20</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>10</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>23</v>
+      </c>
+      <c r="D6">
+        <v>14</v>
+      </c>
+      <c r="E6">
+        <v>18</v>
+      </c>
+      <c r="F6">
+        <v>18</v>
+      </c>
+      <c r="G6">
+        <v>19</v>
+      </c>
+      <c r="H6">
+        <v>27</v>
+      </c>
+      <c r="I6">
+        <v>26</v>
+      </c>
+      <c r="J6">
+        <v>16</v>
+      </c>
+      <c r="K6">
+        <v>24</v>
+      </c>
+      <c r="L6">
+        <v>20</v>
+      </c>
+      <c r="M6">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7368,7 +7595,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7597,7 +7824,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7861,7 +8088,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8031,226 +8258,6 @@
       </c>
       <c r="L6">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>12</v>
-      </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>16</v>
-      </c>
-      <c r="L5">
-        <v>8</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>13</v>
-      </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
-      </c>
-      <c r="K6">
-        <v>21</v>
-      </c>
-      <c r="L6">
-        <v>13</v>
-      </c>
-      <c r="M6">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -8324,19 +8331,19 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -8345,66 +8352,48 @@
         <v>5</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
       <c r="M4">
         <v>1</v>
       </c>
@@ -8414,40 +8403,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>12</v>
+      </c>
+      <c r="I5">
         <v>7</v>
       </c>
-      <c r="D5">
-        <v>11</v>
-      </c>
-      <c r="E5">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>25</v>
-      </c>
-      <c r="G5">
-        <v>15</v>
-      </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>9</v>
-      </c>
       <c r="J5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -8455,40 +8444,40 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
         <v>10</v>
       </c>
-      <c r="C6">
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>13</v>
+      </c>
+      <c r="I6">
+        <v>12</v>
+      </c>
+      <c r="J6">
         <v>10</v>
       </c>
-      <c r="D6">
-        <v>14</v>
-      </c>
-      <c r="E6">
-        <v>23</v>
-      </c>
-      <c r="F6">
-        <v>28</v>
-      </c>
-      <c r="G6">
-        <v>16</v>
-      </c>
-      <c r="H6">
-        <v>14</v>
-      </c>
-      <c r="I6">
-        <v>17</v>
-      </c>
-      <c r="J6">
-        <v>16</v>
-      </c>
       <c r="K6">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="L6">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -8497,6 +8486,244 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>11</v>
+      </c>
+      <c r="E5">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>25</v>
+      </c>
+      <c r="G5">
+        <v>15</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5">
+        <v>11</v>
+      </c>
+      <c r="K5">
+        <v>18</v>
+      </c>
+      <c r="L5">
+        <v>11</v>
+      </c>
+      <c r="M5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>14</v>
+      </c>
+      <c r="E6">
+        <v>23</v>
+      </c>
+      <c r="F6">
+        <v>28</v>
+      </c>
+      <c r="G6">
+        <v>16</v>
+      </c>
+      <c r="H6">
+        <v>14</v>
+      </c>
+      <c r="I6">
+        <v>17</v>
+      </c>
+      <c r="J6">
+        <v>16</v>
+      </c>
+      <c r="K6">
+        <v>31</v>
+      </c>
+      <c r="L6">
+        <v>22</v>
+      </c>
+      <c r="M6">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8721,7 +8948,268 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>8</v>
+      </c>
+      <c r="K2">
+        <v>7</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>7</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>6</v>
+      </c>
+      <c r="J3">
+        <v>10</v>
+      </c>
+      <c r="K3">
+        <v>12</v>
+      </c>
+      <c r="L3">
+        <v>14</v>
+      </c>
+      <c r="M3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>23</v>
+      </c>
+      <c r="C6">
+        <v>31</v>
+      </c>
+      <c r="D6">
+        <v>22</v>
+      </c>
+      <c r="E6">
+        <v>44</v>
+      </c>
+      <c r="F6">
+        <v>38</v>
+      </c>
+      <c r="G6">
+        <v>24</v>
+      </c>
+      <c r="H6">
+        <v>50</v>
+      </c>
+      <c r="I6">
+        <v>34</v>
+      </c>
+      <c r="J6">
+        <v>26</v>
+      </c>
+      <c r="K6">
+        <v>24</v>
+      </c>
+      <c r="L6">
+        <v>14</v>
+      </c>
+      <c r="M6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>40</v>
+      </c>
+      <c r="D7">
+        <v>32</v>
+      </c>
+      <c r="E7">
+        <v>57</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>34</v>
+      </c>
+      <c r="H7">
+        <v>63</v>
+      </c>
+      <c r="I7">
+        <v>44</v>
+      </c>
+      <c r="J7">
+        <v>47</v>
+      </c>
+      <c r="K7">
+        <v>46</v>
+      </c>
+      <c r="L7">
+        <v>33</v>
+      </c>
+      <c r="M7">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8956,208 +9444,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>9</v>
-      </c>
-      <c r="J6">
-        <v>7</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9357,7 +9644,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9573,270 +9860,6 @@
       </c>
       <c r="M6">
         <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2">
-        <v>4</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
-        <v>6</v>
-      </c>
-      <c r="I2">
-        <v>7</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>5</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>5</v>
-      </c>
-      <c r="F3">
-        <v>7</v>
-      </c>
-      <c r="G3">
-        <v>6</v>
-      </c>
-      <c r="H3">
-        <v>6</v>
-      </c>
-      <c r="I3">
-        <v>9</v>
-      </c>
-      <c r="J3">
-        <v>14</v>
-      </c>
-      <c r="K3">
-        <v>7</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>19</v>
-      </c>
-      <c r="C6">
-        <v>16</v>
-      </c>
-      <c r="D6">
-        <v>11</v>
-      </c>
-      <c r="E6">
-        <v>14</v>
-      </c>
-      <c r="F6">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>14</v>
-      </c>
-      <c r="H6">
-        <v>19</v>
-      </c>
-      <c r="I6">
-        <v>29</v>
-      </c>
-      <c r="J6">
-        <v>19</v>
-      </c>
-      <c r="K6">
-        <v>20</v>
-      </c>
-      <c r="L6">
-        <v>26</v>
-      </c>
-      <c r="M6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>26</v>
-      </c>
-      <c r="C7">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>16</v>
-      </c>
-      <c r="E7">
-        <v>23</v>
-      </c>
-      <c r="F7">
-        <v>23</v>
-      </c>
-      <c r="G7">
-        <v>24</v>
-      </c>
-      <c r="H7">
-        <v>31</v>
-      </c>
-      <c r="I7">
-        <v>47</v>
-      </c>
-      <c r="J7">
-        <v>35</v>
-      </c>
-      <c r="K7">
-        <v>31</v>
-      </c>
-      <c r="L7">
-        <v>37</v>
-      </c>
-      <c r="M7">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -11435,7 +11458,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -11499,21 +11522,39 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
       </c>
       <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -11522,127 +11563,156 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
         <v>5</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>11</v>
-      </c>
-      <c r="C5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>7</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
+        <v>19</v>
+      </c>
+      <c r="C6">
         <v>16</v>
       </c>
-      <c r="C6">
-        <v>13</v>
-      </c>
       <c r="D6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="J6">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="K6">
+        <v>20</v>
+      </c>
+      <c r="L6">
+        <v>26</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>26</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>16</v>
+      </c>
+      <c r="E7">
+        <v>23</v>
+      </c>
+      <c r="F7">
+        <v>23</v>
+      </c>
+      <c r="G7">
+        <v>24</v>
+      </c>
+      <c r="H7">
+        <v>31</v>
+      </c>
+      <c r="I7">
+        <v>47</v>
+      </c>
+      <c r="J7">
+        <v>35</v>
+      </c>
+      <c r="K7">
+        <v>31</v>
+      </c>
+      <c r="L7">
+        <v>37</v>
+      </c>
+      <c r="M7">
         <v>12</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -13542,7 +13612,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -13557,10 +13627,9 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13583,66 +13652,51 @@
         <v>2020</v>
       </c>
       <c r="H1" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I1" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J1" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K1" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -13650,127 +13704,106 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>9</v>
+      </c>
+      <c r="J6">
         <v>7</v>
       </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>12</v>
-      </c>
-      <c r="C5">
-        <v>21</v>
-      </c>
-      <c r="D5">
-        <v>28</v>
-      </c>
-      <c r="E5">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>35</v>
-      </c>
-      <c r="G5">
-        <v>12</v>
-      </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>15</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>9</v>
-      </c>
-      <c r="L5">
-        <v>7</v>
-      </c>
-      <c r="M5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>14</v>
-      </c>
-      <c r="C6">
-        <v>26</v>
-      </c>
-      <c r="D6">
-        <v>29</v>
-      </c>
-      <c r="E6">
-        <v>24</v>
-      </c>
-      <c r="F6">
-        <v>42</v>
-      </c>
-      <c r="G6">
-        <v>18</v>
-      </c>
-      <c r="H6">
-        <v>18</v>
-      </c>
-      <c r="I6">
-        <v>21</v>
-      </c>
-      <c r="J6">
-        <v>12</v>
-      </c>
       <c r="K6">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>18</v>
-      </c>
-      <c r="M6">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -15245,10 +15278,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -15309,40 +15342,22 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
         <v>2</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
       <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15353,119 +15368,124 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>5</v>
       </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
       <c r="F3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>4</v>
-      </c>
-      <c r="L3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>11</v>
-      </c>
-      <c r="C4">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <v>6</v>
-      </c>
-      <c r="E4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>7</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>8</v>
-      </c>
-      <c r="J4">
-        <v>12</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>7</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>11</v>
+      </c>
+      <c r="J6">
+        <v>11</v>
+      </c>
+      <c r="K6">
         <v>12</v>
       </c>
-      <c r="E5">
-        <v>11</v>
-      </c>
-      <c r="F5">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>9</v>
-      </c>
-      <c r="H5">
-        <v>11</v>
-      </c>
-      <c r="I5">
-        <v>12</v>
-      </c>
-      <c r="J5">
-        <v>15</v>
-      </c>
-      <c r="K5">
-        <v>9</v>
-      </c>
-      <c r="L5">
-        <v>9</v>
-      </c>
-      <c r="M5">
-        <v>8</v>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -17280,25 +17300,40 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
         <v>2</v>
       </c>
     </row>
@@ -17309,31 +17344,34 @@
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>3</v>
+      <c r="C3">
+        <v>2</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
         <v>3</v>
       </c>
     </row>
@@ -17341,6 +17379,9 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
       <c r="J4">
         <v>1</v>
       </c>
@@ -17350,40 +17391,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G5">
         <v>12</v>
       </c>
       <c r="H5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -17391,40 +17432,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="G6">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L6">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -19022,10 +19063,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -19086,40 +19127,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -19127,177 +19168,122 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="L3">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>11</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="G4">
+        <v>7</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>15</v>
+      </c>
+      <c r="D5">
+        <v>12</v>
+      </c>
+      <c r="E5">
+        <v>11</v>
+      </c>
+      <c r="F5">
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="I5">
+        <v>12</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="K5">
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>30</v>
-      </c>
-      <c r="C6">
-        <v>44</v>
-      </c>
-      <c r="D6">
-        <v>49</v>
-      </c>
-      <c r="E6">
-        <v>67</v>
-      </c>
-      <c r="F6">
-        <v>69</v>
-      </c>
-      <c r="G6">
-        <v>57</v>
-      </c>
-      <c r="H6">
-        <v>80</v>
-      </c>
-      <c r="I6">
-        <v>80</v>
-      </c>
-      <c r="J6">
-        <v>64</v>
-      </c>
-      <c r="K6">
-        <v>48</v>
-      </c>
-      <c r="L6">
-        <v>44</v>
-      </c>
-      <c r="M6">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>49</v>
-      </c>
-      <c r="C7">
-        <v>62</v>
-      </c>
-      <c r="D7">
-        <v>79</v>
-      </c>
-      <c r="E7">
-        <v>92</v>
-      </c>
-      <c r="F7">
-        <v>92</v>
-      </c>
-      <c r="G7">
-        <v>88</v>
-      </c>
-      <c r="H7">
-        <v>120</v>
-      </c>
-      <c r="I7">
-        <v>130</v>
-      </c>
-      <c r="J7">
-        <v>131</v>
-      </c>
-      <c r="K7">
-        <v>91</v>
-      </c>
-      <c r="L7">
-        <v>100</v>
-      </c>
-      <c r="M7">
-        <v>45</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -20386,7 +20372,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -20401,9 +20387,10 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -20423,163 +20410,176 @@
         <v>2019</v>
       </c>
       <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
         <v>2021</v>
       </c>
-      <c r="H1" s="1">
+      <c r="I1" s="1">
         <v>2022</v>
       </c>
-      <c r="I1" s="1">
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="J1" s="1">
+      <c r="K1" s="1">
         <v>2024</v>
       </c>
-      <c r="K1" s="1">
+      <c r="L1" s="1">
         <v>2025</v>
       </c>
-      <c r="L1" s="1">
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="D2">
         <v>2</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
       <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L2">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
       <c r="J4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>17</v>
+      </c>
+      <c r="F5">
+        <v>18</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>12</v>
+      </c>
+      <c r="I5">
+        <v>17</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>17</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>19</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="I6">
+        <v>19</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="K6">
+        <v>24</v>
       </c>
       <c r="L6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>7</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>5</v>
-      </c>
-      <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-full-year.xlsx
+++ b/output/cta-violent-crime-full-year.xlsx
@@ -28,81 +28,81 @@
     <sheet name="Belmont Cragin" sheetId="19" r:id="rId19"/>
     <sheet name="West Loop" sheetId="20" r:id="rId20"/>
     <sheet name="Uptown" sheetId="21" r:id="rId21"/>
-    <sheet name="Lake View" sheetId="22" r:id="rId22"/>
-    <sheet name="Grand Boulevard" sheetId="23" r:id="rId23"/>
-    <sheet name="West Town" sheetId="24" r:id="rId24"/>
-    <sheet name="Englewood" sheetId="25" r:id="rId25"/>
-    <sheet name="Greektown" sheetId="26" r:id="rId26"/>
-    <sheet name="Edgewater" sheetId="27" r:id="rId27"/>
-    <sheet name="Little Italy, UIC" sheetId="28" r:id="rId28"/>
-    <sheet name="Gage Park" sheetId="29" r:id="rId29"/>
-    <sheet name="Humboldt Park" sheetId="30" r:id="rId30"/>
-    <sheet name="Lower West Side" sheetId="31" r:id="rId31"/>
-    <sheet name="Sheffield &amp; DePaul" sheetId="32" r:id="rId32"/>
-    <sheet name="Norwood Park" sheetId="33" r:id="rId33"/>
-    <sheet name="Garfield Park" sheetId="34" r:id="rId34"/>
-    <sheet name="Wrigleyville" sheetId="35" r:id="rId35"/>
-    <sheet name="Auburn Gresham" sheetId="36" r:id="rId36"/>
-    <sheet name="Rogers Park" sheetId="37" r:id="rId37"/>
-    <sheet name="Washington Park" sheetId="38" r:id="rId38"/>
-    <sheet name="Chicago Lawn" sheetId="39" r:id="rId39"/>
-    <sheet name="Kenwood" sheetId="40" r:id="rId40"/>
-    <sheet name="Calumet Heights" sheetId="41" r:id="rId41"/>
-    <sheet name="Hyde Park" sheetId="42" r:id="rId42"/>
-    <sheet name="Fuller Park" sheetId="43" r:id="rId43"/>
-    <sheet name="South Chicago" sheetId="44" r:id="rId44"/>
-    <sheet name="Armour Square" sheetId="45" r:id="rId45"/>
-    <sheet name="Douglas" sheetId="46" r:id="rId46"/>
-    <sheet name="United Center" sheetId="47" r:id="rId47"/>
-    <sheet name="Grant Park" sheetId="48" r:id="rId48"/>
-    <sheet name="Jefferson Park" sheetId="49" r:id="rId49"/>
-    <sheet name="Streeterville" sheetId="50" r:id="rId50"/>
-    <sheet name="Millenium Park" sheetId="51" r:id="rId51"/>
-    <sheet name="River North" sheetId="52" r:id="rId52"/>
-    <sheet name="Beverly" sheetId="53" r:id="rId53"/>
-    <sheet name="South Deering" sheetId="54" r:id="rId54"/>
-    <sheet name="West Elsdon" sheetId="55" r:id="rId55"/>
-    <sheet name="Pullman" sheetId="56" r:id="rId56"/>
-    <sheet name="West Pullman" sheetId="57" r:id="rId57"/>
-    <sheet name="Morgan Park" sheetId="58" r:id="rId58"/>
-    <sheet name="Wicker Park" sheetId="59" r:id="rId59"/>
-    <sheet name="Little Village" sheetId="60" r:id="rId60"/>
-    <sheet name="Irving Park" sheetId="61" r:id="rId61"/>
-    <sheet name="Jackson Park" sheetId="62" r:id="rId62"/>
-    <sheet name="Brighton Park" sheetId="63" r:id="rId63"/>
-    <sheet name="Bridgeport" sheetId="64" r:id="rId64"/>
-    <sheet name="Clearing" sheetId="65" r:id="rId65"/>
-    <sheet name="Mckinley Park" sheetId="66" r:id="rId66"/>
-    <sheet name="Chinatown" sheetId="67" r:id="rId67"/>
-    <sheet name="Bucktown" sheetId="68" r:id="rId68"/>
-    <sheet name="Ukrainian Village" sheetId="69" r:id="rId69"/>
-    <sheet name="Ashburn" sheetId="70" r:id="rId70"/>
-    <sheet name="Washington Heights" sheetId="71" r:id="rId71"/>
-    <sheet name="Printers Row" sheetId="72" r:id="rId72"/>
-    <sheet name="Logan Square" sheetId="73" r:id="rId73"/>
-    <sheet name="Lincoln Park" sheetId="74" r:id="rId74"/>
-    <sheet name="Archer Heights" sheetId="75" r:id="rId75"/>
-    <sheet name="Boystown" sheetId="76" r:id="rId76"/>
-    <sheet name="Lincoln Square" sheetId="77" r:id="rId77"/>
-    <sheet name="Hermosa" sheetId="78" r:id="rId78"/>
-    <sheet name="Riverdale" sheetId="79" r:id="rId79"/>
-    <sheet name="North Center" sheetId="80" r:id="rId80"/>
-    <sheet name="Avalon Park" sheetId="81" r:id="rId81"/>
-    <sheet name="Burnside" sheetId="82" r:id="rId82"/>
-    <sheet name="East Side" sheetId="83" r:id="rId83"/>
-    <sheet name="Portage Park" sheetId="84" r:id="rId84"/>
-    <sheet name="Montclare" sheetId="85" r:id="rId85"/>
-    <sheet name="West Ridge" sheetId="86" r:id="rId86"/>
-    <sheet name="North Park" sheetId="87" r:id="rId87"/>
-    <sheet name="Magnificent Mile" sheetId="88" r:id="rId88"/>
-    <sheet name="East Village" sheetId="89" r:id="rId89"/>
-    <sheet name="Galewood" sheetId="90" r:id="rId90"/>
-    <sheet name="Gold Coast" sheetId="91" r:id="rId91"/>
-    <sheet name="Mount Greenwood" sheetId="92" r:id="rId92"/>
-    <sheet name="Garfield Ridge" sheetId="93" r:id="rId93"/>
-    <sheet name="West Lawn" sheetId="94" r:id="rId94"/>
-    <sheet name="Dunning" sheetId="95" r:id="rId95"/>
-    <sheet name="Hegewisch" sheetId="96" r:id="rId96"/>
+    <sheet name="Hegewisch" sheetId="22" r:id="rId22"/>
+    <sheet name="Lake View" sheetId="23" r:id="rId23"/>
+    <sheet name="Grand Boulevard" sheetId="24" r:id="rId24"/>
+    <sheet name="West Town" sheetId="25" r:id="rId25"/>
+    <sheet name="Englewood" sheetId="26" r:id="rId26"/>
+    <sheet name="Greektown" sheetId="27" r:id="rId27"/>
+    <sheet name="Edgewater" sheetId="28" r:id="rId28"/>
+    <sheet name="Little Italy, UIC" sheetId="29" r:id="rId29"/>
+    <sheet name="Gage Park" sheetId="30" r:id="rId30"/>
+    <sheet name="Humboldt Park" sheetId="31" r:id="rId31"/>
+    <sheet name="Lower West Side" sheetId="32" r:id="rId32"/>
+    <sheet name="Sheffield &amp; DePaul" sheetId="33" r:id="rId33"/>
+    <sheet name="Norwood Park" sheetId="34" r:id="rId34"/>
+    <sheet name="Garfield Park" sheetId="35" r:id="rId35"/>
+    <sheet name="Wrigleyville" sheetId="36" r:id="rId36"/>
+    <sheet name="Auburn Gresham" sheetId="37" r:id="rId37"/>
+    <sheet name="Rogers Park" sheetId="38" r:id="rId38"/>
+    <sheet name="Washington Park" sheetId="39" r:id="rId39"/>
+    <sheet name="Chicago Lawn" sheetId="40" r:id="rId40"/>
+    <sheet name="Kenwood" sheetId="41" r:id="rId41"/>
+    <sheet name="Calumet Heights" sheetId="42" r:id="rId42"/>
+    <sheet name="Hyde Park" sheetId="43" r:id="rId43"/>
+    <sheet name="Fuller Park" sheetId="44" r:id="rId44"/>
+    <sheet name="South Chicago" sheetId="45" r:id="rId45"/>
+    <sheet name="Armour Square" sheetId="46" r:id="rId46"/>
+    <sheet name="Douglas" sheetId="47" r:id="rId47"/>
+    <sheet name="United Center" sheetId="48" r:id="rId48"/>
+    <sheet name="Grant Park" sheetId="49" r:id="rId49"/>
+    <sheet name="Jefferson Park" sheetId="50" r:id="rId50"/>
+    <sheet name="Streeterville" sheetId="51" r:id="rId51"/>
+    <sheet name="Millenium Park" sheetId="52" r:id="rId52"/>
+    <sheet name="River North" sheetId="53" r:id="rId53"/>
+    <sheet name="Beverly" sheetId="54" r:id="rId54"/>
+    <sheet name="South Deering" sheetId="55" r:id="rId55"/>
+    <sheet name="West Elsdon" sheetId="56" r:id="rId56"/>
+    <sheet name="Pullman" sheetId="57" r:id="rId57"/>
+    <sheet name="West Pullman" sheetId="58" r:id="rId58"/>
+    <sheet name="Morgan Park" sheetId="59" r:id="rId59"/>
+    <sheet name="Wicker Park" sheetId="60" r:id="rId60"/>
+    <sheet name="Little Village" sheetId="61" r:id="rId61"/>
+    <sheet name="Irving Park" sheetId="62" r:id="rId62"/>
+    <sheet name="Jackson Park" sheetId="63" r:id="rId63"/>
+    <sheet name="Brighton Park" sheetId="64" r:id="rId64"/>
+    <sheet name="Bridgeport" sheetId="65" r:id="rId65"/>
+    <sheet name="Clearing" sheetId="66" r:id="rId66"/>
+    <sheet name="Mckinley Park" sheetId="67" r:id="rId67"/>
+    <sheet name="Chinatown" sheetId="68" r:id="rId68"/>
+    <sheet name="Bucktown" sheetId="69" r:id="rId69"/>
+    <sheet name="Ukrainian Village" sheetId="70" r:id="rId70"/>
+    <sheet name="Ashburn" sheetId="71" r:id="rId71"/>
+    <sheet name="Washington Heights" sheetId="72" r:id="rId72"/>
+    <sheet name="Printers Row" sheetId="73" r:id="rId73"/>
+    <sheet name="Logan Square" sheetId="74" r:id="rId74"/>
+    <sheet name="Lincoln Park" sheetId="75" r:id="rId75"/>
+    <sheet name="Archer Heights" sheetId="76" r:id="rId76"/>
+    <sheet name="Boystown" sheetId="77" r:id="rId77"/>
+    <sheet name="Lincoln Square" sheetId="78" r:id="rId78"/>
+    <sheet name="Hermosa" sheetId="79" r:id="rId79"/>
+    <sheet name="Riverdale" sheetId="80" r:id="rId80"/>
+    <sheet name="North Center" sheetId="81" r:id="rId81"/>
+    <sheet name="Avalon Park" sheetId="82" r:id="rId82"/>
+    <sheet name="Burnside" sheetId="83" r:id="rId83"/>
+    <sheet name="East Side" sheetId="84" r:id="rId84"/>
+    <sheet name="Portage Park" sheetId="85" r:id="rId85"/>
+    <sheet name="Montclare" sheetId="86" r:id="rId86"/>
+    <sheet name="West Ridge" sheetId="87" r:id="rId87"/>
+    <sheet name="North Park" sheetId="88" r:id="rId88"/>
+    <sheet name="Magnificent Mile" sheetId="89" r:id="rId89"/>
+    <sheet name="East Village" sheetId="90" r:id="rId90"/>
+    <sheet name="Galewood" sheetId="91" r:id="rId91"/>
+    <sheet name="Gold Coast" sheetId="92" r:id="rId92"/>
+    <sheet name="Mount Greenwood" sheetId="93" r:id="rId93"/>
+    <sheet name="Garfield Ridge" sheetId="94" r:id="rId94"/>
+    <sheet name="West Lawn" sheetId="95" r:id="rId95"/>
+    <sheet name="Dunning" sheetId="96" r:id="rId96"/>
     <sheet name="Andersonville" sheetId="97" r:id="rId97"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="104">
   <si>
     <t>crime_category</t>
   </si>
@@ -930,7 +930,7 @@
         <v>262</v>
       </c>
       <c r="M3">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1091,7 +1091,7 @@
         <v>896</v>
       </c>
       <c r="M7">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -4447,6 +4447,9 @@
       <c r="G39">
         <v>1</v>
       </c>
+      <c r="M39">
+        <v>1</v>
+      </c>
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="2" t="s">
@@ -6552,7 +6555,7 @@
         <v>896</v>
       </c>
       <c r="M98">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -7133,6 +7136,84 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -7378,7 +7459,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7595,7 +7676,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7824,7 +7905,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8088,7 +8169,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8258,226 +8339,6 @@
       </c>
       <c r="L6">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>12</v>
-      </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>16</v>
-      </c>
-      <c r="L5">
-        <v>8</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>13</v>
-      </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
-      </c>
-      <c r="K6">
-        <v>21</v>
-      </c>
-      <c r="L6">
-        <v>13</v>
-      </c>
-      <c r="M6">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -8551,19 +8412,19 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -8572,66 +8433,48 @@
         <v>5</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
       <c r="M4">
         <v>1</v>
       </c>
@@ -8641,40 +8484,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>12</v>
+      </c>
+      <c r="I5">
         <v>7</v>
       </c>
-      <c r="D5">
-        <v>11</v>
-      </c>
-      <c r="E5">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>25</v>
-      </c>
-      <c r="G5">
-        <v>15</v>
-      </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>9</v>
-      </c>
       <c r="J5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -8682,40 +8525,40 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
         <v>10</v>
       </c>
-      <c r="C6">
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>13</v>
+      </c>
+      <c r="I6">
+        <v>12</v>
+      </c>
+      <c r="J6">
         <v>10</v>
       </c>
-      <c r="D6">
-        <v>14</v>
-      </c>
-      <c r="E6">
-        <v>23</v>
-      </c>
-      <c r="F6">
-        <v>28</v>
-      </c>
-      <c r="G6">
-        <v>16</v>
-      </c>
-      <c r="H6">
-        <v>14</v>
-      </c>
-      <c r="I6">
-        <v>17</v>
-      </c>
-      <c r="J6">
-        <v>16</v>
-      </c>
       <c r="K6">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="L6">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -8725,7 +8568,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -8789,25 +8632,31 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -8815,132 +8664,139 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4">
-        <v>1</v>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
       </c>
       <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>11</v>
+      </c>
+      <c r="E5">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5">
+        <v>11</v>
+      </c>
+      <c r="K5">
+        <v>18</v>
+      </c>
+      <c r="L5">
+        <v>11</v>
+      </c>
+      <c r="M5">
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>16</v>
+      </c>
+      <c r="H6">
+        <v>14</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="M6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>11</v>
-      </c>
-      <c r="E7">
-        <v>9</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <v>15</v>
-      </c>
-      <c r="L7">
         <v>13</v>
-      </c>
-      <c r="M7">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -9211,6 +9067,231 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>6</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>8</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>6</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>11</v>
+      </c>
+      <c r="E7">
+        <v>9</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>6</v>
+      </c>
+      <c r="K7">
+        <v>15</v>
+      </c>
+      <c r="L7">
+        <v>13</v>
+      </c>
+      <c r="M7">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -9444,7 +9525,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9644,7 +9725,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9867,7 +9948,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10051,7 +10132,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10308,214 +10389,6 @@
       </c>
       <c r="M7">
         <v>27</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>3</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -10591,11 +10464,8 @@
       <c r="B2">
         <v>2</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>2</v>
@@ -10606,20 +10476,8 @@
       <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
       <c r="J2">
         <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10629,42 +10487,39 @@
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
       <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
     </row>
@@ -10672,41 +10527,35 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>19</v>
-      </c>
       <c r="C5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -10714,40 +10563,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -10756,6 +10605,238 @@
 </file>
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>19</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>12</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>7</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>16</v>
+      </c>
+      <c r="F6">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>10</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <v>9</v>
+      </c>
+      <c r="K6">
+        <v>10</v>
+      </c>
+      <c r="L6">
+        <v>6</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11003,235 +11084,6 @@
       </c>
       <c r="M7">
         <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>7</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>8</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>7</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <v>11</v>
-      </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>10</v>
-      </c>
-      <c r="H6">
-        <v>7</v>
-      </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
-      <c r="J6">
-        <v>12</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>8</v>
-      </c>
-      <c r="M6">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -11304,71 +11156,80 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
         <v>2</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -11377,37 +11238,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>1</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -11415,40 +11279,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>10</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
+      </c>
+      <c r="I6">
+        <v>12</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
         <v>8</v>
       </c>
-      <c r="G6">
-        <v>13</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>6</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
       <c r="M6">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -11722,6 +11586,223 @@
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>11</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>11</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>14</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>16</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>13</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -11859,7 +11940,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12028,7 +12109,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12196,7 +12277,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12419,7 +12500,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12634,7 +12715,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12863,7 +12944,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13076,7 +13157,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13299,7 +13380,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13383,226 +13464,6 @@
       </c>
       <c r="F5">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>4</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>3</v>
-      </c>
-      <c r="M5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
-      <c r="H6">
-        <v>9</v>
-      </c>
-      <c r="I6">
-        <v>6</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
-      </c>
-      <c r="L6">
-        <v>8</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -13813,6 +13674,226 @@
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>9</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>8</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -13940,7 +14021,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14033,7 +14114,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14259,7 +14340,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14312,7 +14393,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14488,7 +14569,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14639,7 +14720,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14755,7 +14836,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14940,7 +15021,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15089,186 +15170,6 @@
       </c>
       <c r="K5">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -15495,7 +15396,7 @@
 
 <file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -15510,108 +15411,95 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D1" s="1">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E1" s="1">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="F1" s="1">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G1" s="1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H1" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I1" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J1" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K1" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
         <v>2</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -15619,21 +15507,21 @@
         <v>3</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
         <v>1</v>
       </c>
       <c r="J5">
@@ -15642,51 +15530,42 @@
       <c r="K5">
         <v>1</v>
       </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J6">
         <v>2</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
         <v>4</v>
       </c>
     </row>
@@ -15760,35 +15639,17 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="H2">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15801,10 +15662,7 @@
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
+      <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
@@ -15814,23 +15672,23 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -15839,37 +15697,34 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -15880,40 +15735,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
       <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
         <v>7</v>
       </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
       <c r="G6">
         <v>4</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -15922,326 +15777,6 @@
 </file>
 
 <file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16315,11 +15850,17 @@
       <c r="E2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
       <c r="H2">
         <v>1</v>
       </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2">
         <v>2</v>
@@ -16328,24 +15869,39 @@
         <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
       <c r="C3">
         <v>1</v>
       </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3">
         <v>2</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -16355,7 +15911,7 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J4">
+      <c r="C4">
         <v>1</v>
       </c>
     </row>
@@ -16364,13 +15920,16 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -16379,13 +15938,22 @@
         <v>2</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5">
         <v>2</v>
       </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
       <c r="K5">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -16396,34 +15964,34 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -16434,7 +16002,154 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16457,25 +16172,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
         <v>2016</v>
       </c>
-      <c r="C1" s="1">
+      <c r="D1" s="1">
         <v>2017</v>
       </c>
-      <c r="D1" s="1">
+      <c r="E1" s="1">
         <v>2018</v>
       </c>
-      <c r="E1" s="1">
-        <v>2019</v>
-      </c>
       <c r="F1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="G1" s="1">
         <v>2021</v>
       </c>
-      <c r="G1" s="1">
+      <c r="H1" s="1">
         <v>2022</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2023</v>
       </c>
       <c r="I1" s="1">
         <v>2024</v>
@@ -16494,17 +16209,17 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="E2">
+      <c r="D2">
         <v>1</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
-      <c r="I2">
-        <v>2</v>
+      <c r="J2">
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -16512,29 +16227,32 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>1</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
+      <c r="E4">
         <v>1</v>
       </c>
     </row>
@@ -16543,15 +16261,21 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
         <v>2</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
-      <c r="G5">
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
         <v>1</v>
       </c>
       <c r="J5">
@@ -16563,34 +16287,34 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6">
         <v>3</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J6">
         <v>4</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -16598,7 +16322,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16664,22 +16388,28 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -16689,16 +16419,16 @@
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
       <c r="H3">
         <v>1</v>
       </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="L3">
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="M3">
         <v>1</v>
       </c>
     </row>
@@ -16706,7 +16436,7 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L4">
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
@@ -16715,28 +16445,28 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
       </c>
       <c r="K5">
         <v>4</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -16744,40 +16474,204 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D6">
         <v>3</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J6">
         <v>2</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -16786,6 +16680,193 @@
 </file>
 
 <file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17010,7 +17091,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17123,110 +17204,6 @@
         <v>1</v>
       </c>
       <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
         <v>1</v>
       </c>
     </row>
@@ -17475,7 +17452,7 @@
 
 <file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -17485,140 +17462,71 @@
     <col min="5" max="5" width="4.7109375" customWidth="1"/>
     <col min="6" max="6" width="4.7109375" customWidth="1"/>
     <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="D1" s="1">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="E1" s="1">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="F1" s="1">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="E4">
+      <c r="D4">
         <v>2</v>
       </c>
       <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="G4">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>4</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
-      <c r="L4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -17626,37 +17534,19 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <v>4</v>
       </c>
       <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>8</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>9</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -17665,181 +17555,6 @@
 </file>
 
 <file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>8</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>7</v>
-      </c>
-      <c r="F4">
-        <v>4</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17911,32 +17626,41 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
         <v>2</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="D3">
         <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
       <c r="H3">
         <v>1</v>
       </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="L3">
+        <v>3</v>
+      </c>
+      <c r="M3">
         <v>1</v>
       </c>
     </row>
@@ -17945,40 +17669,34 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>3</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -17986,19 +17704,197 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>8</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>9</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
         <v>7</v>
       </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
       <c r="D5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -18007,18 +17903,15 @@
         <v>2</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>6</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -18029,10 +17922,10 @@
 
 <file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -18093,53 +17986,35 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
         <v>2</v>
       </c>
       <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="J2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="F3">
         <v>1</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
       <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="K3">
         <v>1</v>
       </c>
       <c r="L3">
@@ -18148,100 +18023,83 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>7</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>6</v>
       </c>
       <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G5">
         <v>5</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>9</v>
-      </c>
-      <c r="H6">
-        <v>10</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
-      <c r="J6">
-        <v>15</v>
-      </c>
-      <c r="K6">
-        <v>10</v>
-      </c>
-      <c r="L6">
-        <v>14</v>
-      </c>
-      <c r="M6">
         <v>1</v>
       </c>
     </row>
@@ -18315,56 +18173,74 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
       <c r="J2">
         <v>3</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>1</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -18373,31 +18249,37 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="K5">
+        <v>7</v>
+      </c>
+      <c r="L5">
+        <v>7</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -18411,34 +18293,34 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
+      </c>
+      <c r="I6">
         <v>7</v>
       </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
       <c r="J6">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="M6">
         <v>1</v>
@@ -18450,6 +18332,205 @@
 </file>
 
 <file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>7</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18556,7 +18637,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18619,7 +18700,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18799,7 +18880,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18901,159 +18982,6 @@
       </c>
       <c r="H4">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -19293,6 +19221,159 @@
 
 <file path=xl/worksheets/sheet80.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -19433,7 +19514,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19566,7 +19647,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19642,7 +19723,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19756,7 +19837,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19897,7 +19978,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19980,7 +20061,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet87.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -20076,7 +20157,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet87.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -20189,7 +20270,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet89.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -20269,99 +20350,6 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet89.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
         <v>1</v>
       </c>
     </row>
@@ -20589,6 +20577,99 @@
 
 <file path=xl/worksheets/sheet90.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet91.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -20666,7 +20747,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet91.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet92.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -20722,7 +20803,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet92.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet93.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -20785,7 +20866,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet93.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet94.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -20866,77 +20947,6 @@
       </c>
       <c r="F5">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet94.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -20960,20 +20970,20 @@
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C1" s="1">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="D1" s="1">
-        <v>2020</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="D2">
         <v>1</v>
       </c>
     </row>
@@ -20981,7 +20991,7 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>1</v>
       </c>
     </row>
@@ -20989,7 +20999,10 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D4">
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="C4">
         <v>1</v>
       </c>
     </row>
@@ -20998,13 +21011,13 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -21014,7 +21027,7 @@
 
 <file path=xl/worksheets/sheet96.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -21028,7 +21041,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C1" s="1">
         <v>2017</v>
@@ -21041,16 +21054,13 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
+      <c r="B2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -21058,15 +21068,23 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
         <v>1</v>
       </c>
     </row>

--- a/output/cta-violent-crime-full-year.xlsx
+++ b/output/cta-violent-crime-full-year.xlsx
@@ -9,27 +9,27 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Austin" sheetId="3" r:id="rId3"/>
-    <sheet name="Roseland" sheetId="4" r:id="rId4"/>
-    <sheet name="Albany Park" sheetId="5" r:id="rId5"/>
-    <sheet name="Woodlawn" sheetId="6" r:id="rId6"/>
-    <sheet name="North Lawndale" sheetId="7" r:id="rId7"/>
-    <sheet name="South Shore" sheetId="8" r:id="rId8"/>
-    <sheet name="Old Town" sheetId="9" r:id="rId9"/>
-    <sheet name="Loop" sheetId="10" r:id="rId10"/>
-    <sheet name="O'Hare" sheetId="11" r:id="rId11"/>
-    <sheet name="Near South Side" sheetId="12" r:id="rId12"/>
-    <sheet name="Grand Crossing" sheetId="13" r:id="rId13"/>
-    <sheet name="Avondale" sheetId="14" r:id="rId14"/>
-    <sheet name="Rush &amp; Division" sheetId="15" r:id="rId15"/>
-    <sheet name="Oakland" sheetId="16" r:id="rId16"/>
-    <sheet name="Chatham" sheetId="17" r:id="rId17"/>
-    <sheet name="New City" sheetId="18" r:id="rId18"/>
-    <sheet name="Belmont Cragin" sheetId="19" r:id="rId19"/>
-    <sheet name="West Loop" sheetId="20" r:id="rId20"/>
-    <sheet name="Uptown" sheetId="21" r:id="rId21"/>
-    <sheet name="Hegewisch" sheetId="22" r:id="rId22"/>
-    <sheet name="Lake View" sheetId="23" r:id="rId23"/>
+    <sheet name="Lake View" sheetId="3" r:id="rId3"/>
+    <sheet name="Austin" sheetId="4" r:id="rId4"/>
+    <sheet name="Roseland" sheetId="5" r:id="rId5"/>
+    <sheet name="Albany Park" sheetId="6" r:id="rId6"/>
+    <sheet name="Woodlawn" sheetId="7" r:id="rId7"/>
+    <sheet name="North Lawndale" sheetId="8" r:id="rId8"/>
+    <sheet name="South Shore" sheetId="9" r:id="rId9"/>
+    <sheet name="Old Town" sheetId="10" r:id="rId10"/>
+    <sheet name="Loop" sheetId="11" r:id="rId11"/>
+    <sheet name="O'Hare" sheetId="12" r:id="rId12"/>
+    <sheet name="Near South Side" sheetId="13" r:id="rId13"/>
+    <sheet name="Grand Crossing" sheetId="14" r:id="rId14"/>
+    <sheet name="Avondale" sheetId="15" r:id="rId15"/>
+    <sheet name="Rush &amp; Division" sheetId="16" r:id="rId16"/>
+    <sheet name="Oakland" sheetId="17" r:id="rId17"/>
+    <sheet name="Chatham" sheetId="18" r:id="rId18"/>
+    <sheet name="New City" sheetId="19" r:id="rId19"/>
+    <sheet name="Belmont Cragin" sheetId="20" r:id="rId20"/>
+    <sheet name="West Loop" sheetId="21" r:id="rId21"/>
+    <sheet name="Uptown" sheetId="22" r:id="rId22"/>
+    <sheet name="Hegewisch" sheetId="23" r:id="rId23"/>
     <sheet name="Grand Boulevard" sheetId="24" r:id="rId24"/>
     <sheet name="West Town" sheetId="25" r:id="rId25"/>
     <sheet name="Englewood" sheetId="26" r:id="rId26"/>
@@ -1050,7 +1050,7 @@
         <v>467</v>
       </c>
       <c r="M6">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1091,7 +1091,7 @@
         <v>896</v>
       </c>
       <c r="M7">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
   </sheetData>
@@ -1100,6 +1100,223 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>6</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>17</v>
+      </c>
+      <c r="F5">
+        <v>18</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>12</v>
+      </c>
+      <c r="I5">
+        <v>17</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>17</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>19</v>
+      </c>
+      <c r="F6">
+        <v>24</v>
+      </c>
+      <c r="G6">
+        <v>15</v>
+      </c>
+      <c r="H6">
+        <v>17</v>
+      </c>
+      <c r="I6">
+        <v>19</v>
+      </c>
+      <c r="J6">
+        <v>14</v>
+      </c>
+      <c r="K6">
+        <v>24</v>
+      </c>
+      <c r="L6">
+        <v>10</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1384,7 +1601,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1580,231 +1797,6 @@
       </c>
       <c r="L7">
         <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>7</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>6</v>
-      </c>
-      <c r="E7">
-        <v>7</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="G7">
-        <v>8</v>
-      </c>
-      <c r="H7">
-        <v>9</v>
-      </c>
-      <c r="I7">
-        <v>13</v>
-      </c>
-      <c r="J7">
-        <v>8</v>
-      </c>
-      <c r="K7">
-        <v>8</v>
-      </c>
-      <c r="L7">
-        <v>4</v>
-      </c>
-      <c r="M7">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1877,41 +1869,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>7</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
       <c r="F2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1919,56 +1896,41 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>17</v>
-      </c>
-      <c r="L3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
       <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -1976,19 +1938,7 @@
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
       <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -1997,40 +1947,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2038,40 +1988,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F7">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="G7">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="H7">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="J7">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="M7">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2081,7 +2031,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -2145,144 +2095,200 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
       <c r="E3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="K3">
+        <v>17</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="K4">
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
       <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>42</v>
+      </c>
+      <c r="D7">
+        <v>36</v>
+      </c>
+      <c r="E7">
+        <v>38</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>28</v>
+      </c>
+      <c r="H7">
+        <v>39</v>
+      </c>
+      <c r="I7">
+        <v>39</v>
+      </c>
+      <c r="J7">
+        <v>47</v>
+      </c>
+      <c r="K7">
+        <v>74</v>
+      </c>
+      <c r="L7">
+        <v>63</v>
+      </c>
+      <c r="M7">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -2356,67 +2362,64 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
       </c>
       <c r="L3">
         <v>2</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M4">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -2425,40 +2428,37 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5">
         <v>3</v>
       </c>
       <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2466,40 +2466,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2508,6 +2508,223 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>14</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>16</v>
+      </c>
+      <c r="H6">
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <v>14</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>7</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2601,7 +2818,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2853,7 +3070,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3030,164 +3247,6 @@
       </c>
       <c r="L5">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4740,7 +4799,7 @@
         <v>20</v>
       </c>
       <c r="M47">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -6555,7 +6614,7 @@
         <v>896</v>
       </c>
       <c r="M98">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
   </sheetData>
@@ -6664,6 +6723,164 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6899,7 +7116,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7134,7 +7351,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7205,253 +7422,6 @@
       </c>
       <c r="E5">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>6</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>11</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>14</v>
-      </c>
-      <c r="D5">
-        <v>12</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-      <c r="F5">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>11</v>
-      </c>
-      <c r="H5">
-        <v>17</v>
-      </c>
-      <c r="I5">
-        <v>20</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>10</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>23</v>
-      </c>
-      <c r="D6">
-        <v>14</v>
-      </c>
-      <c r="E6">
-        <v>18</v>
-      </c>
-      <c r="F6">
-        <v>18</v>
-      </c>
-      <c r="G6">
-        <v>19</v>
-      </c>
-      <c r="H6">
-        <v>27</v>
-      </c>
-      <c r="I6">
-        <v>26</v>
-      </c>
-      <c r="J6">
-        <v>16</v>
-      </c>
-      <c r="K6">
-        <v>24</v>
-      </c>
-      <c r="L6">
-        <v>20</v>
-      </c>
-      <c r="M6">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -8806,7 +8776,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -8869,41 +8839,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
       <c r="C2">
         <v>4</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -8911,59 +8878,59 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
         <v>7</v>
       </c>
-      <c r="F3">
-        <v>6</v>
-      </c>
-      <c r="G3">
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>11</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
         <v>7</v>
       </c>
-      <c r="H3">
-        <v>8</v>
-      </c>
-      <c r="I3">
-        <v>6</v>
-      </c>
-      <c r="J3">
-        <v>10</v>
-      </c>
-      <c r="K3">
-        <v>12</v>
-      </c>
-      <c r="L3">
-        <v>14</v>
-      </c>
       <c r="M3">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
       </c>
       <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
         <v>2</v>
       </c>
       <c r="M4">
@@ -8972,92 +8939,81 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>14</v>
+      </c>
+      <c r="D5">
+        <v>12</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>11</v>
+      </c>
+      <c r="H5">
+        <v>17</v>
+      </c>
+      <c r="I5">
+        <v>20</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
         <v>23</v>
       </c>
-      <c r="C6">
-        <v>31</v>
-      </c>
       <c r="D6">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E6">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="F6">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="G6">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H6">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="I6">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="J6">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K6">
         <v>24</v>
       </c>
       <c r="L6">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="M6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>32</v>
-      </c>
-      <c r="C7">
-        <v>40</v>
-      </c>
-      <c r="D7">
-        <v>32</v>
-      </c>
-      <c r="E7">
-        <v>57</v>
-      </c>
-      <c r="F7">
-        <v>53</v>
-      </c>
-      <c r="G7">
-        <v>34</v>
-      </c>
-      <c r="H7">
-        <v>63</v>
-      </c>
-      <c r="I7">
-        <v>44</v>
-      </c>
-      <c r="J7">
-        <v>47</v>
-      </c>
-      <c r="K7">
-        <v>46</v>
-      </c>
-      <c r="L7">
-        <v>33</v>
-      </c>
-      <c r="M7">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -11386,40 +11342,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2">
         <v>4</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>3</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>8</v>
+      </c>
+      <c r="K2">
         <v>7</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
       <c r="L2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -11427,73 +11383,70 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
         <v>7</v>
       </c>
-      <c r="G3">
-        <v>6</v>
-      </c>
       <c r="H3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J3">
+        <v>10</v>
+      </c>
+      <c r="K3">
+        <v>12</v>
+      </c>
+      <c r="L3">
         <v>14</v>
       </c>
-      <c r="K3">
-        <v>7</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
       <c r="M3">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D5">
+      <c r="K5">
         <v>1</v>
       </c>
     </row>
@@ -11502,40 +11455,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C6">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D6">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E6">
+        <v>44</v>
+      </c>
+      <c r="F6">
+        <v>38</v>
+      </c>
+      <c r="G6">
+        <v>24</v>
+      </c>
+      <c r="H6">
+        <v>50</v>
+      </c>
+      <c r="I6">
+        <v>34</v>
+      </c>
+      <c r="J6">
+        <v>26</v>
+      </c>
+      <c r="K6">
+        <v>24</v>
+      </c>
+      <c r="L6">
         <v>14</v>
       </c>
-      <c r="F6">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>14</v>
-      </c>
-      <c r="H6">
-        <v>19</v>
-      </c>
-      <c r="I6">
-        <v>29</v>
-      </c>
-      <c r="J6">
-        <v>19</v>
-      </c>
-      <c r="K6">
-        <v>20</v>
-      </c>
-      <c r="L6">
-        <v>26</v>
-      </c>
       <c r="M6">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -11543,40 +11496,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D7">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E7">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="G7">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="H7">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="I7">
+        <v>44</v>
+      </c>
+      <c r="J7">
         <v>47</v>
       </c>
-      <c r="J7">
-        <v>35</v>
-      </c>
       <c r="K7">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="L7">
+        <v>33</v>
+      </c>
+      <c r="M7">
         <v>37</v>
-      </c>
-      <c r="M7">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -13473,7 +13426,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -13488,9 +13441,10 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13513,158 +13467,220 @@
         <v>2020</v>
       </c>
       <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
         <v>2022</v>
       </c>
-      <c r="I1" s="1">
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="J1" s="1">
+      <c r="K1" s="1">
         <v>2024</v>
       </c>
-      <c r="K1" s="1">
+      <c r="L1" s="1">
         <v>2025</v>
       </c>
-      <c r="L1" s="1">
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>7</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="J3">
+        <v>14</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>2</v>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>26</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>26</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>16</v>
+      </c>
+      <c r="E7">
+        <v>23</v>
+      </c>
+      <c r="F7">
+        <v>23</v>
+      </c>
+      <c r="G7">
+        <v>24</v>
+      </c>
+      <c r="H7">
+        <v>31</v>
+      </c>
+      <c r="I7">
+        <v>47</v>
+      </c>
+      <c r="J7">
+        <v>35</v>
+      </c>
+      <c r="K7">
+        <v>31</v>
+      </c>
+      <c r="L7">
+        <v>37</v>
+      </c>
+      <c r="M7">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -15179,7 +15195,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -15194,10 +15210,9 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -15220,173 +15235,158 @@
         <v>2020</v>
       </c>
       <c r="H1" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I1" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J1" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K1" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
         <v>2</v>
       </c>
       <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>5</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
         <v>9</v>
       </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
-      <c r="K5">
+      <c r="J6">
         <v>7</v>
       </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>16</v>
-      </c>
-      <c r="C6">
-        <v>13</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>11</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>11</v>
-      </c>
-      <c r="J6">
-        <v>11</v>
-      </c>
       <c r="K6">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L6">
         <v>5</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -17278,40 +17278,22 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
       <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17319,47 +17301,44 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G3">
         <v>3</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J3">
         <v>5</v>
       </c>
       <c r="K3">
-        <v>6</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
       <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
         <v>1</v>
       </c>
     </row>
@@ -17368,40 +17347,40 @@
         <v>5</v>
       </c>
       <c r="B5">
+        <v>11</v>
+      </c>
+      <c r="C5">
         <v>12</v>
       </c>
-      <c r="C5">
-        <v>21</v>
-      </c>
       <c r="D5">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -17409,40 +17388,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="E6">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="H6">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J6">
+        <v>11</v>
+      </c>
+      <c r="K6">
         <v>12</v>
       </c>
-      <c r="K6">
-        <v>18</v>
-      </c>
       <c r="L6">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -18991,10 +18970,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -19055,10 +19034,10 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -19070,10 +19049,10 @@
         <v>2</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -19082,13 +19061,13 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -19096,37 +19075,34 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M3">
         <v>3</v>
@@ -19134,83 +19110,94 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>11</v>
-      </c>
-      <c r="C4">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <v>6</v>
-      </c>
-      <c r="E4">
-        <v>7</v>
-      </c>
-      <c r="F4">
-        <v>7</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>12</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>21</v>
+      </c>
+      <c r="D5">
+        <v>28</v>
+      </c>
+      <c r="E5">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>35</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
         <v>15</v>
       </c>
-      <c r="C5">
-        <v>15</v>
-      </c>
-      <c r="D5">
-        <v>12</v>
-      </c>
-      <c r="E5">
-        <v>11</v>
-      </c>
-      <c r="F5">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>9</v>
-      </c>
-      <c r="H5">
-        <v>11</v>
-      </c>
-      <c r="I5">
-        <v>12</v>
-      </c>
       <c r="J5">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <v>9</v>
       </c>
       <c r="L5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>14</v>
+      </c>
+      <c r="C6">
+        <v>26</v>
+      </c>
+      <c r="D6">
+        <v>29</v>
+      </c>
+      <c r="E6">
+        <v>24</v>
+      </c>
+      <c r="F6">
+        <v>42</v>
+      </c>
+      <c r="G6">
+        <v>18</v>
+      </c>
+      <c r="H6">
+        <v>18</v>
+      </c>
+      <c r="I6">
+        <v>21</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+      <c r="K6">
+        <v>18</v>
+      </c>
+      <c r="L6">
+        <v>18</v>
+      </c>
+      <c r="M6">
         <v>8</v>
       </c>
     </row>
@@ -20360,10 +20347,10 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -20423,26 +20410,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>2</v>
+      </c>
+      <c r="M2">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -20450,124 +20452,122 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4">
+        <v>7</v>
+      </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C5">
+        <v>15</v>
+      </c>
+      <c r="D5">
+        <v>12</v>
+      </c>
+      <c r="E5">
         <v>11</v>
       </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>17</v>
-      </c>
       <c r="F5">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5">
+        <v>11</v>
+      </c>
+      <c r="I5">
         <v>12</v>
       </c>
-      <c r="H5">
-        <v>12</v>
-      </c>
-      <c r="I5">
-        <v>17</v>
-      </c>
       <c r="J5">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K5">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>11</v>
-      </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
-      <c r="E6">
-        <v>19</v>
-      </c>
-      <c r="F6">
-        <v>24</v>
-      </c>
-      <c r="G6">
-        <v>15</v>
-      </c>
-      <c r="H6">
-        <v>17</v>
-      </c>
-      <c r="I6">
-        <v>19</v>
-      </c>
-      <c r="J6">
-        <v>14</v>
-      </c>
-      <c r="K6">
-        <v>24</v>
-      </c>
-      <c r="L6">
-        <v>10</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-full-year.xlsx
+++ b/output/cta-violent-crime-full-year.xlsx
@@ -9,65 +9,65 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Lake View" sheetId="3" r:id="rId3"/>
-    <sheet name="Austin" sheetId="4" r:id="rId4"/>
-    <sheet name="Roseland" sheetId="5" r:id="rId5"/>
-    <sheet name="Albany Park" sheetId="6" r:id="rId6"/>
-    <sheet name="Woodlawn" sheetId="7" r:id="rId7"/>
-    <sheet name="North Lawndale" sheetId="8" r:id="rId8"/>
-    <sheet name="South Shore" sheetId="9" r:id="rId9"/>
-    <sheet name="Old Town" sheetId="10" r:id="rId10"/>
-    <sheet name="Loop" sheetId="11" r:id="rId11"/>
-    <sheet name="O'Hare" sheetId="12" r:id="rId12"/>
-    <sheet name="Near South Side" sheetId="13" r:id="rId13"/>
-    <sheet name="Grand Crossing" sheetId="14" r:id="rId14"/>
-    <sheet name="Avondale" sheetId="15" r:id="rId15"/>
-    <sheet name="Rush &amp; Division" sheetId="16" r:id="rId16"/>
-    <sheet name="Oakland" sheetId="17" r:id="rId17"/>
-    <sheet name="Chatham" sheetId="18" r:id="rId18"/>
-    <sheet name="New City" sheetId="19" r:id="rId19"/>
-    <sheet name="Belmont Cragin" sheetId="20" r:id="rId20"/>
-    <sheet name="West Loop" sheetId="21" r:id="rId21"/>
-    <sheet name="Uptown" sheetId="22" r:id="rId22"/>
-    <sheet name="Hegewisch" sheetId="23" r:id="rId23"/>
-    <sheet name="Grand Boulevard" sheetId="24" r:id="rId24"/>
-    <sheet name="West Town" sheetId="25" r:id="rId25"/>
-    <sheet name="Englewood" sheetId="26" r:id="rId26"/>
-    <sheet name="Greektown" sheetId="27" r:id="rId27"/>
-    <sheet name="Edgewater" sheetId="28" r:id="rId28"/>
-    <sheet name="Little Italy, UIC" sheetId="29" r:id="rId29"/>
-    <sheet name="Gage Park" sheetId="30" r:id="rId30"/>
-    <sheet name="Humboldt Park" sheetId="31" r:id="rId31"/>
-    <sheet name="Lower West Side" sheetId="32" r:id="rId32"/>
-    <sheet name="Sheffield &amp; DePaul" sheetId="33" r:id="rId33"/>
-    <sheet name="Norwood Park" sheetId="34" r:id="rId34"/>
-    <sheet name="Garfield Park" sheetId="35" r:id="rId35"/>
-    <sheet name="Wrigleyville" sheetId="36" r:id="rId36"/>
-    <sheet name="Auburn Gresham" sheetId="37" r:id="rId37"/>
-    <sheet name="Rogers Park" sheetId="38" r:id="rId38"/>
-    <sheet name="Washington Park" sheetId="39" r:id="rId39"/>
-    <sheet name="Chicago Lawn" sheetId="40" r:id="rId40"/>
-    <sheet name="Kenwood" sheetId="41" r:id="rId41"/>
-    <sheet name="Calumet Heights" sheetId="42" r:id="rId42"/>
-    <sheet name="Hyde Park" sheetId="43" r:id="rId43"/>
-    <sheet name="Fuller Park" sheetId="44" r:id="rId44"/>
-    <sheet name="South Chicago" sheetId="45" r:id="rId45"/>
-    <sheet name="Armour Square" sheetId="46" r:id="rId46"/>
-    <sheet name="Douglas" sheetId="47" r:id="rId47"/>
-    <sheet name="United Center" sheetId="48" r:id="rId48"/>
-    <sheet name="Grant Park" sheetId="49" r:id="rId49"/>
-    <sheet name="Jefferson Park" sheetId="50" r:id="rId50"/>
-    <sheet name="Streeterville" sheetId="51" r:id="rId51"/>
-    <sheet name="Millenium Park" sheetId="52" r:id="rId52"/>
-    <sheet name="River North" sheetId="53" r:id="rId53"/>
-    <sheet name="Beverly" sheetId="54" r:id="rId54"/>
-    <sheet name="South Deering" sheetId="55" r:id="rId55"/>
-    <sheet name="West Elsdon" sheetId="56" r:id="rId56"/>
-    <sheet name="Pullman" sheetId="57" r:id="rId57"/>
-    <sheet name="West Pullman" sheetId="58" r:id="rId58"/>
-    <sheet name="Morgan Park" sheetId="59" r:id="rId59"/>
-    <sheet name="Wicker Park" sheetId="60" r:id="rId60"/>
-    <sheet name="Little Village" sheetId="61" r:id="rId61"/>
+    <sheet name="North Lawndale" sheetId="3" r:id="rId3"/>
+    <sheet name="Little Village" sheetId="4" r:id="rId4"/>
+    <sheet name="Lake View" sheetId="5" r:id="rId5"/>
+    <sheet name="Austin" sheetId="6" r:id="rId6"/>
+    <sheet name="Roseland" sheetId="7" r:id="rId7"/>
+    <sheet name="Albany Park" sheetId="8" r:id="rId8"/>
+    <sheet name="Woodlawn" sheetId="9" r:id="rId9"/>
+    <sheet name="South Shore" sheetId="10" r:id="rId10"/>
+    <sheet name="Old Town" sheetId="11" r:id="rId11"/>
+    <sheet name="Loop" sheetId="12" r:id="rId12"/>
+    <sheet name="O'Hare" sheetId="13" r:id="rId13"/>
+    <sheet name="Near South Side" sheetId="14" r:id="rId14"/>
+    <sheet name="Grand Crossing" sheetId="15" r:id="rId15"/>
+    <sheet name="Avondale" sheetId="16" r:id="rId16"/>
+    <sheet name="Rush &amp; Division" sheetId="17" r:id="rId17"/>
+    <sheet name="Oakland" sheetId="18" r:id="rId18"/>
+    <sheet name="Chatham" sheetId="19" r:id="rId19"/>
+    <sheet name="New City" sheetId="20" r:id="rId20"/>
+    <sheet name="Belmont Cragin" sheetId="21" r:id="rId21"/>
+    <sheet name="West Loop" sheetId="22" r:id="rId22"/>
+    <sheet name="Uptown" sheetId="23" r:id="rId23"/>
+    <sheet name="Hegewisch" sheetId="24" r:id="rId24"/>
+    <sheet name="Grand Boulevard" sheetId="25" r:id="rId25"/>
+    <sheet name="West Town" sheetId="26" r:id="rId26"/>
+    <sheet name="Englewood" sheetId="27" r:id="rId27"/>
+    <sheet name="Greektown" sheetId="28" r:id="rId28"/>
+    <sheet name="Edgewater" sheetId="29" r:id="rId29"/>
+    <sheet name="Little Italy, UIC" sheetId="30" r:id="rId30"/>
+    <sheet name="Gage Park" sheetId="31" r:id="rId31"/>
+    <sheet name="Humboldt Park" sheetId="32" r:id="rId32"/>
+    <sheet name="Lower West Side" sheetId="33" r:id="rId33"/>
+    <sheet name="Sheffield &amp; DePaul" sheetId="34" r:id="rId34"/>
+    <sheet name="Norwood Park" sheetId="35" r:id="rId35"/>
+    <sheet name="Garfield Park" sheetId="36" r:id="rId36"/>
+    <sheet name="Wrigleyville" sheetId="37" r:id="rId37"/>
+    <sheet name="Auburn Gresham" sheetId="38" r:id="rId38"/>
+    <sheet name="Rogers Park" sheetId="39" r:id="rId39"/>
+    <sheet name="Washington Park" sheetId="40" r:id="rId40"/>
+    <sheet name="Chicago Lawn" sheetId="41" r:id="rId41"/>
+    <sheet name="Kenwood" sheetId="42" r:id="rId42"/>
+    <sheet name="Calumet Heights" sheetId="43" r:id="rId43"/>
+    <sheet name="Hyde Park" sheetId="44" r:id="rId44"/>
+    <sheet name="Fuller Park" sheetId="45" r:id="rId45"/>
+    <sheet name="South Chicago" sheetId="46" r:id="rId46"/>
+    <sheet name="Armour Square" sheetId="47" r:id="rId47"/>
+    <sheet name="Douglas" sheetId="48" r:id="rId48"/>
+    <sheet name="United Center" sheetId="49" r:id="rId49"/>
+    <sheet name="Grant Park" sheetId="50" r:id="rId50"/>
+    <sheet name="Jefferson Park" sheetId="51" r:id="rId51"/>
+    <sheet name="Streeterville" sheetId="52" r:id="rId52"/>
+    <sheet name="Millenium Park" sheetId="53" r:id="rId53"/>
+    <sheet name="River North" sheetId="54" r:id="rId54"/>
+    <sheet name="Beverly" sheetId="55" r:id="rId55"/>
+    <sheet name="South Deering" sheetId="56" r:id="rId56"/>
+    <sheet name="West Elsdon" sheetId="57" r:id="rId57"/>
+    <sheet name="Pullman" sheetId="58" r:id="rId58"/>
+    <sheet name="West Pullman" sheetId="59" r:id="rId59"/>
+    <sheet name="Morgan Park" sheetId="60" r:id="rId60"/>
+    <sheet name="Wicker Park" sheetId="61" r:id="rId61"/>
     <sheet name="Irving Park" sheetId="62" r:id="rId62"/>
     <sheet name="Jackson Park" sheetId="63" r:id="rId63"/>
     <sheet name="Brighton Park" sheetId="64" r:id="rId64"/>
@@ -889,7 +889,7 @@
         <v>137</v>
       </c>
       <c r="M2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -930,7 +930,7 @@
         <v>262</v>
       </c>
       <c r="M3">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1091,7 +1091,7 @@
         <v>896</v>
       </c>
       <c r="M7">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
   </sheetData>
@@ -1100,6 +1100,236 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>6</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4">
+        <v>7</v>
+      </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>8</v>
+      </c>
+      <c r="J4">
+        <v>12</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>15</v>
+      </c>
+      <c r="D5">
+        <v>12</v>
+      </c>
+      <c r="E5">
+        <v>11</v>
+      </c>
+      <c r="F5">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5">
+        <v>11</v>
+      </c>
+      <c r="I5">
+        <v>12</v>
+      </c>
+      <c r="J5">
+        <v>15</v>
+      </c>
+      <c r="K5">
+        <v>9</v>
+      </c>
+      <c r="L5">
+        <v>9</v>
+      </c>
+      <c r="M5">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1316,7 +1546,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1601,7 +1831,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1797,231 +2027,6 @@
       </c>
       <c r="L7">
         <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>7</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>6</v>
-      </c>
-      <c r="E7">
-        <v>7</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="G7">
-        <v>8</v>
-      </c>
-      <c r="H7">
-        <v>9</v>
-      </c>
-      <c r="I7">
-        <v>13</v>
-      </c>
-      <c r="J7">
-        <v>8</v>
-      </c>
-      <c r="K7">
-        <v>8</v>
-      </c>
-      <c r="L7">
-        <v>4</v>
-      </c>
-      <c r="M7">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2094,41 +2099,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>7</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
       <c r="F2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2136,56 +2126,41 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>17</v>
-      </c>
-      <c r="L3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
       <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -2193,19 +2168,7 @@
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
       <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -2214,40 +2177,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2255,40 +2218,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F7">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="G7">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="H7">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="J7">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="M7">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2298,7 +2261,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -2362,144 +2325,200 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
       <c r="E3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="K3">
+        <v>17</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="K4">
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
       <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>42</v>
+      </c>
+      <c r="D7">
+        <v>36</v>
+      </c>
+      <c r="E7">
+        <v>38</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>28</v>
+      </c>
+      <c r="H7">
+        <v>39</v>
+      </c>
+      <c r="I7">
+        <v>39</v>
+      </c>
+      <c r="J7">
+        <v>47</v>
+      </c>
+      <c r="K7">
+        <v>74</v>
+      </c>
+      <c r="L7">
+        <v>63</v>
+      </c>
+      <c r="M7">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -2573,67 +2592,64 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
       </c>
       <c r="L3">
         <v>2</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M4">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -2642,40 +2658,37 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5">
         <v>3</v>
       </c>
       <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2683,40 +2696,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2725,6 +2738,223 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>14</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>16</v>
+      </c>
+      <c r="H6">
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <v>14</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>7</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2818,7 +3048,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3063,190 +3293,6 @@
       </c>
       <c r="M7">
         <v>12</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>6</v>
-      </c>
-      <c r="C4">
-        <v>6</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-      <c r="F4">
-        <v>4</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>8</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>10</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4960,7 +5006,7 @@
         <v>4</v>
       </c>
       <c r="M51">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -5429,7 +5475,7 @@
         <v>18</v>
       </c>
       <c r="M65">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -6614,7 +6660,7 @@
         <v>896</v>
       </c>
       <c r="M98">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
   </sheetData>
@@ -6723,6 +6769,190 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>10</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6879,7 +7109,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7116,7 +7346,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7351,7 +7581,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7429,7 +7659,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7646,7 +7876,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7875,7 +8105,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8139,7 +8369,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8309,226 +8539,6 @@
       </c>
       <c r="L6">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>12</v>
-      </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>16</v>
-      </c>
-      <c r="L5">
-        <v>8</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>13</v>
-      </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
-      </c>
-      <c r="K6">
-        <v>21</v>
-      </c>
-      <c r="L6">
-        <v>13</v>
-      </c>
-      <c r="M6">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -8602,19 +8612,19 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -8623,66 +8633,48 @@
         <v>5</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
       <c r="M4">
         <v>1</v>
       </c>
@@ -8692,40 +8684,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>12</v>
+      </c>
+      <c r="I5">
         <v>7</v>
       </c>
-      <c r="D5">
-        <v>11</v>
-      </c>
-      <c r="E5">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>25</v>
-      </c>
-      <c r="G5">
-        <v>15</v>
-      </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>9</v>
-      </c>
       <c r="J5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -8733,40 +8725,40 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
         <v>10</v>
       </c>
-      <c r="C6">
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>13</v>
+      </c>
+      <c r="I6">
+        <v>12</v>
+      </c>
+      <c r="J6">
         <v>10</v>
       </c>
-      <c r="D6">
-        <v>14</v>
-      </c>
-      <c r="E6">
-        <v>23</v>
-      </c>
-      <c r="F6">
-        <v>28</v>
-      </c>
-      <c r="G6">
-        <v>16</v>
-      </c>
-      <c r="H6">
-        <v>14</v>
-      </c>
-      <c r="I6">
-        <v>17</v>
-      </c>
-      <c r="J6">
-        <v>16</v>
-      </c>
       <c r="K6">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="L6">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -8839,38 +8831,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -8878,98 +8873,86 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3">
         <v>5</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L3">
         <v>7</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
       <c r="H4">
         <v>1</v>
       </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+      <c r="J4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B5">
+        <v>12</v>
+      </c>
       <c r="C5">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D5">
+        <v>28</v>
+      </c>
+      <c r="E5">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>35</v>
+      </c>
+      <c r="G5">
         <v>12</v>
       </c>
-      <c r="E5">
+      <c r="H5">
         <v>10</v>
       </c>
-      <c r="F5">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>11</v>
-      </c>
-      <c r="H5">
-        <v>17</v>
-      </c>
       <c r="I5">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M5">
         <v>3</v>
@@ -8980,40 +8963,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="E6">
+        <v>24</v>
+      </c>
+      <c r="F6">
+        <v>42</v>
+      </c>
+      <c r="G6">
         <v>18</v>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>18</v>
       </c>
-      <c r="G6">
-        <v>19</v>
-      </c>
-      <c r="H6">
-        <v>27</v>
-      </c>
       <c r="I6">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J6">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L6">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -9022,6 +9005,244 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>11</v>
+      </c>
+      <c r="E5">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>25</v>
+      </c>
+      <c r="G5">
+        <v>15</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5">
+        <v>11</v>
+      </c>
+      <c r="K5">
+        <v>18</v>
+      </c>
+      <c r="L5">
+        <v>11</v>
+      </c>
+      <c r="M5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>14</v>
+      </c>
+      <c r="E6">
+        <v>23</v>
+      </c>
+      <c r="F6">
+        <v>28</v>
+      </c>
+      <c r="G6">
+        <v>16</v>
+      </c>
+      <c r="H6">
+        <v>14</v>
+      </c>
+      <c r="I6">
+        <v>17</v>
+      </c>
+      <c r="J6">
+        <v>16</v>
+      </c>
+      <c r="K6">
+        <v>31</v>
+      </c>
+      <c r="L6">
+        <v>22</v>
+      </c>
+      <c r="M6">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9246,7 +9467,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9481,7 +9702,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9681,7 +9902,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9904,7 +10125,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10088,7 +10309,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10345,214 +10566,6 @@
       </c>
       <c r="M7">
         <v>27</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>3</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -10628,11 +10641,8 @@
       <c r="B2">
         <v>2</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>2</v>
@@ -10643,20 +10653,8 @@
       <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
       <c r="J2">
         <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -10666,42 +10664,39 @@
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
       <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
     </row>
@@ -10709,41 +10704,35 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>19</v>
-      </c>
       <c r="C5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -10751,40 +10740,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -10793,6 +10782,238 @@
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>19</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>12</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>7</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>16</v>
+      </c>
+      <c r="F6">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>10</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <v>9</v>
+      </c>
+      <c r="K6">
+        <v>10</v>
+      </c>
+      <c r="L6">
+        <v>6</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11047,7 +11268,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11112,70 +11333,46 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
+      <c r="B2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
       <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M3">
         <v>4</v>
@@ -11185,7 +11382,7 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L4">
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -11194,40 +11391,37 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -11235,301 +11429,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F6">
         <v>7</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>8</v>
-      </c>
-      <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>6</v>
-      </c>
-      <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>6</v>
-      </c>
-      <c r="G3">
-        <v>7</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
-      </c>
-      <c r="I3">
-        <v>6</v>
-      </c>
-      <c r="J3">
-        <v>10</v>
-      </c>
-      <c r="K3">
-        <v>12</v>
-      </c>
-      <c r="L3">
-        <v>14</v>
-      </c>
-      <c r="M3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>23</v>
-      </c>
-      <c r="C6">
-        <v>31</v>
-      </c>
-      <c r="D6">
-        <v>22</v>
-      </c>
-      <c r="E6">
-        <v>44</v>
-      </c>
-      <c r="F6">
-        <v>38</v>
-      </c>
-      <c r="G6">
-        <v>24</v>
-      </c>
-      <c r="H6">
-        <v>50</v>
-      </c>
-      <c r="I6">
-        <v>34</v>
-      </c>
-      <c r="J6">
-        <v>26</v>
-      </c>
-      <c r="K6">
-        <v>24</v>
-      </c>
-      <c r="L6">
-        <v>14</v>
-      </c>
-      <c r="M6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>32</v>
-      </c>
-      <c r="C7">
-        <v>40</v>
-      </c>
-      <c r="D7">
-        <v>32</v>
-      </c>
-      <c r="E7">
-        <v>57</v>
-      </c>
-      <c r="F7">
-        <v>53</v>
-      </c>
-      <c r="G7">
-        <v>34</v>
-      </c>
-      <c r="H7">
-        <v>63</v>
-      </c>
-      <c r="I7">
-        <v>44</v>
-      </c>
-      <c r="J7">
-        <v>47</v>
-      </c>
-      <c r="K7">
-        <v>46</v>
-      </c>
-      <c r="L7">
-        <v>33</v>
-      </c>
-      <c r="M7">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -11602,71 +11535,80 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
         <v>2</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
       <c r="L2">
         <v>1</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -11675,37 +11617,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>1</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -11713,40 +11658,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>10</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
+      </c>
+      <c r="I6">
+        <v>12</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
         <v>8</v>
       </c>
-      <c r="G6">
-        <v>13</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>6</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
       <c r="M6">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -11755,6 +11700,223 @@
 </file>
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>11</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>11</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>14</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>16</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>13</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11893,7 +12055,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12062,7 +12224,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12230,7 +12392,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12453,7 +12615,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12668,7 +12830,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12897,7 +13059,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13110,7 +13272,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13333,7 +13495,254 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>6</v>
+      </c>
+      <c r="L2">
+        <v>6</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>11</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>14</v>
+      </c>
+      <c r="D5">
+        <v>12</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>11</v>
+      </c>
+      <c r="H5">
+        <v>17</v>
+      </c>
+      <c r="I5">
+        <v>20</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>10</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>23</v>
+      </c>
+      <c r="D6">
+        <v>14</v>
+      </c>
+      <c r="E6">
+        <v>18</v>
+      </c>
+      <c r="F6">
+        <v>18</v>
+      </c>
+      <c r="G6">
+        <v>19</v>
+      </c>
+      <c r="H6">
+        <v>27</v>
+      </c>
+      <c r="I6">
+        <v>26</v>
+      </c>
+      <c r="J6">
+        <v>16</v>
+      </c>
+      <c r="K6">
+        <v>24</v>
+      </c>
+      <c r="L6">
+        <v>20</v>
+      </c>
+      <c r="M6">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13424,7 +13833,1356 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>9</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6">
+        <v>8</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="L3">
+        <v>8</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>13</v>
+      </c>
+      <c r="H5">
+        <v>11</v>
+      </c>
+      <c r="I5">
+        <v>14</v>
+      </c>
+      <c r="J5">
+        <v>12</v>
+      </c>
+      <c r="K5">
+        <v>9</v>
+      </c>
+      <c r="L5">
+        <v>6</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>12</v>
+      </c>
+      <c r="E6">
+        <v>7</v>
+      </c>
+      <c r="F6">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>15</v>
+      </c>
+      <c r="H6">
+        <v>15</v>
+      </c>
+      <c r="I6">
+        <v>21</v>
+      </c>
+      <c r="J6">
+        <v>21</v>
+      </c>
+      <c r="K6">
+        <v>15</v>
+      </c>
+      <c r="L6">
+        <v>14</v>
+      </c>
+      <c r="M6">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>5</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13490,40 +15248,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2">
         <v>4</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>3</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>8</v>
+      </c>
+      <c r="K2">
         <v>7</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
       <c r="L2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -13531,73 +15289,70 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
         <v>7</v>
       </c>
-      <c r="G3">
-        <v>6</v>
-      </c>
       <c r="H3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J3">
+        <v>10</v>
+      </c>
+      <c r="K3">
+        <v>12</v>
+      </c>
+      <c r="L3">
         <v>14</v>
       </c>
-      <c r="K3">
-        <v>7</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
       <c r="M3">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D5">
+      <c r="K5">
         <v>1</v>
       </c>
     </row>
@@ -13606,40 +15361,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C6">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D6">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E6">
+        <v>44</v>
+      </c>
+      <c r="F6">
+        <v>38</v>
+      </c>
+      <c r="G6">
+        <v>24</v>
+      </c>
+      <c r="H6">
+        <v>50</v>
+      </c>
+      <c r="I6">
+        <v>34</v>
+      </c>
+      <c r="J6">
+        <v>26</v>
+      </c>
+      <c r="K6">
+        <v>24</v>
+      </c>
+      <c r="L6">
         <v>14</v>
       </c>
-      <c r="F6">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>14</v>
-      </c>
-      <c r="H6">
-        <v>19</v>
-      </c>
-      <c r="I6">
-        <v>29</v>
-      </c>
-      <c r="J6">
-        <v>19</v>
-      </c>
-      <c r="K6">
-        <v>20</v>
-      </c>
-      <c r="L6">
-        <v>26</v>
-      </c>
       <c r="M6">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -13647,40 +15402,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D7">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E7">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="G7">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="H7">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="I7">
+        <v>44</v>
+      </c>
+      <c r="J7">
         <v>47</v>
       </c>
-      <c r="J7">
-        <v>35</v>
-      </c>
       <c r="K7">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="L7">
+        <v>33</v>
+      </c>
+      <c r="M7">
         <v>37</v>
-      </c>
-      <c r="M7">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -13688,1356 +15443,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>4</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>3</v>
-      </c>
-      <c r="M5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
-      <c r="H6">
-        <v>9</v>
-      </c>
-      <c r="I6">
-        <v>6</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
-      </c>
-      <c r="L6">
-        <v>8</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>4</v>
-      </c>
-      <c r="L3">
-        <v>8</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>13</v>
-      </c>
-      <c r="H5">
-        <v>11</v>
-      </c>
-      <c r="I5">
-        <v>14</v>
-      </c>
-      <c r="J5">
-        <v>12</v>
-      </c>
-      <c r="K5">
-        <v>9</v>
-      </c>
-      <c r="L5">
-        <v>6</v>
-      </c>
-      <c r="M5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-      <c r="D6">
-        <v>12</v>
-      </c>
-      <c r="E6">
-        <v>7</v>
-      </c>
-      <c r="F6">
-        <v>13</v>
-      </c>
-      <c r="G6">
-        <v>15</v>
-      </c>
-      <c r="H6">
-        <v>15</v>
-      </c>
-      <c r="I6">
-        <v>21</v>
-      </c>
-      <c r="J6">
-        <v>21</v>
-      </c>
-      <c r="K6">
-        <v>15</v>
-      </c>
-      <c r="L6">
-        <v>14</v>
-      </c>
-      <c r="M6">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>8</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>4</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>5</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>10</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15193,7 +15599,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15217,22 +15623,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D1" s="1">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E1" s="1">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="F1" s="1">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G1" s="1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H1" s="1">
         <v>2022</v>
@@ -15254,67 +15660,46 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
       <c r="L2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="G3">
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
         <v>2</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
       <c r="J4">
         <v>1</v>
       </c>
@@ -15324,31 +15709,31 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -15356,13 +15741,13 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -15371,403 +15756,21 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
         <v>4</v>
       </c>
     </row>
@@ -17214,7 +17217,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -17278,21 +17281,39 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
       </c>
       <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
         <v>1</v>
       </c>
     </row>
@@ -17301,127 +17322,156 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
         <v>5</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>11</v>
-      </c>
-      <c r="C5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>7</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
+        <v>19</v>
+      </c>
+      <c r="C6">
         <v>16</v>
       </c>
-      <c r="C6">
-        <v>13</v>
-      </c>
       <c r="D6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="J6">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="K6">
+        <v>20</v>
+      </c>
+      <c r="L6">
+        <v>26</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>26</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>16</v>
+      </c>
+      <c r="E7">
+        <v>23</v>
+      </c>
+      <c r="F7">
+        <v>23</v>
+      </c>
+      <c r="G7">
+        <v>24</v>
+      </c>
+      <c r="H7">
+        <v>31</v>
+      </c>
+      <c r="I7">
+        <v>47</v>
+      </c>
+      <c r="J7">
+        <v>35</v>
+      </c>
+      <c r="K7">
+        <v>31</v>
+      </c>
+      <c r="L7">
+        <v>37</v>
+      </c>
+      <c r="M7">
         <v>12</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -18970,7 +19020,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -18985,10 +19035,9 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -19011,66 +19060,51 @@
         <v>2020</v>
       </c>
       <c r="H1" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I1" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J1" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K1" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -19078,127 +19112,106 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>9</v>
+      </c>
+      <c r="J6">
         <v>7</v>
       </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>12</v>
-      </c>
-      <c r="C5">
-        <v>21</v>
-      </c>
-      <c r="D5">
-        <v>28</v>
-      </c>
-      <c r="E5">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>35</v>
-      </c>
-      <c r="G5">
-        <v>12</v>
-      </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>15</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>9</v>
-      </c>
-      <c r="L5">
-        <v>7</v>
-      </c>
-      <c r="M5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>14</v>
-      </c>
-      <c r="C6">
-        <v>26</v>
-      </c>
-      <c r="D6">
-        <v>29</v>
-      </c>
-      <c r="E6">
-        <v>24</v>
-      </c>
-      <c r="F6">
-        <v>42</v>
-      </c>
-      <c r="G6">
-        <v>18</v>
-      </c>
-      <c r="H6">
-        <v>18</v>
-      </c>
-      <c r="I6">
-        <v>21</v>
-      </c>
-      <c r="J6">
-        <v>12</v>
-      </c>
       <c r="K6">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>18</v>
-      </c>
-      <c r="M6">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -20347,10 +20360,10 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -20411,40 +20424,22 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
         <v>2</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
       <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -20455,119 +20450,124 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>5</v>
       </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
       <c r="F3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>4</v>
-      </c>
-      <c r="L3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>11</v>
-      </c>
-      <c r="C4">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <v>6</v>
-      </c>
-      <c r="E4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>7</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>8</v>
-      </c>
-      <c r="J4">
-        <v>12</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>7</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>11</v>
+      </c>
+      <c r="J6">
+        <v>11</v>
+      </c>
+      <c r="K6">
         <v>12</v>
       </c>
-      <c r="E5">
-        <v>11</v>
-      </c>
-      <c r="F5">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>9</v>
-      </c>
-      <c r="H5">
-        <v>11</v>
-      </c>
-      <c r="I5">
-        <v>12</v>
-      </c>
-      <c r="J5">
-        <v>15</v>
-      </c>
-      <c r="K5">
-        <v>9</v>
-      </c>
-      <c r="L5">
-        <v>9</v>
-      </c>
-      <c r="M5">
-        <v>8</v>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-full-year.xlsx
+++ b/output/cta-violent-crime-full-year.xlsx
@@ -9,33 +9,33 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Riverdale" sheetId="3" r:id="rId3"/>
-    <sheet name="Fuller Park" sheetId="4" r:id="rId4"/>
-    <sheet name="North Lawndale" sheetId="5" r:id="rId5"/>
-    <sheet name="Little Village" sheetId="6" r:id="rId6"/>
-    <sheet name="Lake View" sheetId="7" r:id="rId7"/>
-    <sheet name="Austin" sheetId="8" r:id="rId8"/>
-    <sheet name="Roseland" sheetId="9" r:id="rId9"/>
-    <sheet name="Albany Park" sheetId="10" r:id="rId10"/>
-    <sheet name="Woodlawn" sheetId="11" r:id="rId11"/>
-    <sheet name="South Shore" sheetId="12" r:id="rId12"/>
-    <sheet name="Old Town" sheetId="13" r:id="rId13"/>
-    <sheet name="Loop" sheetId="14" r:id="rId14"/>
-    <sheet name="O'Hare" sheetId="15" r:id="rId15"/>
-    <sheet name="Near South Side" sheetId="16" r:id="rId16"/>
-    <sheet name="Grand Crossing" sheetId="17" r:id="rId17"/>
-    <sheet name="Avondale" sheetId="18" r:id="rId18"/>
-    <sheet name="Rush &amp; Division" sheetId="19" r:id="rId19"/>
-    <sheet name="Oakland" sheetId="20" r:id="rId20"/>
-    <sheet name="Chatham" sheetId="21" r:id="rId21"/>
-    <sheet name="New City" sheetId="22" r:id="rId22"/>
-    <sheet name="Belmont Cragin" sheetId="23" r:id="rId23"/>
-    <sheet name="West Loop" sheetId="24" r:id="rId24"/>
-    <sheet name="Uptown" sheetId="25" r:id="rId25"/>
-    <sheet name="Hegewisch" sheetId="26" r:id="rId26"/>
-    <sheet name="Grand Boulevard" sheetId="27" r:id="rId27"/>
-    <sheet name="West Town" sheetId="28" r:id="rId28"/>
-    <sheet name="Englewood" sheetId="29" r:id="rId29"/>
+    <sheet name="Englewood" sheetId="3" r:id="rId3"/>
+    <sheet name="Uptown" sheetId="4" r:id="rId4"/>
+    <sheet name="Riverdale" sheetId="5" r:id="rId5"/>
+    <sheet name="Fuller Park" sheetId="6" r:id="rId6"/>
+    <sheet name="North Lawndale" sheetId="7" r:id="rId7"/>
+    <sheet name="Little Village" sheetId="8" r:id="rId8"/>
+    <sheet name="Lake View" sheetId="9" r:id="rId9"/>
+    <sheet name="Austin" sheetId="10" r:id="rId10"/>
+    <sheet name="Roseland" sheetId="11" r:id="rId11"/>
+    <sheet name="Albany Park" sheetId="12" r:id="rId12"/>
+    <sheet name="Woodlawn" sheetId="13" r:id="rId13"/>
+    <sheet name="South Shore" sheetId="14" r:id="rId14"/>
+    <sheet name="Old Town" sheetId="15" r:id="rId15"/>
+    <sheet name="Loop" sheetId="16" r:id="rId16"/>
+    <sheet name="O'Hare" sheetId="17" r:id="rId17"/>
+    <sheet name="Near South Side" sheetId="18" r:id="rId18"/>
+    <sheet name="Grand Crossing" sheetId="19" r:id="rId19"/>
+    <sheet name="Avondale" sheetId="20" r:id="rId20"/>
+    <sheet name="Rush &amp; Division" sheetId="21" r:id="rId21"/>
+    <sheet name="Oakland" sheetId="22" r:id="rId22"/>
+    <sheet name="Chatham" sheetId="23" r:id="rId23"/>
+    <sheet name="New City" sheetId="24" r:id="rId24"/>
+    <sheet name="Belmont Cragin" sheetId="25" r:id="rId25"/>
+    <sheet name="West Loop" sheetId="26" r:id="rId26"/>
+    <sheet name="Hegewisch" sheetId="27" r:id="rId27"/>
+    <sheet name="Grand Boulevard" sheetId="28" r:id="rId28"/>
+    <sheet name="West Town" sheetId="29" r:id="rId29"/>
     <sheet name="Greektown" sheetId="30" r:id="rId30"/>
     <sheet name="Edgewater" sheetId="31" r:id="rId31"/>
     <sheet name="Little Italy, UIC" sheetId="32" r:id="rId32"/>
@@ -889,7 +889,7 @@
         <v>137</v>
       </c>
       <c r="M2">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1050,7 +1050,7 @@
         <v>467</v>
       </c>
       <c r="M6">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1091,7 +1091,7 @@
         <v>896</v>
       </c>
       <c r="M7">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -1100,6 +1100,531 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>8</v>
+      </c>
+      <c r="K2">
+        <v>7</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>7</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>6</v>
+      </c>
+      <c r="J3">
+        <v>10</v>
+      </c>
+      <c r="K3">
+        <v>12</v>
+      </c>
+      <c r="L3">
+        <v>14</v>
+      </c>
+      <c r="M3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>23</v>
+      </c>
+      <c r="C6">
+        <v>31</v>
+      </c>
+      <c r="D6">
+        <v>22</v>
+      </c>
+      <c r="E6">
+        <v>44</v>
+      </c>
+      <c r="F6">
+        <v>38</v>
+      </c>
+      <c r="G6">
+        <v>24</v>
+      </c>
+      <c r="H6">
+        <v>50</v>
+      </c>
+      <c r="I6">
+        <v>34</v>
+      </c>
+      <c r="J6">
+        <v>26</v>
+      </c>
+      <c r="K6">
+        <v>24</v>
+      </c>
+      <c r="L6">
+        <v>14</v>
+      </c>
+      <c r="M6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>40</v>
+      </c>
+      <c r="D7">
+        <v>32</v>
+      </c>
+      <c r="E7">
+        <v>57</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>34</v>
+      </c>
+      <c r="H7">
+        <v>63</v>
+      </c>
+      <c r="I7">
+        <v>44</v>
+      </c>
+      <c r="J7">
+        <v>47</v>
+      </c>
+      <c r="K7">
+        <v>46</v>
+      </c>
+      <c r="L7">
+        <v>33</v>
+      </c>
+      <c r="M7">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>4</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
+      </c>
+      <c r="I2">
+        <v>7</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>7</v>
+      </c>
+      <c r="G3">
+        <v>6</v>
+      </c>
+      <c r="H3">
+        <v>6</v>
+      </c>
+      <c r="I3">
+        <v>9</v>
+      </c>
+      <c r="J3">
+        <v>14</v>
+      </c>
+      <c r="K3">
+        <v>7</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>19</v>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>11</v>
+      </c>
+      <c r="E6">
+        <v>14</v>
+      </c>
+      <c r="F6">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>14</v>
+      </c>
+      <c r="H6">
+        <v>19</v>
+      </c>
+      <c r="I6">
+        <v>29</v>
+      </c>
+      <c r="J6">
+        <v>19</v>
+      </c>
+      <c r="K6">
+        <v>20</v>
+      </c>
+      <c r="L6">
+        <v>26</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>26</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>16</v>
+      </c>
+      <c r="E7">
+        <v>23</v>
+      </c>
+      <c r="F7">
+        <v>23</v>
+      </c>
+      <c r="G7">
+        <v>24</v>
+      </c>
+      <c r="H7">
+        <v>31</v>
+      </c>
+      <c r="I7">
+        <v>47</v>
+      </c>
+      <c r="J7">
+        <v>35</v>
+      </c>
+      <c r="K7">
+        <v>31</v>
+      </c>
+      <c r="L7">
+        <v>37</v>
+      </c>
+      <c r="M7">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1293,453 +1818,6 @@
       </c>
       <c r="L6">
         <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>5</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>11</v>
-      </c>
-      <c r="C5">
-        <v>12</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>7</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>16</v>
-      </c>
-      <c r="C6">
-        <v>13</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>11</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>11</v>
-      </c>
-      <c r="J6">
-        <v>11</v>
-      </c>
-      <c r="K6">
-        <v>12</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>6</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>4</v>
-      </c>
-      <c r="L3">
-        <v>6</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>11</v>
-      </c>
-      <c r="C4">
-        <v>10</v>
-      </c>
-      <c r="D4">
-        <v>6</v>
-      </c>
-      <c r="E4">
-        <v>7</v>
-      </c>
-      <c r="F4">
-        <v>7</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>8</v>
-      </c>
-      <c r="J4">
-        <v>12</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>15</v>
-      </c>
-      <c r="C5">
-        <v>15</v>
-      </c>
-      <c r="D5">
-        <v>12</v>
-      </c>
-      <c r="E5">
-        <v>11</v>
-      </c>
-      <c r="F5">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>9</v>
-      </c>
-      <c r="H5">
-        <v>11</v>
-      </c>
-      <c r="I5">
-        <v>12</v>
-      </c>
-      <c r="J5">
-        <v>15</v>
-      </c>
-      <c r="K5">
-        <v>9</v>
-      </c>
-      <c r="L5">
-        <v>9</v>
-      </c>
-      <c r="M5">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1812,26 +1890,23 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="E2">
         <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>2</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>4</v>
+      <c r="I2">
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1839,41 +1914,44 @@
         <v>2</v>
       </c>
       <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J4">
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
@@ -1882,40 +1960,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="J5">
         <v>6</v>
       </c>
       <c r="K5">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1923,37 +2001,37 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
         <v>11</v>
       </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
-      <c r="E6">
-        <v>19</v>
-      </c>
       <c r="F6">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H6">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J6">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M6">
         <v>4</v>
@@ -1966,7 +2044,237 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>6</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>4</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4">
+        <v>7</v>
+      </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>8</v>
+      </c>
+      <c r="J4">
+        <v>12</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>15</v>
+      </c>
+      <c r="D5">
+        <v>12</v>
+      </c>
+      <c r="E5">
+        <v>11</v>
+      </c>
+      <c r="F5">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5">
+        <v>11</v>
+      </c>
+      <c r="I5">
+        <v>12</v>
+      </c>
+      <c r="J5">
+        <v>15</v>
+      </c>
+      <c r="K5">
+        <v>9</v>
+      </c>
+      <c r="L5">
+        <v>9</v>
+      </c>
+      <c r="M5">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -2029,40 +2337,25 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>6</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
       <c r="D2">
-        <v>12</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>13</v>
-      </c>
-      <c r="I2">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>15</v>
-      </c>
-      <c r="M2">
         <v>2</v>
       </c>
     </row>
@@ -2071,380 +2364,124 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>13</v>
-      </c>
-      <c r="C3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="K3">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>34</v>
-      </c>
-      <c r="M3">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>4</v>
-      </c>
       <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>5</v>
-      </c>
-      <c r="M4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>17</v>
+      </c>
+      <c r="F5">
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="I5">
+        <v>17</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>17</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="F6">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="H6">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="I6">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="J6">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="K6">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="L6">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>49</v>
-      </c>
-      <c r="C7">
-        <v>62</v>
-      </c>
-      <c r="D7">
-        <v>79</v>
-      </c>
-      <c r="E7">
-        <v>92</v>
-      </c>
-      <c r="F7">
-        <v>92</v>
-      </c>
-      <c r="G7">
-        <v>88</v>
-      </c>
-      <c r="H7">
-        <v>120</v>
-      </c>
-      <c r="I7">
-        <v>130</v>
-      </c>
-      <c r="J7">
-        <v>131</v>
-      </c>
-      <c r="K7">
-        <v>91</v>
-      </c>
-      <c r="L7">
-        <v>100</v>
-      </c>
-      <c r="M7">
-        <v>45</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-      <c r="H7">
-        <v>7</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>5</v>
-      </c>
-      <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2517,23 +2554,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
       <c r="F2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>15</v>
+      </c>
+      <c r="L2">
+        <v>15</v>
       </c>
       <c r="M2">
         <v>2</v>
@@ -2544,49 +2596,94 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>26</v>
+      </c>
+      <c r="L3">
+        <v>34</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>4</v>
+      </c>
       <c r="J4">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>5</v>
+      </c>
+      <c r="M4">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K5">
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -2595,40 +2692,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2636,40 +2733,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>92</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="G7">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>120</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>130</v>
       </c>
       <c r="J7">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="K7">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="L7">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="M7">
-        <v>7</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -2678,6 +2775,209 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>5</v>
+      </c>
+      <c r="K7">
+        <v>9</v>
+      </c>
+      <c r="L7">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2742,41 +3042,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>7</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
       <c r="F2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2784,56 +3069,41 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>17</v>
-      </c>
-      <c r="L3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
       <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -2841,19 +3111,7 @@
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
       <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -2862,40 +3120,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2903,40 +3161,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F7">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="G7">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="H7">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="J7">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="M7">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2944,9 +3202,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -3010,361 +3268,200 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
       <c r="E3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="K3">
+        <v>17</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="K4">
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
       <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="M6">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-      <c r="F5">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>14</v>
-      </c>
-      <c r="H5">
-        <v>7</v>
-      </c>
-      <c r="I5">
-        <v>9</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>3</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>11</v>
-      </c>
-      <c r="F6">
         <v>13</v>
       </c>
-      <c r="G6">
-        <v>16</v>
-      </c>
-      <c r="H6">
-        <v>11</v>
-      </c>
-      <c r="I6">
-        <v>14</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>7</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>42</v>
+      </c>
+      <c r="D7">
+        <v>36</v>
+      </c>
+      <c r="E7">
+        <v>38</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>28</v>
+      </c>
+      <c r="H7">
+        <v>39</v>
+      </c>
+      <c r="I7">
+        <v>39</v>
+      </c>
+      <c r="J7">
+        <v>47</v>
+      </c>
+      <c r="K7">
+        <v>74</v>
+      </c>
+      <c r="L7">
+        <v>63</v>
+      </c>
+      <c r="M7">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -4297,7 +4394,7 @@
         <v>71</v>
       </c>
       <c r="M28">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -6300,7 +6397,7 @@
         <v>13</v>
       </c>
       <c r="M86">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -6735,7 +6832,7 @@
         <v>896</v>
       </c>
       <c r="M98">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -6844,6 +6941,434 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>9</v>
+      </c>
+      <c r="K6">
+        <v>6</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>14</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>16</v>
+      </c>
+      <c r="H6">
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <v>14</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>7</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6936,7 +7461,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7188,7 +7713,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7372,7 +7897,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7530,7 +8055,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7767,7 +8292,302 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>9</v>
+      </c>
+      <c r="L6">
+        <v>12</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7833,40 +8653,34 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L2">
         <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -7877,41 +8691,41 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
         <v>7</v>
       </c>
-      <c r="K3">
-        <v>7</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
       <c r="M3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -7920,40 +8734,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="I5">
         <v>7</v>
       </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
       <c r="J5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -7961,40 +8775,40 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>12</v>
+      </c>
+      <c r="E6">
+        <v>12</v>
+      </c>
+      <c r="F6">
         <v>8</v>
       </c>
-      <c r="C6">
-        <v>14</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>11</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
       <c r="G6">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>10</v>
       </c>
       <c r="J6">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M6">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -8002,531 +8816,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>4</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>8</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>13</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>8</v>
-      </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>6</v>
-      </c>
-      <c r="J6">
-        <v>8</v>
-      </c>
-      <c r="K6">
-        <v>9</v>
-      </c>
-      <c r="L6">
-        <v>12</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>8</v>
-      </c>
-      <c r="E5">
-        <v>8</v>
-      </c>
-      <c r="F5">
-        <v>7</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>6</v>
-      </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>12</v>
-      </c>
-      <c r="E6">
-        <v>12</v>
-      </c>
-      <c r="F6">
-        <v>8</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>9</v>
-      </c>
-      <c r="L6">
-        <v>15</v>
-      </c>
-      <c r="M6">
-        <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8741,7 +9031,7 @@
         <v>44</v>
       </c>
       <c r="M6">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -8782,170 +9072,7 @@
         <v>71</v>
       </c>
       <c r="M7">
-        <v>26</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -11132,7 +11259,7 @@
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -11192,74 +11319,86 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
       <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
         <v>2</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3">
         <v>7</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
@@ -11268,40 +11407,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G5">
+        <v>14</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>11</v>
+      </c>
+      <c r="L5">
         <v>8</v>
       </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>9</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>22</v>
-      </c>
-      <c r="L5">
-        <v>22</v>
-      </c>
       <c r="M5">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -11312,37 +11451,37 @@
         <v>8</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>22</v>
+      </c>
+      <c r="H6">
         <v>14</v>
       </c>
-      <c r="G6">
+      <c r="I6">
         <v>10</v>
       </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
       <c r="J6">
+        <v>16</v>
+      </c>
+      <c r="K6">
+        <v>23</v>
+      </c>
+      <c r="L6">
         <v>13</v>
       </c>
-      <c r="K6">
-        <v>28</v>
-      </c>
-      <c r="L6">
-        <v>28</v>
-      </c>
       <c r="M6">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -13418,10 +13557,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -13433,10 +13572,9 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13459,194 +13597,120 @@
         <v>2020</v>
       </c>
       <c r="H1" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I1" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J1" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K1" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
       <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
       <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>7</v>
-      </c>
-      <c r="M5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>14</v>
-      </c>
-      <c r="C6">
-        <v>26</v>
-      </c>
-      <c r="D6">
-        <v>29</v>
-      </c>
-      <c r="E6">
-        <v>24</v>
-      </c>
-      <c r="F6">
-        <v>42</v>
-      </c>
-      <c r="G6">
-        <v>18</v>
-      </c>
-      <c r="H6">
-        <v>18</v>
-      </c>
-      <c r="I6">
-        <v>21</v>
-      </c>
-      <c r="J6">
-        <v>12</v>
-      </c>
-      <c r="K6">
-        <v>18</v>
-      </c>
-      <c r="L6">
-        <v>18</v>
-      </c>
-      <c r="M6">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -15137,7 +15201,7 @@
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -15197,17 +15261,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="G2">
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15215,10 +15288,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -15230,23 +15309,26 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="C4">
         <v>1</v>
       </c>
     </row>
@@ -15255,37 +15337,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -15293,40 +15378,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -17235,38 +17320,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>2</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17274,98 +17362,86 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3">
         <v>5</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L3">
         <v>7</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
       <c r="H4">
         <v>1</v>
       </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+      <c r="J4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B5">
+        <v>12</v>
+      </c>
       <c r="C5">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D5">
+        <v>28</v>
+      </c>
+      <c r="E5">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>35</v>
+      </c>
+      <c r="G5">
         <v>12</v>
       </c>
-      <c r="E5">
+      <c r="H5">
         <v>10</v>
       </c>
-      <c r="F5">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>11</v>
-      </c>
-      <c r="H5">
-        <v>17</v>
-      </c>
       <c r="I5">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M5">
         <v>3</v>
@@ -17376,40 +17452,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="E6">
+        <v>24</v>
+      </c>
+      <c r="F6">
+        <v>42</v>
+      </c>
+      <c r="G6">
         <v>18</v>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>18</v>
       </c>
-      <c r="G6">
-        <v>19</v>
-      </c>
-      <c r="H6">
-        <v>27</v>
-      </c>
       <c r="I6">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J6">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L6">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -18970,7 +19046,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -19034,40 +19110,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -19075,153 +19127,118 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>6</v>
-      </c>
-      <c r="E3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>10</v>
-      </c>
-      <c r="K3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
-      </c>
       <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
       </c>
       <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>32</v>
-      </c>
-      <c r="C7">
-        <v>40</v>
-      </c>
-      <c r="D7">
-        <v>32</v>
-      </c>
-      <c r="E7">
-        <v>57</v>
-      </c>
-      <c r="F7">
-        <v>53</v>
-      </c>
-      <c r="G7">
-        <v>34</v>
-      </c>
-      <c r="H7">
-        <v>63</v>
-      </c>
-      <c r="I7">
-        <v>44</v>
-      </c>
-      <c r="J7">
-        <v>47</v>
-      </c>
-      <c r="K7">
-        <v>46</v>
-      </c>
-      <c r="L7">
-        <v>33</v>
-      </c>
-      <c r="M7">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -20326,7 +20343,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -20389,41 +20406,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
       <c r="C2">
         <v>4</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>4</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -20431,34 +20445,34 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C3">
         <v>4</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
         <v>7</v>
       </c>
-      <c r="G3">
-        <v>6</v>
-      </c>
-      <c r="H3">
-        <v>6</v>
-      </c>
       <c r="I3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L3">
         <v>7</v>
@@ -20474,113 +20488,99 @@
       <c r="C4">
         <v>1</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>2</v>
-      </c>
-      <c r="J4">
         <v>1</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>14</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>11</v>
+      </c>
+      <c r="H5">
+        <v>17</v>
+      </c>
+      <c r="I5">
+        <v>20</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>10</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>23</v>
+      </c>
+      <c r="D6">
+        <v>14</v>
+      </c>
+      <c r="E6">
+        <v>18</v>
+      </c>
+      <c r="F6">
+        <v>18</v>
+      </c>
+      <c r="G6">
         <v>19</v>
       </c>
-      <c r="C6">
+      <c r="H6">
+        <v>27</v>
+      </c>
+      <c r="I6">
+        <v>26</v>
+      </c>
+      <c r="J6">
         <v>16</v>
       </c>
-      <c r="D6">
-        <v>11</v>
-      </c>
-      <c r="E6">
-        <v>14</v>
-      </c>
-      <c r="F6">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>14</v>
-      </c>
-      <c r="H6">
-        <v>19</v>
-      </c>
-      <c r="I6">
-        <v>29</v>
-      </c>
-      <c r="J6">
-        <v>19</v>
-      </c>
       <c r="K6">
+        <v>24</v>
+      </c>
+      <c r="L6">
         <v>20</v>
       </c>
-      <c r="L6">
-        <v>26</v>
-      </c>
       <c r="M6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>26</v>
-      </c>
-      <c r="C7">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>16</v>
-      </c>
-      <c r="E7">
-        <v>23</v>
-      </c>
-      <c r="F7">
-        <v>23</v>
-      </c>
-      <c r="G7">
-        <v>24</v>
-      </c>
-      <c r="H7">
-        <v>31</v>
-      </c>
-      <c r="I7">
-        <v>47</v>
-      </c>
-      <c r="J7">
-        <v>35</v>
-      </c>
-      <c r="K7">
-        <v>31</v>
-      </c>
-      <c r="L7">
-        <v>37</v>
-      </c>
-      <c r="M7">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-full-year.xlsx
+++ b/output/cta-violent-crime-full-year.xlsx
@@ -971,7 +971,7 @@
         <v>25</v>
       </c>
       <c r="M4">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1091,7 +1091,7 @@
         <v>896</v>
       </c>
       <c r="M7">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -2664,7 +2664,7 @@
         <v>5</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2766,7 +2766,7 @@
         <v>100</v>
       </c>
       <c r="M7">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -5257,7 +5257,7 @@
         <v>100</v>
       </c>
       <c r="M53">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -6832,7 +6832,7 @@
         <v>896</v>
       </c>
       <c r="M98">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-full-year.xlsx
+++ b/output/cta-violent-crime-full-year.xlsx
@@ -9,42 +9,42 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="North Lawndale" sheetId="3" r:id="rId3"/>
-    <sheet name="Englewood" sheetId="4" r:id="rId4"/>
-    <sheet name="Uptown" sheetId="5" r:id="rId5"/>
-    <sheet name="Riverdale" sheetId="6" r:id="rId6"/>
-    <sheet name="Fuller Park" sheetId="7" r:id="rId7"/>
-    <sheet name="Little Village" sheetId="8" r:id="rId8"/>
-    <sheet name="Lake View" sheetId="9" r:id="rId9"/>
-    <sheet name="Austin" sheetId="10" r:id="rId10"/>
-    <sheet name="Roseland" sheetId="11" r:id="rId11"/>
-    <sheet name="Albany Park" sheetId="12" r:id="rId12"/>
-    <sheet name="Woodlawn" sheetId="13" r:id="rId13"/>
-    <sheet name="South Shore" sheetId="14" r:id="rId14"/>
-    <sheet name="Old Town" sheetId="15" r:id="rId15"/>
-    <sheet name="Loop" sheetId="16" r:id="rId16"/>
-    <sheet name="O'Hare" sheetId="17" r:id="rId17"/>
-    <sheet name="Near South Side" sheetId="18" r:id="rId18"/>
-    <sheet name="Grand Crossing" sheetId="19" r:id="rId19"/>
-    <sheet name="Avondale" sheetId="20" r:id="rId20"/>
-    <sheet name="Rush &amp; Division" sheetId="21" r:id="rId21"/>
-    <sheet name="Oakland" sheetId="22" r:id="rId22"/>
-    <sheet name="Chatham" sheetId="23" r:id="rId23"/>
-    <sheet name="New City" sheetId="24" r:id="rId24"/>
-    <sheet name="Belmont Cragin" sheetId="25" r:id="rId25"/>
-    <sheet name="West Loop" sheetId="26" r:id="rId26"/>
-    <sheet name="Hegewisch" sheetId="27" r:id="rId27"/>
-    <sheet name="Grand Boulevard" sheetId="28" r:id="rId28"/>
-    <sheet name="West Town" sheetId="29" r:id="rId29"/>
-    <sheet name="Greektown" sheetId="30" r:id="rId30"/>
-    <sheet name="Edgewater" sheetId="31" r:id="rId31"/>
-    <sheet name="Little Italy, UIC" sheetId="32" r:id="rId32"/>
-    <sheet name="Gage Park" sheetId="33" r:id="rId33"/>
-    <sheet name="Humboldt Park" sheetId="34" r:id="rId34"/>
-    <sheet name="Lower West Side" sheetId="35" r:id="rId35"/>
-    <sheet name="Sheffield &amp; DePaul" sheetId="36" r:id="rId36"/>
-    <sheet name="Norwood Park" sheetId="37" r:id="rId37"/>
-    <sheet name="Garfield Park" sheetId="38" r:id="rId38"/>
+    <sheet name="Garfield Park" sheetId="3" r:id="rId3"/>
+    <sheet name="North Lawndale" sheetId="4" r:id="rId4"/>
+    <sheet name="Englewood" sheetId="5" r:id="rId5"/>
+    <sheet name="Uptown" sheetId="6" r:id="rId6"/>
+    <sheet name="Riverdale" sheetId="7" r:id="rId7"/>
+    <sheet name="Fuller Park" sheetId="8" r:id="rId8"/>
+    <sheet name="Little Village" sheetId="9" r:id="rId9"/>
+    <sheet name="Lake View" sheetId="10" r:id="rId10"/>
+    <sheet name="Austin" sheetId="11" r:id="rId11"/>
+    <sheet name="Roseland" sheetId="12" r:id="rId12"/>
+    <sheet name="Albany Park" sheetId="13" r:id="rId13"/>
+    <sheet name="Woodlawn" sheetId="14" r:id="rId14"/>
+    <sheet name="South Shore" sheetId="15" r:id="rId15"/>
+    <sheet name="Old Town" sheetId="16" r:id="rId16"/>
+    <sheet name="Loop" sheetId="17" r:id="rId17"/>
+    <sheet name="O'Hare" sheetId="18" r:id="rId18"/>
+    <sheet name="Near South Side" sheetId="19" r:id="rId19"/>
+    <sheet name="Grand Crossing" sheetId="20" r:id="rId20"/>
+    <sheet name="Avondale" sheetId="21" r:id="rId21"/>
+    <sheet name="Rush &amp; Division" sheetId="22" r:id="rId22"/>
+    <sheet name="Oakland" sheetId="23" r:id="rId23"/>
+    <sheet name="Chatham" sheetId="24" r:id="rId24"/>
+    <sheet name="New City" sheetId="25" r:id="rId25"/>
+    <sheet name="Belmont Cragin" sheetId="26" r:id="rId26"/>
+    <sheet name="West Loop" sheetId="27" r:id="rId27"/>
+    <sheet name="Hegewisch" sheetId="28" r:id="rId28"/>
+    <sheet name="Grand Boulevard" sheetId="29" r:id="rId29"/>
+    <sheet name="West Town" sheetId="30" r:id="rId30"/>
+    <sheet name="Greektown" sheetId="31" r:id="rId31"/>
+    <sheet name="Edgewater" sheetId="32" r:id="rId32"/>
+    <sheet name="Little Italy, UIC" sheetId="33" r:id="rId33"/>
+    <sheet name="Gage Park" sheetId="34" r:id="rId34"/>
+    <sheet name="Humboldt Park" sheetId="35" r:id="rId35"/>
+    <sheet name="Lower West Side" sheetId="36" r:id="rId36"/>
+    <sheet name="Sheffield &amp; DePaul" sheetId="37" r:id="rId37"/>
+    <sheet name="Norwood Park" sheetId="38" r:id="rId38"/>
     <sheet name="Wrigleyville" sheetId="39" r:id="rId39"/>
     <sheet name="Auburn Gresham" sheetId="40" r:id="rId40"/>
     <sheet name="Rogers Park" sheetId="41" r:id="rId41"/>
@@ -930,7 +930,7 @@
         <v>262</v>
       </c>
       <c r="M3">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1091,7 +1091,7 @@
         <v>896</v>
       </c>
       <c r="M7">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>
@@ -1101,7 +1101,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -1164,41 +1164,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
       <c r="C2">
         <v>4</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L2">
         <v>5</v>
       </c>
       <c r="M2">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1206,59 +1203,59 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
         <v>7</v>
       </c>
-      <c r="F3">
-        <v>6</v>
-      </c>
-      <c r="G3">
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>11</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
         <v>7</v>
       </c>
-      <c r="H3">
-        <v>8</v>
-      </c>
-      <c r="I3">
-        <v>6</v>
-      </c>
-      <c r="J3">
-        <v>10</v>
-      </c>
-      <c r="K3">
-        <v>12</v>
-      </c>
-      <c r="L3">
-        <v>14</v>
-      </c>
       <c r="M3">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
       </c>
       <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
         <v>2</v>
       </c>
       <c r="M4">
@@ -1267,92 +1264,81 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>14</v>
+      </c>
+      <c r="D5">
+        <v>12</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>11</v>
+      </c>
+      <c r="H5">
+        <v>17</v>
+      </c>
+      <c r="I5">
+        <v>20</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
         <v>23</v>
       </c>
-      <c r="C6">
-        <v>31</v>
-      </c>
       <c r="D6">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E6">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="F6">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="G6">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H6">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="I6">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="J6">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K6">
         <v>24</v>
       </c>
       <c r="L6">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="M6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>32</v>
-      </c>
-      <c r="C7">
-        <v>40</v>
-      </c>
-      <c r="D7">
-        <v>32</v>
-      </c>
-      <c r="E7">
-        <v>57</v>
-      </c>
-      <c r="F7">
-        <v>53</v>
-      </c>
-      <c r="G7">
-        <v>34</v>
-      </c>
-      <c r="H7">
-        <v>63</v>
-      </c>
-      <c r="I7">
-        <v>44</v>
-      </c>
-      <c r="J7">
-        <v>47</v>
-      </c>
-      <c r="K7">
-        <v>46</v>
-      </c>
-      <c r="L7">
-        <v>33</v>
-      </c>
-      <c r="M7">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1426,40 +1412,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2">
         <v>4</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>3</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>8</v>
+      </c>
+      <c r="K2">
         <v>7</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
       <c r="L2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1467,73 +1453,70 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
         <v>7</v>
       </c>
-      <c r="G3">
-        <v>6</v>
-      </c>
       <c r="H3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J3">
+        <v>10</v>
+      </c>
+      <c r="K3">
+        <v>12</v>
+      </c>
+      <c r="L3">
         <v>14</v>
       </c>
-      <c r="K3">
-        <v>7</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
       <c r="M3">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D5">
+      <c r="K5">
         <v>1</v>
       </c>
     </row>
@@ -1542,40 +1525,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C6">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D6">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E6">
+        <v>44</v>
+      </c>
+      <c r="F6">
+        <v>38</v>
+      </c>
+      <c r="G6">
+        <v>24</v>
+      </c>
+      <c r="H6">
+        <v>50</v>
+      </c>
+      <c r="I6">
+        <v>34</v>
+      </c>
+      <c r="J6">
+        <v>26</v>
+      </c>
+      <c r="K6">
+        <v>24</v>
+      </c>
+      <c r="L6">
         <v>14</v>
       </c>
-      <c r="F6">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>14</v>
-      </c>
-      <c r="H6">
-        <v>19</v>
-      </c>
-      <c r="I6">
-        <v>29</v>
-      </c>
-      <c r="J6">
-        <v>19</v>
-      </c>
-      <c r="K6">
-        <v>20</v>
-      </c>
-      <c r="L6">
-        <v>26</v>
-      </c>
       <c r="M6">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1583,40 +1566,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D7">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E7">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="G7">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="H7">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="I7">
+        <v>44</v>
+      </c>
+      <c r="J7">
         <v>47</v>
       </c>
-      <c r="J7">
-        <v>35</v>
-      </c>
       <c r="K7">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="L7">
+        <v>33</v>
+      </c>
+      <c r="M7">
         <v>37</v>
-      </c>
-      <c r="M7">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1625,6 +1608,270 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>4</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
+      </c>
+      <c r="I2">
+        <v>7</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>7</v>
+      </c>
+      <c r="G3">
+        <v>6</v>
+      </c>
+      <c r="H3">
+        <v>6</v>
+      </c>
+      <c r="I3">
+        <v>9</v>
+      </c>
+      <c r="J3">
+        <v>14</v>
+      </c>
+      <c r="K3">
+        <v>7</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>19</v>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>11</v>
+      </c>
+      <c r="E6">
+        <v>14</v>
+      </c>
+      <c r="F6">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>14</v>
+      </c>
+      <c r="H6">
+        <v>19</v>
+      </c>
+      <c r="I6">
+        <v>29</v>
+      </c>
+      <c r="J6">
+        <v>19</v>
+      </c>
+      <c r="K6">
+        <v>20</v>
+      </c>
+      <c r="L6">
+        <v>26</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>26</v>
+      </c>
+      <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>16</v>
+      </c>
+      <c r="E7">
+        <v>23</v>
+      </c>
+      <c r="F7">
+        <v>23</v>
+      </c>
+      <c r="G7">
+        <v>24</v>
+      </c>
+      <c r="H7">
+        <v>31</v>
+      </c>
+      <c r="I7">
+        <v>47</v>
+      </c>
+      <c r="J7">
+        <v>35</v>
+      </c>
+      <c r="K7">
+        <v>31</v>
+      </c>
+      <c r="L7">
+        <v>37</v>
+      </c>
+      <c r="M7">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1825,7 +2072,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2042,7 +2289,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2272,7 +2519,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2489,7 +2736,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2774,7 +3021,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2970,231 +3217,6 @@
       </c>
       <c r="L7">
         <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>7</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>6</v>
-      </c>
-      <c r="E7">
-        <v>7</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="G7">
-        <v>8</v>
-      </c>
-      <c r="H7">
-        <v>9</v>
-      </c>
-      <c r="I7">
-        <v>13</v>
-      </c>
-      <c r="J7">
-        <v>8</v>
-      </c>
-      <c r="K7">
-        <v>8</v>
-      </c>
-      <c r="L7">
-        <v>4</v>
-      </c>
-      <c r="M7">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3267,41 +3289,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>7</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
       <c r="F2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3309,56 +3316,41 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>17</v>
-      </c>
-      <c r="L3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
       <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -3366,19 +3358,7 @@
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
       <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -3387,40 +3367,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3428,40 +3408,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F7">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="G7">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="H7">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="J7">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="M7">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4534,7 +4514,7 @@
         <v>44</v>
       </c>
       <c r="M32">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -6832,7 +6812,7 @@
         <v>896</v>
       </c>
       <c r="M98">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>
@@ -6941,7 +6921,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -7005,144 +6985,200 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
       <c r="E3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="K3">
+        <v>17</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="K4">
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
       <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>42</v>
+      </c>
+      <c r="D7">
+        <v>36</v>
+      </c>
+      <c r="E7">
+        <v>38</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>28</v>
+      </c>
+      <c r="H7">
+        <v>39</v>
+      </c>
+      <c r="I7">
+        <v>39</v>
+      </c>
+      <c r="J7">
+        <v>47</v>
+      </c>
+      <c r="K7">
+        <v>74</v>
+      </c>
+      <c r="L7">
+        <v>63</v>
+      </c>
+      <c r="M7">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -7216,67 +7252,64 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
       </c>
       <c r="L3">
         <v>2</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M4">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -7285,40 +7318,37 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5">
         <v>3</v>
       </c>
       <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -7326,40 +7356,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -7368,6 +7398,223 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>14</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>16</v>
+      </c>
+      <c r="H6">
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <v>14</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>7</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7461,7 +7708,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7713,7 +7960,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7897,7 +8144,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8055,7 +8302,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8292,7 +8539,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8370,7 +8617,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8587,7 +8834,271 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>7</v>
+      </c>
+      <c r="E2">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>5</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>9</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>6</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>9</v>
+      </c>
+      <c r="J3">
+        <v>14</v>
+      </c>
+      <c r="K3">
+        <v>16</v>
+      </c>
+      <c r="L3">
+        <v>8</v>
+      </c>
+      <c r="M3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>35</v>
+      </c>
+      <c r="D6">
+        <v>34</v>
+      </c>
+      <c r="E6">
+        <v>56</v>
+      </c>
+      <c r="F6">
+        <v>54</v>
+      </c>
+      <c r="G6">
+        <v>37</v>
+      </c>
+      <c r="H6">
+        <v>39</v>
+      </c>
+      <c r="I6">
+        <v>32</v>
+      </c>
+      <c r="J6">
+        <v>34</v>
+      </c>
+      <c r="K6">
+        <v>27</v>
+      </c>
+      <c r="L6">
+        <v>31</v>
+      </c>
+      <c r="M6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>19</v>
+      </c>
+      <c r="C7">
+        <v>40</v>
+      </c>
+      <c r="D7">
+        <v>51</v>
+      </c>
+      <c r="E7">
+        <v>69</v>
+      </c>
+      <c r="F7">
+        <v>65</v>
+      </c>
+      <c r="G7">
+        <v>47</v>
+      </c>
+      <c r="H7">
+        <v>50</v>
+      </c>
+      <c r="I7">
+        <v>49</v>
+      </c>
+      <c r="J7">
+        <v>51</v>
+      </c>
+      <c r="K7">
+        <v>48</v>
+      </c>
+      <c r="L7">
+        <v>44</v>
+      </c>
+      <c r="M7">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8816,245 +9327,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>6</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>12</v>
-      </c>
-      <c r="C5">
-        <v>21</v>
-      </c>
-      <c r="D5">
-        <v>28</v>
-      </c>
-      <c r="E5">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>35</v>
-      </c>
-      <c r="G5">
-        <v>12</v>
-      </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>15</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>9</v>
-      </c>
-      <c r="L5">
-        <v>7</v>
-      </c>
-      <c r="M5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>14</v>
-      </c>
-      <c r="C6">
-        <v>26</v>
-      </c>
-      <c r="D6">
-        <v>29</v>
-      </c>
-      <c r="E6">
-        <v>24</v>
-      </c>
-      <c r="F6">
-        <v>42</v>
-      </c>
-      <c r="G6">
-        <v>18</v>
-      </c>
-      <c r="H6">
-        <v>18</v>
-      </c>
-      <c r="I6">
-        <v>21</v>
-      </c>
-      <c r="J6">
-        <v>12</v>
-      </c>
-      <c r="K6">
-        <v>18</v>
-      </c>
-      <c r="L6">
-        <v>18</v>
-      </c>
-      <c r="M6">
-        <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9224,226 +9497,6 @@
       </c>
       <c r="L6">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>12</v>
-      </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>16</v>
-      </c>
-      <c r="L5">
-        <v>8</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>13</v>
-      </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
-      </c>
-      <c r="K6">
-        <v>21</v>
-      </c>
-      <c r="L6">
-        <v>13</v>
-      </c>
-      <c r="M6">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -9517,19 +9570,19 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -9538,66 +9591,48 @@
         <v>5</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
       <c r="M4">
         <v>1</v>
       </c>
@@ -9607,40 +9642,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>12</v>
+      </c>
+      <c r="I5">
         <v>7</v>
       </c>
-      <c r="D5">
-        <v>11</v>
-      </c>
-      <c r="E5">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>25</v>
-      </c>
-      <c r="G5">
-        <v>15</v>
-      </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>9</v>
-      </c>
       <c r="J5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -9648,40 +9683,40 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
         <v>10</v>
       </c>
-      <c r="C6">
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>13</v>
+      </c>
+      <c r="I6">
+        <v>12</v>
+      </c>
+      <c r="J6">
         <v>10</v>
       </c>
-      <c r="D6">
-        <v>14</v>
-      </c>
-      <c r="E6">
-        <v>23</v>
-      </c>
-      <c r="F6">
-        <v>28</v>
-      </c>
-      <c r="G6">
-        <v>16</v>
-      </c>
-      <c r="H6">
-        <v>14</v>
-      </c>
-      <c r="I6">
-        <v>17</v>
-      </c>
-      <c r="J6">
-        <v>16</v>
-      </c>
       <c r="K6">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="L6">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -9690,6 +9725,244 @@
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>11</v>
+      </c>
+      <c r="E5">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>25</v>
+      </c>
+      <c r="G5">
+        <v>15</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5">
+        <v>11</v>
+      </c>
+      <c r="K5">
+        <v>18</v>
+      </c>
+      <c r="L5">
+        <v>11</v>
+      </c>
+      <c r="M5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>14</v>
+      </c>
+      <c r="E6">
+        <v>23</v>
+      </c>
+      <c r="F6">
+        <v>28</v>
+      </c>
+      <c r="G6">
+        <v>16</v>
+      </c>
+      <c r="H6">
+        <v>14</v>
+      </c>
+      <c r="I6">
+        <v>17</v>
+      </c>
+      <c r="J6">
+        <v>16</v>
+      </c>
+      <c r="K6">
+        <v>31</v>
+      </c>
+      <c r="L6">
+        <v>22</v>
+      </c>
+      <c r="M6">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9914,7 +10187,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10149,7 +10422,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10349,7 +10622,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10572,7 +10845,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10749,270 +11022,6 @@
       </c>
       <c r="K7">
         <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>7</v>
-      </c>
-      <c r="E2">
-        <v>8</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>5</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>9</v>
-      </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>6</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
-      </c>
-      <c r="I3">
-        <v>9</v>
-      </c>
-      <c r="J3">
-        <v>14</v>
-      </c>
-      <c r="K3">
-        <v>16</v>
-      </c>
-      <c r="L3">
-        <v>8</v>
-      </c>
-      <c r="M3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>35</v>
-      </c>
-      <c r="D6">
-        <v>34</v>
-      </c>
-      <c r="E6">
-        <v>56</v>
-      </c>
-      <c r="F6">
-        <v>54</v>
-      </c>
-      <c r="G6">
-        <v>37</v>
-      </c>
-      <c r="H6">
-        <v>39</v>
-      </c>
-      <c r="I6">
-        <v>32</v>
-      </c>
-      <c r="J6">
-        <v>34</v>
-      </c>
-      <c r="K6">
-        <v>27</v>
-      </c>
-      <c r="L6">
-        <v>31</v>
-      </c>
-      <c r="M6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>19</v>
-      </c>
-      <c r="C7">
-        <v>40</v>
-      </c>
-      <c r="D7">
-        <v>51</v>
-      </c>
-      <c r="E7">
-        <v>69</v>
-      </c>
-      <c r="F7">
-        <v>65</v>
-      </c>
-      <c r="G7">
-        <v>47</v>
-      </c>
-      <c r="H7">
-        <v>50</v>
-      </c>
-      <c r="I7">
-        <v>49</v>
-      </c>
-      <c r="J7">
-        <v>51</v>
-      </c>
-      <c r="K7">
-        <v>48</v>
-      </c>
-      <c r="L7">
-        <v>44</v>
-      </c>
-      <c r="M7">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -11230,7 +11239,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -11293,38 +11302,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <v>3</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -11332,159 +11344,130 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>6</v>
+      </c>
+      <c r="L3">
         <v>7</v>
       </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>12</v>
-      </c>
-      <c r="K3">
-        <v>20</v>
-      </c>
-      <c r="L3">
-        <v>20</v>
-      </c>
       <c r="M3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
       <c r="H4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>21</v>
+      </c>
+      <c r="D5">
+        <v>28</v>
+      </c>
+      <c r="E5">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>35</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>9</v>
+      </c>
+      <c r="L5">
+        <v>7</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F6">
         <v>42</v>
       </c>
       <c r="G6">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H6">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="I6">
         <v>21</v>
       </c>
       <c r="J6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K6">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="L6">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="M6">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>40</v>
-      </c>
-      <c r="C7">
-        <v>51</v>
-      </c>
-      <c r="D7">
-        <v>50</v>
-      </c>
-      <c r="E7">
-        <v>33</v>
-      </c>
-      <c r="F7">
-        <v>63</v>
-      </c>
-      <c r="G7">
-        <v>50</v>
-      </c>
-      <c r="H7">
-        <v>47</v>
-      </c>
-      <c r="I7">
-        <v>45</v>
-      </c>
-      <c r="J7">
-        <v>37</v>
-      </c>
-      <c r="K7">
-        <v>68</v>
-      </c>
-      <c r="L7">
-        <v>70</v>
-      </c>
-      <c r="M7">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -13560,7 +13543,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -13623,76 +13606,76 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
       <c r="C2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="M3">
         <v>5</v>
@@ -13705,87 +13688,116 @@
       <c r="B4">
         <v>1</v>
       </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>9</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>11</v>
-      </c>
-      <c r="L5">
-        <v>8</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="G6">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H6">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="J6">
+        <v>15</v>
+      </c>
+      <c r="K6">
+        <v>44</v>
+      </c>
+      <c r="L6">
+        <v>43</v>
+      </c>
+      <c r="M6">
         <v>16</v>
       </c>
-      <c r="K6">
-        <v>23</v>
-      </c>
-      <c r="L6">
-        <v>13</v>
-      </c>
-      <c r="M6">
-        <v>9</v>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>40</v>
+      </c>
+      <c r="C7">
+        <v>51</v>
+      </c>
+      <c r="D7">
+        <v>50</v>
+      </c>
+      <c r="E7">
+        <v>33</v>
+      </c>
+      <c r="F7">
+        <v>63</v>
+      </c>
+      <c r="G7">
+        <v>50</v>
+      </c>
+      <c r="H7">
+        <v>47</v>
+      </c>
+      <c r="I7">
+        <v>45</v>
+      </c>
+      <c r="J7">
+        <v>37</v>
+      </c>
+      <c r="K7">
+        <v>68</v>
+      </c>
+      <c r="L7">
+        <v>70</v>
+      </c>
+      <c r="M7">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -15273,10 +15285,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -15288,9 +15300,10 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -15313,33 +15326,66 @@
         <v>2020</v>
       </c>
       <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
         <v>2022</v>
       </c>
-      <c r="I1" s="1">
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="J1" s="1">
+      <c r="K1" s="1">
         <v>2024</v>
       </c>
-      <c r="K1" s="1">
+      <c r="L1" s="1">
         <v>2025</v>
       </c>
-      <c r="L1" s="1">
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
       <c r="F2">
         <v>1</v>
       </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
       <c r="I2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -15347,86 +15393,124 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
+      </c>
+      <c r="K3">
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>4</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>22</v>
+      </c>
+      <c r="H6">
+        <v>14</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <v>16</v>
+      </c>
+      <c r="K6">
+        <v>23</v>
+      </c>
+      <c r="L6">
+        <v>13</v>
+      </c>
+      <c r="M6">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -17272,7 +17356,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -17287,10 +17371,9 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -17313,179 +17396,120 @@
         <v>2020</v>
       </c>
       <c r="H1" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="I1" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="J1" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="K1" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="H2">
+      <c r="F2">
         <v>1</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>4</v>
-      </c>
-      <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
-      </c>
-      <c r="K3">
-        <v>3</v>
-      </c>
       <c r="L3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <v>5</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>22</v>
-      </c>
-      <c r="M5">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>8</v>
-      </c>
-      <c r="D6">
-        <v>8</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>14</v>
-      </c>
-      <c r="G6">
-        <v>10</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
-      <c r="J6">
-        <v>13</v>
-      </c>
-      <c r="K6">
-        <v>28</v>
-      </c>
-      <c r="L6">
-        <v>28</v>
-      </c>
-      <c r="M6">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -19049,7 +19073,7 @@
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -19109,17 +19133,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="G2">
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -19127,10 +19160,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -19142,23 +19181,26 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="C4">
         <v>1</v>
       </c>
     </row>
@@ -19167,37 +19209,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -19205,40 +19250,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -20406,38 +20451,17 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -20445,37 +20469,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>11</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M3">
         <v>4</v>
@@ -20485,61 +20500,46 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
       <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
       <c r="C5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>17</v>
-      </c>
-      <c r="I5">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -20547,40 +20547,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-full-year.xlsx
+++ b/output/cta-violent-crime-full-year.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
     <sheet name="Garfield Park" sheetId="3" r:id="rId3"/>
-    <sheet name="North Lawndale" sheetId="4" r:id="rId4"/>
-    <sheet name="Englewood" sheetId="5" r:id="rId5"/>
+    <sheet name="Englewood" sheetId="4" r:id="rId4"/>
+    <sheet name="North Lawndale" sheetId="5" r:id="rId5"/>
     <sheet name="Uptown" sheetId="6" r:id="rId6"/>
     <sheet name="Riverdale" sheetId="7" r:id="rId7"/>
     <sheet name="Fuller Park" sheetId="8" r:id="rId8"/>
@@ -1050,7 +1050,7 @@
         <v>467</v>
       </c>
       <c r="M6">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1091,7 +1091,7 @@
         <v>896</v>
       </c>
       <c r="M7">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>
@@ -4374,7 +4374,7 @@
         <v>70</v>
       </c>
       <c r="M28">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -4514,7 +4514,7 @@
         <v>44</v>
       </c>
       <c r="M32">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -6812,7 +6812,7 @@
         <v>896</v>
       </c>
       <c r="M98">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>
@@ -9049,7 +9049,7 @@
         <v>31</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9090,7 +9090,7 @@
         <v>44</v>
       </c>
       <c r="M7">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -11239,7 +11239,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -11302,41 +11302,38 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K2">
         <v>3</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -11344,130 +11341,159 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4">
         <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>12</v>
-      </c>
-      <c r="C5">
-        <v>21</v>
-      </c>
-      <c r="D5">
-        <v>28</v>
-      </c>
-      <c r="E5">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>35</v>
-      </c>
-      <c r="G5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>15</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>9</v>
-      </c>
-      <c r="L5">
-        <v>7</v>
-      </c>
-      <c r="M5">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="C6">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E6">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F6">
         <v>42</v>
       </c>
       <c r="G6">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="H6">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I6">
         <v>21</v>
       </c>
       <c r="J6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K6">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="L6">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="M6">
-        <v>10</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>40</v>
+      </c>
+      <c r="C7">
+        <v>51</v>
+      </c>
+      <c r="D7">
+        <v>50</v>
+      </c>
+      <c r="E7">
+        <v>33</v>
+      </c>
+      <c r="F7">
+        <v>63</v>
+      </c>
+      <c r="G7">
+        <v>50</v>
+      </c>
+      <c r="H7">
+        <v>47</v>
+      </c>
+      <c r="I7">
+        <v>45</v>
+      </c>
+      <c r="J7">
+        <v>37</v>
+      </c>
+      <c r="K7">
+        <v>68</v>
+      </c>
+      <c r="L7">
+        <v>70</v>
+      </c>
+      <c r="M7">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -13543,7 +13569,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -13606,38 +13632,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <v>3</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -13645,159 +13674,130 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>6</v>
+      </c>
+      <c r="L3">
         <v>7</v>
       </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>12</v>
-      </c>
-      <c r="K3">
-        <v>20</v>
-      </c>
-      <c r="L3">
-        <v>20</v>
-      </c>
       <c r="M3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
       <c r="H4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>21</v>
+      </c>
+      <c r="D5">
+        <v>28</v>
+      </c>
+      <c r="E5">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>35</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>9</v>
+      </c>
+      <c r="L5">
+        <v>7</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F6">
         <v>42</v>
       </c>
       <c r="G6">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H6">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="I6">
         <v>21</v>
       </c>
       <c r="J6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K6">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="L6">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="M6">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>40</v>
-      </c>
-      <c r="C7">
-        <v>51</v>
-      </c>
-      <c r="D7">
-        <v>50</v>
-      </c>
-      <c r="E7">
-        <v>33</v>
-      </c>
-      <c r="F7">
-        <v>63</v>
-      </c>
-      <c r="G7">
-        <v>50</v>
-      </c>
-      <c r="H7">
-        <v>47</v>
-      </c>
-      <c r="I7">
-        <v>45</v>
-      </c>
-      <c r="J7">
-        <v>37</v>
-      </c>
-      <c r="K7">
-        <v>68</v>
-      </c>
-      <c r="L7">
-        <v>70</v>
-      </c>
-      <c r="M7">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-full-year.xlsx
+++ b/output/cta-violent-crime-full-year.xlsx
@@ -10,20 +10,20 @@
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
     <sheet name="West Town" sheetId="3" r:id="rId3"/>
-    <sheet name="Grand Boulevard" sheetId="4" r:id="rId4"/>
-    <sheet name="Avondale" sheetId="5" r:id="rId5"/>
-    <sheet name="Mount Greenwood" sheetId="6" r:id="rId6"/>
-    <sheet name="Grand Crossing" sheetId="7" r:id="rId7"/>
-    <sheet name="Englewood" sheetId="8" r:id="rId8"/>
-    <sheet name="Washington Park" sheetId="9" r:id="rId9"/>
-    <sheet name="South Chicago" sheetId="10" r:id="rId10"/>
-    <sheet name="Humboldt Park" sheetId="11" r:id="rId11"/>
-    <sheet name="Garfield Park" sheetId="12" r:id="rId12"/>
-    <sheet name="Rush &amp; Division" sheetId="13" r:id="rId13"/>
-    <sheet name="Loop" sheetId="14" r:id="rId14"/>
-    <sheet name="United Center" sheetId="15" r:id="rId15"/>
-    <sheet name="Chatham" sheetId="16" r:id="rId16"/>
-    <sheet name="Ashburn" sheetId="17" r:id="rId17"/>
+    <sheet name="Ashburn" sheetId="4" r:id="rId4"/>
+    <sheet name="Grand Crossing" sheetId="5" r:id="rId5"/>
+    <sheet name="Englewood" sheetId="6" r:id="rId6"/>
+    <sheet name="Grand Boulevard" sheetId="7" r:id="rId7"/>
+    <sheet name="Avondale" sheetId="8" r:id="rId8"/>
+    <sheet name="Mount Greenwood" sheetId="9" r:id="rId9"/>
+    <sheet name="Washington Park" sheetId="10" r:id="rId10"/>
+    <sheet name="South Chicago" sheetId="11" r:id="rId11"/>
+    <sheet name="Humboldt Park" sheetId="12" r:id="rId12"/>
+    <sheet name="Garfield Park" sheetId="13" r:id="rId13"/>
+    <sheet name="Rush &amp; Division" sheetId="14" r:id="rId14"/>
+    <sheet name="Loop" sheetId="15" r:id="rId15"/>
+    <sheet name="United Center" sheetId="16" r:id="rId16"/>
+    <sheet name="Chatham" sheetId="17" r:id="rId17"/>
     <sheet name="South Shore" sheetId="18" r:id="rId18"/>
     <sheet name="Sheffield &amp; DePaul" sheetId="19" r:id="rId19"/>
     <sheet name="Lake View" sheetId="20" r:id="rId20"/>
@@ -889,7 +889,7 @@
         <v>137</v>
       </c>
       <c r="M2">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -930,7 +930,7 @@
         <v>262</v>
       </c>
       <c r="M3">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1091,7 +1091,7 @@
         <v>896</v>
       </c>
       <c r="M7">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
   </sheetData>
@@ -1100,6 +1100,235 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>7</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>8</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>11</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>10</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
+      </c>
+      <c r="I6">
+        <v>12</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>8</v>
+      </c>
+      <c r="M6">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1314,7 +1543,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1549,7 +1778,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1813,7 +2042,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2030,7 +2259,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2315,7 +2544,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2538,7 +2767,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2783,197 +3012,6 @@
       </c>
       <c r="M7">
         <v>12</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="G4">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>4</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
-      <c r="L4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>8</v>
-      </c>
-      <c r="J5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>9</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4359,7 +4397,7 @@
         <v>70</v>
       </c>
       <c r="M28">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -4612,7 +4650,7 @@
         <v>63</v>
       </c>
       <c r="M36">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -6797,7 +6835,7 @@
         <v>896</v>
       </c>
       <c r="M98">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
   </sheetData>
@@ -11607,7 +11645,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -11671,150 +11709,124 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="I2">
         <v>2</v>
       </c>
       <c r="L2">
         <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
       <c r="I3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
       </c>
       <c r="H4">
         <v>1</v>
+      </c>
+      <c r="I4">
+        <v>4</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
         <v>8</v>
       </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
       <c r="J5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
         <v>9</v>
       </c>
-      <c r="C6">
-        <v>13</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>8</v>
-      </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>6</v>
-      </c>
-      <c r="J6">
-        <v>8</v>
-      </c>
-      <c r="K6">
-        <v>9</v>
-      </c>
-      <c r="L6">
-        <v>12</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
+      <c r="M5">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -13745,7 +13757,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -13809,144 +13821,200 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
       <c r="E3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="K3">
+        <v>17</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="K4">
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
       <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>42</v>
+      </c>
+      <c r="D7">
+        <v>36</v>
+      </c>
+      <c r="E7">
+        <v>38</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>28</v>
+      </c>
+      <c r="H7">
+        <v>39</v>
+      </c>
+      <c r="I7">
+        <v>39</v>
+      </c>
+      <c r="J7">
+        <v>47</v>
+      </c>
+      <c r="K7">
+        <v>74</v>
+      </c>
+      <c r="L7">
+        <v>63</v>
+      </c>
+      <c r="M7">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -15546,60 +15614,261 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
         <v>2016</v>
       </c>
-      <c r="C1" s="1">
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
         <v>2022</v>
       </c>
-      <c r="D1" s="1">
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>7</v>
+      </c>
+      <c r="H2">
+        <v>11</v>
+      </c>
+      <c r="I2">
+        <v>10</v>
+      </c>
+      <c r="J2">
+        <v>9</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>6</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>18</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>12</v>
+      </c>
+      <c r="G3">
+        <v>11</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
+      </c>
+      <c r="J3">
+        <v>12</v>
+      </c>
+      <c r="K3">
+        <v>20</v>
+      </c>
+      <c r="L3">
+        <v>20</v>
+      </c>
+      <c r="M3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
       <c r="D4">
         <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>34</v>
+      </c>
+      <c r="C6">
+        <v>45</v>
+      </c>
+      <c r="D6">
+        <v>25</v>
+      </c>
+      <c r="E6">
+        <v>22</v>
+      </c>
+      <c r="F6">
+        <v>42</v>
+      </c>
+      <c r="G6">
+        <v>32</v>
+      </c>
+      <c r="H6">
+        <v>26</v>
+      </c>
+      <c r="I6">
+        <v>21</v>
+      </c>
+      <c r="J6">
+        <v>15</v>
+      </c>
+      <c r="K6">
+        <v>44</v>
+      </c>
+      <c r="L6">
+        <v>43</v>
+      </c>
+      <c r="M6">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>40</v>
+      </c>
+      <c r="C7">
+        <v>51</v>
+      </c>
+      <c r="D7">
+        <v>50</v>
+      </c>
+      <c r="E7">
+        <v>33</v>
+      </c>
+      <c r="F7">
+        <v>63</v>
+      </c>
+      <c r="G7">
+        <v>50</v>
+      </c>
+      <c r="H7">
+        <v>47</v>
+      </c>
+      <c r="I7">
+        <v>45</v>
+      </c>
+      <c r="J7">
+        <v>37</v>
+      </c>
+      <c r="K7">
+        <v>68</v>
+      </c>
+      <c r="L7">
+        <v>70</v>
+      </c>
+      <c r="M7">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -17332,10 +17601,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -17395,41 +17664,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>6</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -17437,159 +17694,121 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>8</v>
-      </c>
-      <c r="E3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>9</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="M4">
+        <v>4</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="G6">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H6">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="I6">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="M6">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>32</v>
-      </c>
-      <c r="C7">
-        <v>42</v>
-      </c>
-      <c r="D7">
-        <v>36</v>
-      </c>
-      <c r="E7">
-        <v>38</v>
-      </c>
-      <c r="F7">
-        <v>53</v>
-      </c>
-      <c r="G7">
-        <v>28</v>
-      </c>
-      <c r="H7">
-        <v>39</v>
-      </c>
-      <c r="I7">
-        <v>39</v>
-      </c>
-      <c r="J7">
-        <v>47</v>
-      </c>
-      <c r="K7">
-        <v>74</v>
-      </c>
-      <c r="L7">
-        <v>63</v>
-      </c>
-      <c r="M7">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -18960,7 +19179,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -19023,79 +19242,55 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>5</v>
-      </c>
-      <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>18</v>
-      </c>
       <c r="E3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>11</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
-      </c>
-      <c r="I3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>12</v>
-      </c>
-      <c r="K3">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -19105,116 +19300,87 @@
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
       <c r="K4">
         <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
         <v>4</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>40</v>
-      </c>
-      <c r="C7">
-        <v>51</v>
-      </c>
-      <c r="D7">
-        <v>50</v>
-      </c>
-      <c r="E7">
-        <v>33</v>
-      </c>
-      <c r="F7">
-        <v>63</v>
-      </c>
-      <c r="G7">
-        <v>50</v>
-      </c>
-      <c r="H7">
-        <v>47</v>
-      </c>
-      <c r="I7">
-        <v>45</v>
-      </c>
-      <c r="J7">
-        <v>37</v>
-      </c>
-      <c r="K7">
-        <v>68</v>
-      </c>
-      <c r="L7">
-        <v>70</v>
-      </c>
-      <c r="M7">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -20328,226 +20494,60 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>7</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>8</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>7</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <v>11</v>
-      </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>10</v>
-      </c>
-      <c r="H6">
-        <v>7</v>
-      </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
-      <c r="J6">
-        <v>12</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>8</v>
-      </c>
-      <c r="M6">
-        <v>9</v>
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-full-year.xlsx
+++ b/output/cta-violent-crime-full-year.xlsx
@@ -27,78 +27,78 @@
     <sheet name="Loop" sheetId="18" r:id="rId18"/>
     <sheet name="United Center" sheetId="19" r:id="rId19"/>
     <sheet name="Chatham" sheetId="20" r:id="rId20"/>
-    <sheet name="South Shore" sheetId="21" r:id="rId21"/>
-    <sheet name="Sheffield &amp; DePaul" sheetId="22" r:id="rId22"/>
-    <sheet name="Lake View" sheetId="23" r:id="rId23"/>
-    <sheet name="River North" sheetId="24" r:id="rId24"/>
-    <sheet name="Bridgeport" sheetId="25" r:id="rId25"/>
-    <sheet name="Roseland" sheetId="26" r:id="rId26"/>
-    <sheet name="Chinatown" sheetId="27" r:id="rId27"/>
-    <sheet name="Austin" sheetId="28" r:id="rId28"/>
-    <sheet name="Little Italy, UIC" sheetId="29" r:id="rId29"/>
-    <sheet name="North Lawndale" sheetId="30" r:id="rId30"/>
-    <sheet name="Armour Square" sheetId="31" r:id="rId31"/>
-    <sheet name="West Elsdon" sheetId="32" r:id="rId32"/>
-    <sheet name="Logan Square" sheetId="33" r:id="rId33"/>
-    <sheet name="Woodlawn" sheetId="34" r:id="rId34"/>
-    <sheet name="Douglas" sheetId="35" r:id="rId35"/>
-    <sheet name="Edgewater" sheetId="36" r:id="rId36"/>
-    <sheet name="Chicago Lawn" sheetId="37" r:id="rId37"/>
-    <sheet name="West Loop" sheetId="38" r:id="rId38"/>
-    <sheet name="South Deering" sheetId="39" r:id="rId39"/>
-    <sheet name="Rogers Park" sheetId="40" r:id="rId40"/>
-    <sheet name="Brighton Park" sheetId="41" r:id="rId41"/>
-    <sheet name="Irving Park" sheetId="42" r:id="rId42"/>
-    <sheet name="Near South Side" sheetId="43" r:id="rId43"/>
-    <sheet name="Riverdale" sheetId="44" r:id="rId44"/>
-    <sheet name="North Center" sheetId="45" r:id="rId45"/>
-    <sheet name="Norwood Park" sheetId="46" r:id="rId46"/>
-    <sheet name="O'Hare" sheetId="47" r:id="rId47"/>
-    <sheet name="Little Village" sheetId="48" r:id="rId48"/>
-    <sheet name="Fuller Park" sheetId="49" r:id="rId49"/>
-    <sheet name="Lincoln Square" sheetId="50" r:id="rId50"/>
-    <sheet name="Greektown" sheetId="51" r:id="rId51"/>
-    <sheet name="Clearing" sheetId="52" r:id="rId52"/>
-    <sheet name="Boystown" sheetId="53" r:id="rId53"/>
-    <sheet name="Uptown" sheetId="54" r:id="rId54"/>
-    <sheet name="Auburn Gresham" sheetId="55" r:id="rId55"/>
-    <sheet name="Bucktown" sheetId="56" r:id="rId56"/>
-    <sheet name="Hermosa" sheetId="57" r:id="rId57"/>
-    <sheet name="Millenium Park" sheetId="58" r:id="rId58"/>
-    <sheet name="Wrigleyville" sheetId="59" r:id="rId59"/>
-    <sheet name="Printers Row" sheetId="60" r:id="rId60"/>
-    <sheet name="Archer Heights" sheetId="61" r:id="rId61"/>
-    <sheet name="Lincoln Park" sheetId="62" r:id="rId62"/>
-    <sheet name="Ukrainian Village" sheetId="63" r:id="rId63"/>
-    <sheet name="Hyde Park" sheetId="64" r:id="rId64"/>
-    <sheet name="Calumet Heights" sheetId="65" r:id="rId65"/>
-    <sheet name="Jefferson Park" sheetId="66" r:id="rId66"/>
-    <sheet name="Wicker Park" sheetId="67" r:id="rId67"/>
-    <sheet name="Albany Park" sheetId="68" r:id="rId68"/>
-    <sheet name="Washington Heights" sheetId="69" r:id="rId69"/>
-    <sheet name="Pullman" sheetId="70" r:id="rId70"/>
-    <sheet name="Belmont Cragin" sheetId="71" r:id="rId71"/>
-    <sheet name="Mckinley Park" sheetId="72" r:id="rId72"/>
-    <sheet name="Kenwood" sheetId="73" r:id="rId73"/>
-    <sheet name="West Pullman" sheetId="74" r:id="rId74"/>
-    <sheet name="Jackson Park" sheetId="75" r:id="rId75"/>
-    <sheet name="Morgan Park" sheetId="76" r:id="rId76"/>
-    <sheet name="Beverly" sheetId="77" r:id="rId77"/>
-    <sheet name="Streeterville" sheetId="78" r:id="rId78"/>
-    <sheet name="Grant Park" sheetId="79" r:id="rId79"/>
-    <sheet name="Oakland" sheetId="80" r:id="rId80"/>
-    <sheet name="New City" sheetId="81" r:id="rId81"/>
-    <sheet name="Hegewisch" sheetId="82" r:id="rId82"/>
-    <sheet name="East Side" sheetId="83" r:id="rId83"/>
-    <sheet name="Avalon Park" sheetId="84" r:id="rId84"/>
-    <sheet name="Portage Park" sheetId="85" r:id="rId85"/>
-    <sheet name="North Park" sheetId="86" r:id="rId86"/>
-    <sheet name="Montclare" sheetId="87" r:id="rId87"/>
-    <sheet name="Garfield Ridge" sheetId="88" r:id="rId88"/>
-    <sheet name="Burnside" sheetId="89" r:id="rId89"/>
-    <sheet name="Dunning" sheetId="90" r:id="rId90"/>
-    <sheet name="Galewood" sheetId="91" r:id="rId91"/>
-    <sheet name="West Lawn" sheetId="92" r:id="rId92"/>
+    <sheet name="West Lawn" sheetId="21" r:id="rId21"/>
+    <sheet name="South Shore" sheetId="22" r:id="rId22"/>
+    <sheet name="Sheffield &amp; DePaul" sheetId="23" r:id="rId23"/>
+    <sheet name="Lake View" sheetId="24" r:id="rId24"/>
+    <sheet name="River North" sheetId="25" r:id="rId25"/>
+    <sheet name="Bridgeport" sheetId="26" r:id="rId26"/>
+    <sheet name="Roseland" sheetId="27" r:id="rId27"/>
+    <sheet name="Chinatown" sheetId="28" r:id="rId28"/>
+    <sheet name="Austin" sheetId="29" r:id="rId29"/>
+    <sheet name="Little Italy, UIC" sheetId="30" r:id="rId30"/>
+    <sheet name="North Lawndale" sheetId="31" r:id="rId31"/>
+    <sheet name="Armour Square" sheetId="32" r:id="rId32"/>
+    <sheet name="West Elsdon" sheetId="33" r:id="rId33"/>
+    <sheet name="Logan Square" sheetId="34" r:id="rId34"/>
+    <sheet name="Woodlawn" sheetId="35" r:id="rId35"/>
+    <sheet name="Douglas" sheetId="36" r:id="rId36"/>
+    <sheet name="Edgewater" sheetId="37" r:id="rId37"/>
+    <sheet name="Chicago Lawn" sheetId="38" r:id="rId38"/>
+    <sheet name="West Loop" sheetId="39" r:id="rId39"/>
+    <sheet name="South Deering" sheetId="40" r:id="rId40"/>
+    <sheet name="Rogers Park" sheetId="41" r:id="rId41"/>
+    <sheet name="Brighton Park" sheetId="42" r:id="rId42"/>
+    <sheet name="Irving Park" sheetId="43" r:id="rId43"/>
+    <sheet name="Near South Side" sheetId="44" r:id="rId44"/>
+    <sheet name="Riverdale" sheetId="45" r:id="rId45"/>
+    <sheet name="North Center" sheetId="46" r:id="rId46"/>
+    <sheet name="Norwood Park" sheetId="47" r:id="rId47"/>
+    <sheet name="O'Hare" sheetId="48" r:id="rId48"/>
+    <sheet name="Little Village" sheetId="49" r:id="rId49"/>
+    <sheet name="Fuller Park" sheetId="50" r:id="rId50"/>
+    <sheet name="Lincoln Square" sheetId="51" r:id="rId51"/>
+    <sheet name="Greektown" sheetId="52" r:id="rId52"/>
+    <sheet name="Clearing" sheetId="53" r:id="rId53"/>
+    <sheet name="Boystown" sheetId="54" r:id="rId54"/>
+    <sheet name="Uptown" sheetId="55" r:id="rId55"/>
+    <sheet name="Auburn Gresham" sheetId="56" r:id="rId56"/>
+    <sheet name="Bucktown" sheetId="57" r:id="rId57"/>
+    <sheet name="Hermosa" sheetId="58" r:id="rId58"/>
+    <sheet name="Millenium Park" sheetId="59" r:id="rId59"/>
+    <sheet name="Wrigleyville" sheetId="60" r:id="rId60"/>
+    <sheet name="Printers Row" sheetId="61" r:id="rId61"/>
+    <sheet name="Archer Heights" sheetId="62" r:id="rId62"/>
+    <sheet name="Lincoln Park" sheetId="63" r:id="rId63"/>
+    <sheet name="Ukrainian Village" sheetId="64" r:id="rId64"/>
+    <sheet name="Hyde Park" sheetId="65" r:id="rId65"/>
+    <sheet name="Calumet Heights" sheetId="66" r:id="rId66"/>
+    <sheet name="Jefferson Park" sheetId="67" r:id="rId67"/>
+    <sheet name="Wicker Park" sheetId="68" r:id="rId68"/>
+    <sheet name="Albany Park" sheetId="69" r:id="rId69"/>
+    <sheet name="Washington Heights" sheetId="70" r:id="rId70"/>
+    <sheet name="Pullman" sheetId="71" r:id="rId71"/>
+    <sheet name="Belmont Cragin" sheetId="72" r:id="rId72"/>
+    <sheet name="Mckinley Park" sheetId="73" r:id="rId73"/>
+    <sheet name="Kenwood" sheetId="74" r:id="rId74"/>
+    <sheet name="West Pullman" sheetId="75" r:id="rId75"/>
+    <sheet name="Jackson Park" sheetId="76" r:id="rId76"/>
+    <sheet name="Morgan Park" sheetId="77" r:id="rId77"/>
+    <sheet name="Beverly" sheetId="78" r:id="rId78"/>
+    <sheet name="Streeterville" sheetId="79" r:id="rId79"/>
+    <sheet name="Grant Park" sheetId="80" r:id="rId80"/>
+    <sheet name="Oakland" sheetId="81" r:id="rId81"/>
+    <sheet name="New City" sheetId="82" r:id="rId82"/>
+    <sheet name="Hegewisch" sheetId="83" r:id="rId83"/>
+    <sheet name="East Side" sheetId="84" r:id="rId84"/>
+    <sheet name="Avalon Park" sheetId="85" r:id="rId85"/>
+    <sheet name="Portage Park" sheetId="86" r:id="rId86"/>
+    <sheet name="North Park" sheetId="87" r:id="rId87"/>
+    <sheet name="Montclare" sheetId="88" r:id="rId88"/>
+    <sheet name="Garfield Ridge" sheetId="89" r:id="rId89"/>
+    <sheet name="Burnside" sheetId="90" r:id="rId90"/>
+    <sheet name="Dunning" sheetId="91" r:id="rId91"/>
+    <sheet name="Galewood" sheetId="92" r:id="rId92"/>
     <sheet name="West Ridge" sheetId="93" r:id="rId93"/>
     <sheet name="East Village" sheetId="94" r:id="rId94"/>
     <sheet name="Gold Coast" sheetId="95" r:id="rId95"/>
@@ -930,7 +930,7 @@
         <v>262</v>
       </c>
       <c r="M3">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1091,7 +1091,7 @@
         <v>896</v>
       </c>
       <c r="M7">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>
@@ -6302,6 +6302,9 @@
       <c r="I90">
         <v>2</v>
       </c>
+      <c r="M90">
+        <v>1</v>
+      </c>
     </row>
     <row r="91" spans="1:13">
       <c r="A91" s="2" t="s">
@@ -6604,7 +6607,7 @@
         <v>896</v>
       </c>
       <c r="M98">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>
@@ -6965,6 +6968,87 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -7186,229 +7270,6 @@
       </c>
       <c r="M5">
         <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>6</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
-        <v>7</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>8</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>5</v>
-      </c>
-      <c r="L5">
-        <v>4</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>7</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6">
-        <v>9</v>
-      </c>
-      <c r="I6">
-        <v>15</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>8</v>
-      </c>
-      <c r="L6">
-        <v>12</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -7481,38 +7342,32 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -7522,60 +7377,39 @@
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
       <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
         <v>2</v>
       </c>
     </row>
@@ -7583,38 +7417,41 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
       <c r="C5">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G5">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -7622,40 +7459,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="I6">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="J6">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -7729,118 +7566,139 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2">
         <v>2</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
       <c r="C3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
       <c r="C5">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H5">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I5">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J5">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -7848,40 +7706,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F6">
+        <v>18</v>
+      </c>
+      <c r="G6">
+        <v>19</v>
+      </c>
+      <c r="H6">
+        <v>27</v>
+      </c>
+      <c r="I6">
+        <v>26</v>
+      </c>
+      <c r="J6">
+        <v>16</v>
+      </c>
+      <c r="K6">
+        <v>24</v>
+      </c>
+      <c r="L6">
+        <v>19</v>
+      </c>
+      <c r="M6">
         <v>13</v>
-      </c>
-      <c r="G6">
-        <v>15</v>
-      </c>
-      <c r="H6">
-        <v>15</v>
-      </c>
-      <c r="I6">
-        <v>21</v>
-      </c>
-      <c r="J6">
-        <v>21</v>
-      </c>
-      <c r="K6">
-        <v>15</v>
-      </c>
-      <c r="L6">
-        <v>14</v>
-      </c>
-      <c r="M6">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -7963,20 +7821,23 @@
       <c r="E2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K2">
         <v>2</v>
       </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
       <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -7984,25 +7845,43 @@
         <v>2</v>
       </c>
       <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="L3">
+        <v>8</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
       <c r="J4">
         <v>1</v>
       </c>
@@ -8012,27 +7891,39 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>14</v>
+      </c>
+      <c r="J5">
+        <v>12</v>
       </c>
       <c r="K5">
+        <v>9</v>
+      </c>
+      <c r="L5">
+        <v>6</v>
+      </c>
+      <c r="M5">
         <v>4</v>
       </c>
     </row>
@@ -8041,40 +7932,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="K6">
+        <v>15</v>
+      </c>
+      <c r="L6">
+        <v>14</v>
+      </c>
+      <c r="M6">
         <v>8</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -8084,7 +7975,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -8147,198 +8038,127 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
       <c r="C2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2">
-        <v>4</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>6</v>
-      </c>
-      <c r="I2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>5</v>
-      </c>
       <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>5</v>
-      </c>
-      <c r="F3">
-        <v>7</v>
-      </c>
-      <c r="G3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>9</v>
-      </c>
-      <c r="J3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>7</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
       <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
         <v>4</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>26</v>
-      </c>
-      <c r="C7">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>16</v>
-      </c>
-      <c r="E7">
-        <v>23</v>
-      </c>
-      <c r="F7">
-        <v>23</v>
-      </c>
-      <c r="G7">
-        <v>24</v>
-      </c>
-      <c r="H7">
-        <v>31</v>
-      </c>
-      <c r="I7">
-        <v>47</v>
-      </c>
-      <c r="J7">
-        <v>35</v>
-      </c>
-      <c r="K7">
-        <v>31</v>
-      </c>
-      <c r="L7">
-        <v>37</v>
-      </c>
-      <c r="M7">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -8411,26 +8231,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
       <c r="E2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="I2">
+        <v>7</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -8438,41 +8273,65 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
       </c>
       <c r="E3">
         <v>5</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
       <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -8480,7 +8339,7 @@
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F5">
+      <c r="D5">
         <v>1</v>
       </c>
     </row>
@@ -8489,40 +8348,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="K6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L6">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -8530,40 +8389,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G7">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H7">
+        <v>31</v>
+      </c>
+      <c r="I7">
+        <v>47</v>
+      </c>
+      <c r="J7">
+        <v>35</v>
+      </c>
+      <c r="K7">
+        <v>31</v>
+      </c>
+      <c r="L7">
+        <v>37</v>
+      </c>
+      <c r="M7">
         <v>12</v>
-      </c>
-      <c r="I7">
-        <v>17</v>
-      </c>
-      <c r="J7">
-        <v>9</v>
-      </c>
-      <c r="K7">
-        <v>26</v>
-      </c>
-      <c r="L7">
-        <v>23</v>
-      </c>
-      <c r="M7">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -8636,41 +8495,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
       <c r="E2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -8678,70 +8522,49 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I3">
         <v>6</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+      <c r="I4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K5">
+      <c r="F5">
         <v>1</v>
       </c>
     </row>
@@ -8750,40 +8573,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="D6">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="H6">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L6">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M6">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -8791,40 +8614,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="E7">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="G7">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="H7">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="I7">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="J7">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="L7">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="M7">
-        <v>37</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -8834,7 +8657,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -8897,32 +8720,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2">
         <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -8932,35 +8764,38 @@
       <c r="B3">
         <v>4</v>
       </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
       <c r="D3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8970,99 +8805,110 @@
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="H4">
-        <v>2</v>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
       </c>
       <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-      <c r="D5">
-        <v>11</v>
-      </c>
-      <c r="E5">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>25</v>
-      </c>
-      <c r="G5">
-        <v>15</v>
-      </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>9</v>
-      </c>
-      <c r="J5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>18</v>
-      </c>
-      <c r="L5">
-        <v>11</v>
-      </c>
-      <c r="M5">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D6">
+        <v>22</v>
+      </c>
+      <c r="E6">
+        <v>44</v>
+      </c>
+      <c r="F6">
+        <v>38</v>
+      </c>
+      <c r="G6">
+        <v>24</v>
+      </c>
+      <c r="H6">
+        <v>50</v>
+      </c>
+      <c r="I6">
+        <v>34</v>
+      </c>
+      <c r="J6">
+        <v>26</v>
+      </c>
+      <c r="K6">
+        <v>24</v>
+      </c>
+      <c r="L6">
         <v>14</v>
       </c>
-      <c r="E6">
-        <v>23</v>
-      </c>
-      <c r="F6">
-        <v>28</v>
-      </c>
-      <c r="G6">
-        <v>16</v>
-      </c>
-      <c r="H6">
-        <v>14</v>
-      </c>
-      <c r="I6">
-        <v>17</v>
-      </c>
-      <c r="J6">
-        <v>16</v>
-      </c>
-      <c r="K6">
-        <v>31</v>
-      </c>
-      <c r="L6">
-        <v>22</v>
-      </c>
       <c r="M6">
-        <v>14</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>40</v>
+      </c>
+      <c r="D7">
+        <v>32</v>
+      </c>
+      <c r="E7">
+        <v>57</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>34</v>
+      </c>
+      <c r="H7">
+        <v>63</v>
+      </c>
+      <c r="I7">
+        <v>44</v>
+      </c>
+      <c r="J7">
+        <v>47</v>
+      </c>
+      <c r="K7">
+        <v>46</v>
+      </c>
+      <c r="L7">
+        <v>33</v>
+      </c>
+      <c r="M7">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -9364,41 +9210,32 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
       <c r="F2">
         <v>2</v>
       </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L2">
         <v>4</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9406,47 +9243,56 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
         <v>2</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>4</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
       <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -9455,40 +9301,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E5">
         <v>21</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H5">
         <v>10</v>
       </c>
       <c r="I5">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K5">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="L5">
+        <v>11</v>
+      </c>
+      <c r="M5">
         <v>7</v>
-      </c>
-      <c r="M5">
-        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -9496,40 +9342,40 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
         <v>14</v>
       </c>
-      <c r="C6">
-        <v>26</v>
-      </c>
-      <c r="D6">
-        <v>29</v>
-      </c>
       <c r="E6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F6">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H6">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I6">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J6">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K6">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="L6">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="M6">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -9602,32 +9448,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9638,31 +9493,31 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M3">
         <v>3</v>
@@ -9672,10 +9527,10 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="M4">
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
@@ -9684,40 +9539,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="F5">
+        <v>35</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
         <v>15</v>
       </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>9</v>
+      </c>
+      <c r="L5">
         <v>7</v>
       </c>
-      <c r="I5">
-        <v>11</v>
-      </c>
-      <c r="J5">
-        <v>15</v>
-      </c>
-      <c r="K5">
-        <v>11</v>
-      </c>
-      <c r="L5">
-        <v>19</v>
-      </c>
       <c r="M5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -9725,40 +9580,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E6">
+        <v>24</v>
+      </c>
+      <c r="F6">
+        <v>42</v>
+      </c>
+      <c r="G6">
+        <v>18</v>
+      </c>
+      <c r="H6">
+        <v>18</v>
+      </c>
+      <c r="I6">
+        <v>21</v>
+      </c>
+      <c r="J6">
         <v>12</v>
       </c>
-      <c r="F6">
-        <v>19</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>15</v>
-      </c>
-      <c r="J6">
-        <v>21</v>
-      </c>
       <c r="K6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L6">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -9767,157 +9622,6 @@
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9988,29 +9692,35 @@
       <c r="D2">
         <v>2</v>
       </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
       <c r="C3">
         <v>1</v>
       </c>
@@ -10018,6 +9728,9 @@
         <v>1</v>
       </c>
       <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
         <v>1</v>
       </c>
       <c r="H3">
@@ -10027,29 +9740,26 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="L4">
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -10058,40 +9768,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J5">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L5">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -10099,39 +9809,190 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6">
         <v>7</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I6">
+        <v>15</v>
+      </c>
+      <c r="J6">
+        <v>21</v>
+      </c>
+      <c r="K6">
+        <v>16</v>
+      </c>
+      <c r="L6">
+        <v>28</v>
+      </c>
+      <c r="M6">
         <v>7</v>
       </c>
-      <c r="J6">
-        <v>15</v>
-      </c>
-      <c r="K6">
-        <v>10</v>
-      </c>
-      <c r="L6">
-        <v>14</v>
-      </c>
-      <c r="M6">
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
         <v>1</v>
       </c>
     </row>
@@ -10205,68 +10066,74 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
       </c>
       <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -10275,40 +10142,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K5">
         <v>7</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -10316,40 +10183,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
         <v>10</v>
       </c>
-      <c r="E6">
-        <v>11</v>
-      </c>
-      <c r="F6">
+      <c r="I6">
         <v>7</v>
       </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>11</v>
-      </c>
       <c r="J6">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -10358,6 +10225,223 @@
 </file>
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>5</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>11</v>
+      </c>
+      <c r="C5">
+        <v>12</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>7</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>11</v>
+      </c>
+      <c r="J6">
+        <v>11</v>
+      </c>
+      <c r="K6">
+        <v>12</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10563,226 +10647,6 @@
       </c>
       <c r="M7">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>12</v>
-      </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>16</v>
-      </c>
-      <c r="L5">
-        <v>8</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>13</v>
-      </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
-      </c>
-      <c r="K6">
-        <v>21</v>
-      </c>
-      <c r="L6">
-        <v>13</v>
-      </c>
-      <c r="M6">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -10855,20 +10719,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M2">
         <v>2</v>
@@ -10878,48 +10751,39 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
       <c r="D3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3">
         <v>3</v>
       </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
       <c r="L3">
         <v>2</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -10928,37 +10792,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -10966,40 +10833,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
         <v>13</v>
       </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
       <c r="I6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -11008,6 +10875,223 @@
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>11</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>11</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>14</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>16</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>13</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11237,182 +11321,6 @@
       </c>
       <c r="M7">
         <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>3</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -11613,6 +11521,182 @@
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -11866,7 +11950,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12039,7 +12123,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12265,7 +12349,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12490,7 +12574,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12653,7 +12737,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12795,7 +12879,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12979,7 +13063,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13182,7 +13266,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13377,229 +13461,6 @@
       </c>
       <c r="M6">
         <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
-      </c>
-      <c r="K3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>6</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>5</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>13</v>
-      </c>
-      <c r="G5">
-        <v>8</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>9</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>22</v>
-      </c>
-      <c r="L5">
-        <v>22</v>
-      </c>
-      <c r="M5">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>8</v>
-      </c>
-      <c r="D6">
-        <v>8</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>14</v>
-      </c>
-      <c r="G6">
-        <v>10</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
-      <c r="J6">
-        <v>13</v>
-      </c>
-      <c r="K6">
-        <v>28</v>
-      </c>
-      <c r="L6">
-        <v>28</v>
-      </c>
-      <c r="M6">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -13876,10 +13737,10 @@
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -13891,9 +13752,10 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
     <col min="11" max="11" width="4.7109375" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13930,123 +13792,165 @@
       <c r="L1" s="1">
         <v>2025</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2">
         <v>2</v>
       </c>
-      <c r="G2">
-        <v>3</v>
+      <c r="H2">
+        <v>1</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="J2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
       <c r="C5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="L5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>22</v>
+      </c>
+      <c r="M5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="L6">
-        <v>9</v>
+        <v>28</v>
+      </c>
+      <c r="M6">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -14078,51 +13982,54 @@
         <v>0</v>
       </c>
       <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
         <v>2016</v>
       </c>
-      <c r="C1" s="1">
+      <c r="D1" s="1">
         <v>2017</v>
       </c>
-      <c r="D1" s="1">
+      <c r="E1" s="1">
         <v>2018</v>
       </c>
-      <c r="E1" s="1">
+      <c r="F1" s="1">
         <v>2019</v>
       </c>
-      <c r="F1" s="1">
+      <c r="G1" s="1">
         <v>2020</v>
       </c>
-      <c r="G1" s="1">
+      <c r="H1" s="1">
         <v>2021</v>
       </c>
-      <c r="H1" s="1">
+      <c r="I1" s="1">
         <v>2022</v>
       </c>
-      <c r="I1" s="1">
+      <c r="J1" s="1">
         <v>2023</v>
       </c>
-      <c r="J1" s="1">
+      <c r="K1" s="1">
         <v>2024</v>
       </c>
-      <c r="K1" s="1">
+      <c r="L1" s="1">
         <v>2025</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2026</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="I2">
         <v>1</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -14133,23 +14040,29 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="K3">
-        <v>1</v>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="J4">
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -14158,34 +14071,28 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
       <c r="J5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -14193,37 +14100,37 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -14232,6 +14139,183 @@
 </file>
 
 <file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14395,7 +14479,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -14451,241 +14535,6 @@
       </c>
       <c r="D4">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>4</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>6</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
-      </c>
-      <c r="K3">
-        <v>7</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>9</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>14</v>
-      </c>
-      <c r="H5">
-        <v>7</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>11</v>
-      </c>
-      <c r="L5">
-        <v>8</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>8</v>
-      </c>
-      <c r="C6">
-        <v>14</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>11</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>22</v>
-      </c>
-      <c r="H6">
-        <v>14</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>16</v>
-      </c>
-      <c r="K6">
-        <v>23</v>
-      </c>
-      <c r="L6">
-        <v>13</v>
-      </c>
-      <c r="M6">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -14762,79 +14611,82 @@
         <v>2</v>
       </c>
       <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
         <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
       <c r="C3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>4</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
@@ -14843,40 +14695,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>14</v>
+      </c>
+      <c r="H5">
         <v>7</v>
       </c>
-      <c r="E5">
-        <v>12</v>
-      </c>
-      <c r="F5">
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>11</v>
+      </c>
+      <c r="L5">
         <v>8</v>
       </c>
-      <c r="G5">
-        <v>7</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -14884,40 +14736,40 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
         <v>22</v>
       </c>
-      <c r="C6">
-        <v>11</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>16</v>
-      </c>
-      <c r="F6">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>10</v>
-      </c>
       <c r="H6">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I6">
         <v>10</v>
       </c>
       <c r="J6">
+        <v>16</v>
+      </c>
+      <c r="K6">
+        <v>23</v>
+      </c>
+      <c r="L6">
+        <v>13</v>
+      </c>
+      <c r="M6">
         <v>9</v>
-      </c>
-      <c r="K6">
-        <v>10</v>
-      </c>
-      <c r="L6">
-        <v>6</v>
-      </c>
-      <c r="M6">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -14926,329 +14778,6 @@
 </file>
 
 <file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -15316,8 +14845,11 @@
       <c r="B2">
         <v>2</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>2</v>
@@ -15328,8 +14860,20 @@
       <c r="H2">
         <v>1</v>
       </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
       <c r="J2">
         <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -15339,39 +14883,42 @@
       <c r="B3">
         <v>1</v>
       </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
       <c r="D3">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="E4">
+      <c r="C4">
         <v>1</v>
       </c>
     </row>
@@ -15379,35 +14926,41 @@
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B5">
+        <v>19</v>
+      </c>
       <c r="C5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -15415,40 +14968,363 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -15722,6 +15598,214 @@
 
 <file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -15908,7 +15992,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16015,7 +16099,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16214,7 +16298,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16318,7 +16402,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16486,7 +16570,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16655,7 +16739,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -16867,186 +16951,6 @@
         <v>8</v>
       </c>
       <c r="M6">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>6</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
         <v>4</v>
       </c>
     </row>
@@ -17079,22 +16983,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D1" s="1">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E1" s="1">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="F1" s="1">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="G1" s="1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H1" s="1">
         <v>2022</v>
@@ -17116,67 +17020,46 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
       <c r="L2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="G3">
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
         <v>2</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
       <c r="J4">
         <v>1</v>
       </c>
@@ -17186,31 +17069,31 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -17218,13 +17101,13 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -17233,22 +17116,22 @@
         <v>1</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -17258,10 +17141,10 @@
 
 <file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -17317,26 +17200,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>2</v>
+      <c r="F2">
+        <v>1</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -17344,18 +17230,21 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
         <v>1</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>1</v>
       </c>
       <c r="L3">
@@ -17364,66 +17253,86 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>8</v>
-      </c>
-      <c r="D4">
         <v>3</v>
       </c>
       <c r="E4">
-        <v>7</v>
-      </c>
-      <c r="F4">
-        <v>4</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
         <v>9</v>
       </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
+      <c r="J6">
+        <v>7</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -17650,6 +17559,181 @@
 
 <file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -17764,7 +17848,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -17922,7 +18006,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18109,7 +18193,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18248,7 +18332,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18426,153 +18510,6 @@
       </c>
       <c r="M5">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -18603,31 +18540,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
         <v>2016</v>
       </c>
-      <c r="C1" s="1">
+      <c r="D1" s="1">
         <v>2017</v>
       </c>
-      <c r="D1" s="1">
+      <c r="E1" s="1">
         <v>2018</v>
       </c>
-      <c r="E1" s="1">
+      <c r="F1" s="1">
         <v>2019</v>
       </c>
-      <c r="F1" s="1">
+      <c r="G1" s="1">
         <v>2020</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2021</v>
       </c>
       <c r="H1" s="1">
         <v>2022</v>
       </c>
       <c r="I1" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="J1" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="K1" s="1">
         <v>2026</v>
@@ -18637,16 +18574,10 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
       <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
         <v>1</v>
       </c>
     </row>
@@ -18654,19 +18585,13 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="K3">
         <v>1</v>
       </c>
     </row>
@@ -18678,22 +18603,25 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>2</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -18704,22 +18632,22 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -18737,6 +18665,162 @@
 </file>
 
 <file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18789,7 +18873,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -18910,97 +18994,6 @@
         <v>2</v>
       </c>
       <c r="I6">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
         <v>1</v>
       </c>
     </row>
@@ -19244,16 +19237,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="C1" s="1">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="D1" s="1">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="E1" s="1">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="1">
         <v>2026</v>
@@ -19263,7 +19256,7 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E2">
+      <c r="C2">
         <v>1</v>
       </c>
     </row>
@@ -19271,14 +19264,11 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -19288,11 +19278,11 @@
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="D4">
+      <c r="C4">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -19303,16 +19293,16 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -19321,6 +19311,100 @@
 </file>
 
 <file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19504,7 +19588,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19582,7 +19666,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19696,7 +19780,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19829,7 +19913,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -19970,7 +20054,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet87.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -20083,7 +20167,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet87.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -20166,7 +20250,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet89.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -20246,82 +20330,6 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet89.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
         <v>1</v>
       </c>
     </row>
@@ -20560,6 +20568,82 @@
 
 <file path=xl/worksheets/sheet90.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet91.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -20626,7 +20710,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet91.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet92.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -20698,77 +20782,6 @@
       </c>
       <c r="E4">
         <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet92.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-full-year.xlsx
+++ b/output/cta-violent-crime-full-year.xlsx
@@ -32,18 +32,18 @@
     <sheet name="Sheffield &amp; DePaul" sheetId="23" r:id="rId23"/>
     <sheet name="Lake View" sheetId="24" r:id="rId24"/>
     <sheet name="River North" sheetId="25" r:id="rId25"/>
-    <sheet name="Bridgeport" sheetId="26" r:id="rId26"/>
-    <sheet name="Roseland" sheetId="27" r:id="rId27"/>
-    <sheet name="Chinatown" sheetId="28" r:id="rId28"/>
-    <sheet name="Austin" sheetId="29" r:id="rId29"/>
-    <sheet name="Little Italy, UIC" sheetId="30" r:id="rId30"/>
-    <sheet name="North Lawndale" sheetId="31" r:id="rId31"/>
-    <sheet name="Armour Square" sheetId="32" r:id="rId32"/>
-    <sheet name="West Elsdon" sheetId="33" r:id="rId33"/>
-    <sheet name="Logan Square" sheetId="34" r:id="rId34"/>
-    <sheet name="Woodlawn" sheetId="35" r:id="rId35"/>
-    <sheet name="Douglas" sheetId="36" r:id="rId36"/>
-    <sheet name="Edgewater" sheetId="37" r:id="rId37"/>
+    <sheet name="Edgewater" sheetId="26" r:id="rId26"/>
+    <sheet name="Bridgeport" sheetId="27" r:id="rId27"/>
+    <sheet name="Roseland" sheetId="28" r:id="rId28"/>
+    <sheet name="Chinatown" sheetId="29" r:id="rId29"/>
+    <sheet name="Austin" sheetId="30" r:id="rId30"/>
+    <sheet name="Little Italy, UIC" sheetId="31" r:id="rId31"/>
+    <sheet name="North Lawndale" sheetId="32" r:id="rId32"/>
+    <sheet name="Armour Square" sheetId="33" r:id="rId33"/>
+    <sheet name="West Elsdon" sheetId="34" r:id="rId34"/>
+    <sheet name="Logan Square" sheetId="35" r:id="rId35"/>
+    <sheet name="Woodlawn" sheetId="36" r:id="rId36"/>
+    <sheet name="Douglas" sheetId="37" r:id="rId37"/>
     <sheet name="Chicago Lawn" sheetId="38" r:id="rId38"/>
     <sheet name="West Loop" sheetId="39" r:id="rId39"/>
     <sheet name="South Deering" sheetId="40" r:id="rId40"/>
@@ -889,7 +889,7 @@
         <v>137</v>
       </c>
       <c r="M2">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1050,7 +1050,7 @@
         <v>467</v>
       </c>
       <c r="M6">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1091,7 +1091,7 @@
         <v>896</v>
       </c>
       <c r="M7">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
   </sheetData>
@@ -1968,7 +1968,7 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2009,7 +2009,7 @@
         <v>13</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -4125,7 +4125,7 @@
         <v>13</v>
       </c>
       <c r="M27">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -5264,7 +5264,7 @@
         <v>9</v>
       </c>
       <c r="M61">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -5959,7 +5959,7 @@
         <v>13</v>
       </c>
       <c r="M80">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -6607,7 +6607,7 @@
         <v>896</v>
       </c>
       <c r="M98">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
   </sheetData>
@@ -8042,52 +8042,67 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="L3">
         <v>2</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J4">
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -8096,28 +8111,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>16</v>
+      </c>
+      <c r="L5">
+        <v>8</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -8125,40 +8152,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6">
         <v>6</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -8168,7 +8195,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -8231,198 +8258,127 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
       <c r="C2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2">
-        <v>4</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>6</v>
-      </c>
-      <c r="I2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>5</v>
-      </c>
       <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>5</v>
-      </c>
-      <c r="F3">
-        <v>7</v>
-      </c>
-      <c r="G3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>9</v>
-      </c>
-      <c r="J3">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>7</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
       <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
         <v>4</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>26</v>
-      </c>
-      <c r="C7">
-        <v>25</v>
-      </c>
-      <c r="D7">
-        <v>16</v>
-      </c>
-      <c r="E7">
-        <v>23</v>
-      </c>
-      <c r="F7">
-        <v>23</v>
-      </c>
-      <c r="G7">
-        <v>24</v>
-      </c>
-      <c r="H7">
-        <v>31</v>
-      </c>
-      <c r="I7">
-        <v>47</v>
-      </c>
-      <c r="J7">
-        <v>35</v>
-      </c>
-      <c r="K7">
-        <v>31</v>
-      </c>
-      <c r="L7">
-        <v>37</v>
-      </c>
-      <c r="M7">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -8495,26 +8451,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
       <c r="E2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="I2">
+        <v>7</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -8522,41 +8493,65 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
       </c>
       <c r="E3">
         <v>5</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
       <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -8564,7 +8559,7 @@
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F5">
+      <c r="D5">
         <v>1</v>
       </c>
     </row>
@@ -8573,40 +8568,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="J6">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="K6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L6">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -8614,40 +8609,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G7">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H7">
+        <v>31</v>
+      </c>
+      <c r="I7">
+        <v>47</v>
+      </c>
+      <c r="J7">
+        <v>35</v>
+      </c>
+      <c r="K7">
+        <v>31</v>
+      </c>
+      <c r="L7">
+        <v>37</v>
+      </c>
+      <c r="M7">
         <v>12</v>
-      </c>
-      <c r="I7">
-        <v>17</v>
-      </c>
-      <c r="J7">
-        <v>9</v>
-      </c>
-      <c r="K7">
-        <v>26</v>
-      </c>
-      <c r="L7">
-        <v>23</v>
-      </c>
-      <c r="M7">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -8720,41 +8715,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
       <c r="E2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -8762,70 +8742,49 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I3">
         <v>6</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+      <c r="I4">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K5">
+      <c r="F5">
         <v>1</v>
       </c>
     </row>
@@ -8834,40 +8793,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="D6">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="H6">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L6">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M6">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -8875,40 +8834,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="E7">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="G7">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="H7">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="I7">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="J7">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="L7">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="M7">
-        <v>37</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -9147,7 +9106,7 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -9210,32 +9169,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2">
         <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9245,35 +9213,38 @@
       <c r="B3">
         <v>4</v>
       </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
       <c r="D3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9283,99 +9254,110 @@
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="H4">
-        <v>2</v>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
       </c>
       <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-      <c r="D5">
-        <v>11</v>
-      </c>
-      <c r="E5">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>25</v>
-      </c>
-      <c r="G5">
-        <v>15</v>
-      </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>9</v>
-      </c>
-      <c r="J5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>18</v>
-      </c>
-      <c r="L5">
-        <v>11</v>
-      </c>
-      <c r="M5">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="D6">
+        <v>22</v>
+      </c>
+      <c r="E6">
+        <v>44</v>
+      </c>
+      <c r="F6">
+        <v>38</v>
+      </c>
+      <c r="G6">
+        <v>24</v>
+      </c>
+      <c r="H6">
+        <v>50</v>
+      </c>
+      <c r="I6">
+        <v>34</v>
+      </c>
+      <c r="J6">
+        <v>26</v>
+      </c>
+      <c r="K6">
+        <v>24</v>
+      </c>
+      <c r="L6">
         <v>14</v>
       </c>
-      <c r="E6">
-        <v>23</v>
-      </c>
-      <c r="F6">
-        <v>28</v>
-      </c>
-      <c r="G6">
-        <v>16</v>
-      </c>
-      <c r="H6">
-        <v>14</v>
-      </c>
-      <c r="I6">
-        <v>17</v>
-      </c>
-      <c r="J6">
-        <v>16</v>
-      </c>
-      <c r="K6">
-        <v>31</v>
-      </c>
-      <c r="L6">
-        <v>22</v>
-      </c>
       <c r="M6">
-        <v>14</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>40</v>
+      </c>
+      <c r="D7">
+        <v>32</v>
+      </c>
+      <c r="E7">
+        <v>57</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>34</v>
+      </c>
+      <c r="H7">
+        <v>63</v>
+      </c>
+      <c r="I7">
+        <v>44</v>
+      </c>
+      <c r="J7">
+        <v>47</v>
+      </c>
+      <c r="K7">
+        <v>46</v>
+      </c>
+      <c r="L7">
+        <v>33</v>
+      </c>
+      <c r="M7">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -9448,41 +9430,32 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
       <c r="F2">
         <v>2</v>
       </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
       <c r="H2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L2">
         <v>4</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9490,47 +9463,56 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
         <v>2</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>4</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
       <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -9539,40 +9521,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E5">
         <v>21</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H5">
         <v>10</v>
       </c>
       <c r="I5">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K5">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="L5">
+        <v>11</v>
+      </c>
+      <c r="M5">
         <v>7</v>
-      </c>
-      <c r="M5">
-        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -9580,40 +9562,40 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6">
         <v>14</v>
       </c>
-      <c r="C6">
-        <v>26</v>
-      </c>
-      <c r="D6">
-        <v>29</v>
-      </c>
       <c r="E6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F6">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H6">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I6">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J6">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K6">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="L6">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="M6">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -9686,32 +9668,41 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9722,31 +9713,31 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M3">
         <v>3</v>
@@ -9756,10 +9747,10 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="M4">
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
@@ -9768,40 +9759,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="F5">
+        <v>35</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
         <v>15</v>
       </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>9</v>
+      </c>
+      <c r="L5">
         <v>7</v>
       </c>
-      <c r="I5">
-        <v>11</v>
-      </c>
-      <c r="J5">
-        <v>15</v>
-      </c>
-      <c r="K5">
-        <v>11</v>
-      </c>
-      <c r="L5">
-        <v>19</v>
-      </c>
       <c r="M5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -9809,40 +9800,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E6">
+        <v>24</v>
+      </c>
+      <c r="F6">
+        <v>42</v>
+      </c>
+      <c r="G6">
+        <v>18</v>
+      </c>
+      <c r="H6">
+        <v>18</v>
+      </c>
+      <c r="I6">
+        <v>21</v>
+      </c>
+      <c r="J6">
         <v>12</v>
       </c>
-      <c r="F6">
-        <v>19</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>15</v>
-      </c>
-      <c r="J6">
-        <v>21</v>
-      </c>
       <c r="K6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L6">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="M6">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -9851,157 +9842,6 @@
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10072,29 +9912,35 @@
       <c r="D2">
         <v>2</v>
       </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
       <c r="C3">
         <v>1</v>
       </c>
@@ -10102,6 +9948,9 @@
         <v>1</v>
       </c>
       <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
         <v>1</v>
       </c>
       <c r="H3">
@@ -10111,29 +9960,26 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="L4">
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -10142,40 +9988,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J5">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L5">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -10183,39 +10029,190 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6">
         <v>7</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I6">
+        <v>15</v>
+      </c>
+      <c r="J6">
+        <v>21</v>
+      </c>
+      <c r="K6">
+        <v>16</v>
+      </c>
+      <c r="L6">
+        <v>28</v>
+      </c>
+      <c r="M6">
         <v>7</v>
       </c>
-      <c r="J6">
-        <v>15</v>
-      </c>
-      <c r="K6">
-        <v>10</v>
-      </c>
-      <c r="L6">
-        <v>14</v>
-      </c>
-      <c r="M6">
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
         <v>1</v>
       </c>
     </row>
@@ -10289,68 +10286,74 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
       </c>
       <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
         <v>2</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
         <v>1</v>
       </c>
     </row>
@@ -10359,40 +10362,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K5">
         <v>7</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -10400,40 +10403,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
         <v>10</v>
       </c>
-      <c r="E6">
-        <v>11</v>
-      </c>
-      <c r="F6">
+      <c r="I6">
         <v>7</v>
       </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
-      <c r="H6">
-        <v>8</v>
-      </c>
-      <c r="I6">
-        <v>11</v>
-      </c>
       <c r="J6">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -10442,6 +10445,223 @@
 </file>
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>5</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>11</v>
+      </c>
+      <c r="C5">
+        <v>12</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>7</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>11</v>
+      </c>
+      <c r="J6">
+        <v>11</v>
+      </c>
+      <c r="K6">
+        <v>12</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10647,226 +10867,6 @@
       </c>
       <c r="M7">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>5</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>12</v>
-      </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
-      </c>
-      <c r="K5">
-        <v>16</v>
-      </c>
-      <c r="L5">
-        <v>8</v>
-      </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>13</v>
-      </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
-      </c>
-      <c r="K6">
-        <v>21</v>
-      </c>
-      <c r="L6">
-        <v>13</v>
-      </c>
-      <c r="M6">
-        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-full-year.xlsx
+++ b/output/cta-violent-crime-full-year.xlsx
@@ -9,47 +9,47 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Austin" sheetId="3" r:id="rId3"/>
-    <sheet name="Kenwood" sheetId="4" r:id="rId4"/>
-    <sheet name="Loop" sheetId="5" r:id="rId5"/>
-    <sheet name="South Chicago" sheetId="6" r:id="rId6"/>
-    <sheet name="Edgewater" sheetId="7" r:id="rId7"/>
-    <sheet name="West Lawn" sheetId="8" r:id="rId8"/>
-    <sheet name="Lower West Side" sheetId="9" r:id="rId9"/>
-    <sheet name="Old Town" sheetId="10" r:id="rId10"/>
-    <sheet name="Gage Park" sheetId="11" r:id="rId11"/>
-    <sheet name="Grand Boulevard" sheetId="12" r:id="rId12"/>
-    <sheet name="Englewood" sheetId="13" r:id="rId13"/>
-    <sheet name="Washington Park" sheetId="14" r:id="rId14"/>
-    <sheet name="Little Italy, UIC" sheetId="15" r:id="rId15"/>
-    <sheet name="West Town" sheetId="16" r:id="rId16"/>
-    <sheet name="Garfield Park" sheetId="17" r:id="rId17"/>
-    <sheet name="North Lawndale" sheetId="18" r:id="rId18"/>
-    <sheet name="Uptown" sheetId="19" r:id="rId19"/>
-    <sheet name="Riverdale" sheetId="20" r:id="rId20"/>
-    <sheet name="Fuller Park" sheetId="21" r:id="rId21"/>
-    <sheet name="Little Village" sheetId="22" r:id="rId22"/>
-    <sheet name="Lake View" sheetId="23" r:id="rId23"/>
-    <sheet name="Roseland" sheetId="24" r:id="rId24"/>
-    <sheet name="Albany Park" sheetId="25" r:id="rId25"/>
-    <sheet name="Woodlawn" sheetId="26" r:id="rId26"/>
-    <sheet name="South Shore" sheetId="27" r:id="rId27"/>
-    <sheet name="O'Hare" sheetId="28" r:id="rId28"/>
-    <sheet name="Near South Side" sheetId="29" r:id="rId29"/>
-    <sheet name="Grand Crossing" sheetId="30" r:id="rId30"/>
-    <sheet name="Avondale" sheetId="31" r:id="rId31"/>
-    <sheet name="Rush &amp; Division" sheetId="32" r:id="rId32"/>
-    <sheet name="Oakland" sheetId="33" r:id="rId33"/>
-    <sheet name="Chatham" sheetId="34" r:id="rId34"/>
-    <sheet name="New City" sheetId="35" r:id="rId35"/>
-    <sheet name="Belmont Cragin" sheetId="36" r:id="rId36"/>
-    <sheet name="West Loop" sheetId="37" r:id="rId37"/>
-    <sheet name="Hegewisch" sheetId="38" r:id="rId38"/>
-    <sheet name="Greektown" sheetId="39" r:id="rId39"/>
-    <sheet name="Humboldt Park" sheetId="40" r:id="rId40"/>
-    <sheet name="Sheffield &amp; DePaul" sheetId="41" r:id="rId41"/>
-    <sheet name="Norwood Park" sheetId="42" r:id="rId42"/>
-    <sheet name="Wrigleyville" sheetId="43" r:id="rId43"/>
+    <sheet name="Wrigleyville" sheetId="3" r:id="rId3"/>
+    <sheet name="Austin" sheetId="4" r:id="rId4"/>
+    <sheet name="Kenwood" sheetId="5" r:id="rId5"/>
+    <sheet name="Loop" sheetId="6" r:id="rId6"/>
+    <sheet name="South Chicago" sheetId="7" r:id="rId7"/>
+    <sheet name="Edgewater" sheetId="8" r:id="rId8"/>
+    <sheet name="West Lawn" sheetId="9" r:id="rId9"/>
+    <sheet name="Lower West Side" sheetId="10" r:id="rId10"/>
+    <sheet name="Old Town" sheetId="11" r:id="rId11"/>
+    <sheet name="Gage Park" sheetId="12" r:id="rId12"/>
+    <sheet name="Grand Boulevard" sheetId="13" r:id="rId13"/>
+    <sheet name="Englewood" sheetId="14" r:id="rId14"/>
+    <sheet name="Washington Park" sheetId="15" r:id="rId15"/>
+    <sheet name="Little Italy, UIC" sheetId="16" r:id="rId16"/>
+    <sheet name="West Town" sheetId="17" r:id="rId17"/>
+    <sheet name="Garfield Park" sheetId="18" r:id="rId18"/>
+    <sheet name="North Lawndale" sheetId="19" r:id="rId19"/>
+    <sheet name="Uptown" sheetId="20" r:id="rId20"/>
+    <sheet name="Riverdale" sheetId="21" r:id="rId21"/>
+    <sheet name="Fuller Park" sheetId="22" r:id="rId22"/>
+    <sheet name="Little Village" sheetId="23" r:id="rId23"/>
+    <sheet name="Lake View" sheetId="24" r:id="rId24"/>
+    <sheet name="Roseland" sheetId="25" r:id="rId25"/>
+    <sheet name="Albany Park" sheetId="26" r:id="rId26"/>
+    <sheet name="Woodlawn" sheetId="27" r:id="rId27"/>
+    <sheet name="South Shore" sheetId="28" r:id="rId28"/>
+    <sheet name="O'Hare" sheetId="29" r:id="rId29"/>
+    <sheet name="Near South Side" sheetId="30" r:id="rId30"/>
+    <sheet name="Grand Crossing" sheetId="31" r:id="rId31"/>
+    <sheet name="Avondale" sheetId="32" r:id="rId32"/>
+    <sheet name="Rush &amp; Division" sheetId="33" r:id="rId33"/>
+    <sheet name="Oakland" sheetId="34" r:id="rId34"/>
+    <sheet name="Chatham" sheetId="35" r:id="rId35"/>
+    <sheet name="New City" sheetId="36" r:id="rId36"/>
+    <sheet name="Belmont Cragin" sheetId="37" r:id="rId37"/>
+    <sheet name="West Loop" sheetId="38" r:id="rId38"/>
+    <sheet name="Hegewisch" sheetId="39" r:id="rId39"/>
+    <sheet name="Greektown" sheetId="40" r:id="rId40"/>
+    <sheet name="Humboldt Park" sheetId="41" r:id="rId41"/>
+    <sheet name="Sheffield &amp; DePaul" sheetId="42" r:id="rId42"/>
+    <sheet name="Norwood Park" sheetId="43" r:id="rId43"/>
     <sheet name="Auburn Gresham" sheetId="44" r:id="rId44"/>
     <sheet name="Rogers Park" sheetId="45" r:id="rId45"/>
     <sheet name="Chicago Lawn" sheetId="46" r:id="rId46"/>
@@ -889,7 +889,7 @@
         <v>137</v>
       </c>
       <c r="M2">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1091,7 +1091,7 @@
         <v>896</v>
       </c>
       <c r="M7">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
   </sheetData>
@@ -1100,6 +1100,206 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>7</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>6</v>
+      </c>
+      <c r="J5">
+        <v>10</v>
+      </c>
+      <c r="K5">
+        <v>6</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1316,7 +1516,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1544,7 +1744,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1761,7 +1961,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2018,235 +2218,6 @@
       </c>
       <c r="M7">
         <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>5</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>7</v>
-      </c>
-      <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>7</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>8</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>7</v>
-      </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <v>11</v>
-      </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>10</v>
-      </c>
-      <c r="H6">
-        <v>7</v>
-      </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
-      <c r="J6">
-        <v>12</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>8</v>
-      </c>
-      <c r="M6">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -2320,39 +2291,42 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>4</v>
+      <c r="C3">
+        <v>2</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -2367,41 +2341,29 @@
         <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3">
         <v>4</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
       <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -2410,40 +2372,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C5">
         <v>7</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2451,40 +2413,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C6">
         <v>10</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H6">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J6">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K6">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -2557,32 +2519,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
+      <c r="C2">
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M2">
         <v>4</v>
@@ -2592,14 +2551,14 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
+      <c r="B3">
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -2611,26 +2570,38 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J4">
-        <v>1</v>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
       </c>
       <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -2639,40 +2610,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F5">
+        <v>25</v>
+      </c>
+      <c r="G5">
+        <v>15</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5">
+        <v>11</v>
+      </c>
+      <c r="K5">
+        <v>18</v>
+      </c>
+      <c r="L5">
+        <v>11</v>
+      </c>
+      <c r="M5">
         <v>7</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>6</v>
-      </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2680,40 +2651,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="L6">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="M6">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -2722,6 +2693,235 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>7</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="I5">
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>12</v>
+      </c>
+      <c r="E6">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>9</v>
+      </c>
+      <c r="L6">
+        <v>15</v>
+      </c>
+      <c r="M6">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2978,244 +3178,6 @@
       </c>
       <c r="M7">
         <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>6</v>
-      </c>
-      <c r="L3">
-        <v>7</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>12</v>
-      </c>
-      <c r="C5">
-        <v>21</v>
-      </c>
-      <c r="D5">
-        <v>28</v>
-      </c>
-      <c r="E5">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>35</v>
-      </c>
-      <c r="G5">
-        <v>12</v>
-      </c>
-      <c r="H5">
-        <v>10</v>
-      </c>
-      <c r="I5">
-        <v>15</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>9</v>
-      </c>
-      <c r="L5">
-        <v>7</v>
-      </c>
-      <c r="M5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>14</v>
-      </c>
-      <c r="C6">
-        <v>26</v>
-      </c>
-      <c r="D6">
-        <v>29</v>
-      </c>
-      <c r="E6">
-        <v>24</v>
-      </c>
-      <c r="F6">
-        <v>42</v>
-      </c>
-      <c r="G6">
-        <v>18</v>
-      </c>
-      <c r="H6">
-        <v>18</v>
-      </c>
-      <c r="I6">
-        <v>21</v>
-      </c>
-      <c r="J6">
-        <v>12</v>
-      </c>
-      <c r="K6">
-        <v>18</v>
-      </c>
-      <c r="L6">
-        <v>18</v>
-      </c>
-      <c r="M6">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3289,22 +3251,22 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2">
         <v>5</v>
@@ -3313,13 +3275,13 @@
         <v>2</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M2">
         <v>3</v>
@@ -3329,20 +3291,20 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
       <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
         <v>2</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -3351,23 +3313,26 @@
         <v>4</v>
       </c>
       <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>6</v>
+      </c>
+      <c r="L3">
         <v>7</v>
       </c>
-      <c r="K3">
-        <v>7</v>
-      </c>
-      <c r="L3">
-        <v>3</v>
-      </c>
       <c r="M3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4">
         <v>1</v>
       </c>
     </row>
@@ -3376,40 +3341,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C5">
+        <v>21</v>
+      </c>
+      <c r="D5">
+        <v>28</v>
+      </c>
+      <c r="E5">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>35</v>
+      </c>
+      <c r="G5">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>15</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
         <v>9</v>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>14</v>
-      </c>
-      <c r="H5">
+      <c r="L5">
         <v>7</v>
       </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>11</v>
-      </c>
-      <c r="L5">
-        <v>8</v>
-      </c>
       <c r="M5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -3417,40 +3382,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F6">
+        <v>42</v>
+      </c>
+      <c r="G6">
+        <v>18</v>
+      </c>
+      <c r="H6">
+        <v>18</v>
+      </c>
+      <c r="I6">
+        <v>21</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+      <c r="K6">
+        <v>18</v>
+      </c>
+      <c r="L6">
+        <v>18</v>
+      </c>
+      <c r="M6">
         <v>10</v>
-      </c>
-      <c r="G6">
-        <v>22</v>
-      </c>
-      <c r="H6">
-        <v>14</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>16</v>
-      </c>
-      <c r="K6">
-        <v>23</v>
-      </c>
-      <c r="L6">
-        <v>13</v>
-      </c>
-      <c r="M6">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -6783,7 +6748,7 @@
         <v>3</v>
       </c>
       <c r="M97">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -6824,7 +6789,7 @@
         <v>896</v>
       </c>
       <c r="M98">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
   </sheetData>
@@ -6933,6 +6898,241 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>6</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>7</v>
+      </c>
+      <c r="K3">
+        <v>7</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>14</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>11</v>
+      </c>
+      <c r="L5">
+        <v>8</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>22</v>
+      </c>
+      <c r="H6">
+        <v>14</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <v>16</v>
+      </c>
+      <c r="K6">
+        <v>23</v>
+      </c>
+      <c r="L6">
+        <v>13</v>
+      </c>
+      <c r="M6">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -7094,7 +7294,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7310,208 +7510,6 @@
       </c>
       <c r="M6">
         <v>11</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -7584,38 +7582,17 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -7623,37 +7600,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>11</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M3">
         <v>4</v>
@@ -7663,61 +7631,46 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
       <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
       <c r="C5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>17</v>
-      </c>
-      <c r="I5">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -7725,40 +7678,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -7767,6 +7720,253 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>4</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>6</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>11</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>14</v>
+      </c>
+      <c r="D5">
+        <v>12</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>11</v>
+      </c>
+      <c r="H5">
+        <v>17</v>
+      </c>
+      <c r="I5">
+        <v>20</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>10</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>23</v>
+      </c>
+      <c r="D6">
+        <v>14</v>
+      </c>
+      <c r="E6">
+        <v>18</v>
+      </c>
+      <c r="F6">
+        <v>18</v>
+      </c>
+      <c r="G6">
+        <v>19</v>
+      </c>
+      <c r="H6">
+        <v>27</v>
+      </c>
+      <c r="I6">
+        <v>26</v>
+      </c>
+      <c r="J6">
+        <v>16</v>
+      </c>
+      <c r="K6">
+        <v>24</v>
+      </c>
+      <c r="L6">
+        <v>19</v>
+      </c>
+      <c r="M6">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8030,7 +8230,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8231,7 +8431,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8448,7 +8648,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8678,7 +8878,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8881,9 +9081,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -8946,26 +9146,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
       <c r="F2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
       <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -8975,391 +9175,116 @@
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3">
-        <v>2</v>
+      <c r="F3">
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J4">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
       </c>
       <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K6">
         <v>3</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M6">
         <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>7</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>6</v>
-      </c>
-      <c r="E7">
-        <v>7</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="G7">
-        <v>8</v>
-      </c>
-      <c r="H7">
-        <v>9</v>
-      </c>
-      <c r="I7">
-        <v>13</v>
-      </c>
-      <c r="J7">
-        <v>8</v>
-      </c>
-      <c r="K7">
-        <v>8</v>
-      </c>
-      <c r="L7">
-        <v>4</v>
-      </c>
-      <c r="M7">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>4</v>
-      </c>
-      <c r="J2">
-        <v>8</v>
-      </c>
-      <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>5</v>
-      </c>
-      <c r="D3">
-        <v>6</v>
-      </c>
-      <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3">
-        <v>6</v>
-      </c>
-      <c r="G3">
-        <v>7</v>
-      </c>
-      <c r="H3">
-        <v>8</v>
-      </c>
-      <c r="I3">
-        <v>6</v>
-      </c>
-      <c r="J3">
-        <v>10</v>
-      </c>
-      <c r="K3">
-        <v>12</v>
-      </c>
-      <c r="L3">
-        <v>14</v>
-      </c>
-      <c r="M3">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>23</v>
-      </c>
-      <c r="C6">
-        <v>31</v>
-      </c>
-      <c r="D6">
-        <v>22</v>
-      </c>
-      <c r="E6">
-        <v>44</v>
-      </c>
-      <c r="F6">
-        <v>38</v>
-      </c>
-      <c r="G6">
-        <v>24</v>
-      </c>
-      <c r="H6">
-        <v>50</v>
-      </c>
-      <c r="I6">
-        <v>34</v>
-      </c>
-      <c r="J6">
-        <v>26</v>
-      </c>
-      <c r="K6">
-        <v>24</v>
-      </c>
-      <c r="L6">
-        <v>14</v>
-      </c>
-      <c r="M6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>32</v>
-      </c>
-      <c r="C7">
-        <v>40</v>
-      </c>
-      <c r="D7">
-        <v>32</v>
-      </c>
-      <c r="E7">
-        <v>57</v>
-      </c>
-      <c r="F7">
-        <v>53</v>
-      </c>
-      <c r="G7">
-        <v>34</v>
-      </c>
-      <c r="H7">
-        <v>63</v>
-      </c>
-      <c r="I7">
-        <v>44</v>
-      </c>
-      <c r="J7">
-        <v>47</v>
-      </c>
-      <c r="K7">
-        <v>46</v>
-      </c>
-      <c r="L7">
-        <v>33</v>
-      </c>
-      <c r="M7">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -9432,41 +9357,26 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>7</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
       <c r="F2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -9474,56 +9384,41 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>17</v>
-      </c>
-      <c r="L3">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
       <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -9531,19 +9426,7 @@
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
       <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
         <v>1</v>
       </c>
     </row>
@@ -9552,40 +9435,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -9593,40 +9476,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F7">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="G7">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="H7">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="J7">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="M7">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -9636,7 +9519,7 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -9700,144 +9583,200 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
       <c r="E3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="K3">
+        <v>17</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="K4">
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
       <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="L6">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>42</v>
+      </c>
+      <c r="D7">
+        <v>36</v>
+      </c>
+      <c r="E7">
+        <v>38</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>28</v>
+      </c>
+      <c r="H7">
+        <v>39</v>
+      </c>
+      <c r="I7">
+        <v>39</v>
+      </c>
+      <c r="J7">
+        <v>47</v>
+      </c>
+      <c r="K7">
+        <v>74</v>
+      </c>
+      <c r="L7">
+        <v>63</v>
+      </c>
+      <c r="M7">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -9911,67 +9850,64 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
       </c>
       <c r="L3">
         <v>2</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M4">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
     </row>
@@ -9980,40 +9916,37 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5">
         <v>3</v>
       </c>
       <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -10021,40 +9954,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -10063,6 +9996,223 @@
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>14</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>16</v>
+      </c>
+      <c r="H6">
+        <v>11</v>
+      </c>
+      <c r="I6">
+        <v>14</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <v>7</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10156,7 +10306,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10408,7 +10558,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10592,7 +10742,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10750,7 +10900,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10987,7 +11137,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11065,7 +11215,268 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>8</v>
+      </c>
+      <c r="K2">
+        <v>7</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>7</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>6</v>
+      </c>
+      <c r="J3">
+        <v>10</v>
+      </c>
+      <c r="K3">
+        <v>12</v>
+      </c>
+      <c r="L3">
+        <v>14</v>
+      </c>
+      <c r="M3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>23</v>
+      </c>
+      <c r="C6">
+        <v>31</v>
+      </c>
+      <c r="D6">
+        <v>22</v>
+      </c>
+      <c r="E6">
+        <v>44</v>
+      </c>
+      <c r="F6">
+        <v>38</v>
+      </c>
+      <c r="G6">
+        <v>24</v>
+      </c>
+      <c r="H6">
+        <v>50</v>
+      </c>
+      <c r="I6">
+        <v>34</v>
+      </c>
+      <c r="J6">
+        <v>26</v>
+      </c>
+      <c r="K6">
+        <v>24</v>
+      </c>
+      <c r="L6">
+        <v>14</v>
+      </c>
+      <c r="M6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>40</v>
+      </c>
+      <c r="D7">
+        <v>32</v>
+      </c>
+      <c r="E7">
+        <v>57</v>
+      </c>
+      <c r="F7">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>34</v>
+      </c>
+      <c r="H7">
+        <v>63</v>
+      </c>
+      <c r="I7">
+        <v>44</v>
+      </c>
+      <c r="J7">
+        <v>47</v>
+      </c>
+      <c r="K7">
+        <v>46</v>
+      </c>
+      <c r="L7">
+        <v>33</v>
+      </c>
+      <c r="M7">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11242,149 +11653,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11619,7 +11888,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -11842,7 +12111,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -12019,214 +12288,6 @@
       </c>
       <c r="K7">
         <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>3</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>3</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -13506,7 +13567,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -13519,269 +13580,126 @@
     <col min="8" max="8" width="4.7109375" customWidth="1"/>
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="D1" s="1">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="E1" s="1">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="F1" s="1">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="G1" s="1">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="H1" s="1">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="I1" s="1">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>6</v>
-      </c>
       <c r="C2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>12</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>8</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>13</v>
-      </c>
-      <c r="I2">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>22</v>
-      </c>
-      <c r="K2">
-        <v>15</v>
-      </c>
-      <c r="L2">
-        <v>15</v>
-      </c>
-      <c r="M2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>13</v>
-      </c>
-      <c r="C3">
-        <v>13</v>
-      </c>
       <c r="D3">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>18</v>
-      </c>
-      <c r="F3">
-        <v>14</v>
-      </c>
-      <c r="G3">
-        <v>26</v>
-      </c>
-      <c r="H3">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>32</v>
-      </c>
-      <c r="J3">
-        <v>40</v>
-      </c>
-      <c r="K3">
-        <v>26</v>
-      </c>
-      <c r="L3">
-        <v>34</v>
-      </c>
-      <c r="M3">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>4</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>2</v>
-      </c>
-      <c r="L4">
-        <v>5</v>
-      </c>
-      <c r="M4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="E5">
         <v>1</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>2</v>
       </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>64</v>
-      </c>
-      <c r="K6">
-        <v>48</v>
-      </c>
-      <c r="L6">
-        <v>44</v>
-      </c>
-      <c r="M6">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>49</v>
-      </c>
-      <c r="C7">
-        <v>62</v>
-      </c>
-      <c r="D7">
-        <v>79</v>
-      </c>
-      <c r="E7">
-        <v>92</v>
-      </c>
-      <c r="F7">
-        <v>92</v>
-      </c>
-      <c r="G7">
-        <v>88</v>
-      </c>
-      <c r="H7">
-        <v>120</v>
-      </c>
-      <c r="I7">
-        <v>130</v>
-      </c>
-      <c r="J7">
-        <v>131</v>
-      </c>
-      <c r="K7">
-        <v>91</v>
-      </c>
-      <c r="L7">
-        <v>100</v>
-      </c>
-      <c r="M7">
-        <v>45</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -15366,10 +15284,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -15430,30 +15348,39 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="L2">
+        <v>15</v>
+      </c>
+      <c r="M2">
         <v>2</v>
       </c>
     </row>
@@ -15462,116 +15389,177 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>13</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
       </c>
       <c r="K4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>17</v>
-      </c>
-      <c r="C5">
-        <v>9</v>
-      </c>
-      <c r="D5">
-        <v>6</v>
-      </c>
-      <c r="E5">
-        <v>11</v>
-      </c>
-      <c r="F5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>6</v>
-      </c>
-      <c r="I5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="M5">
-        <v>5</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>30</v>
+      </c>
+      <c r="C6">
+        <v>44</v>
+      </c>
+      <c r="D6">
+        <v>49</v>
+      </c>
+      <c r="E6">
+        <v>67</v>
+      </c>
+      <c r="F6">
+        <v>69</v>
+      </c>
+      <c r="G6">
+        <v>57</v>
+      </c>
+      <c r="H6">
+        <v>80</v>
+      </c>
+      <c r="I6">
+        <v>80</v>
+      </c>
+      <c r="J6">
+        <v>64</v>
+      </c>
+      <c r="K6">
+        <v>48</v>
+      </c>
+      <c r="L6">
+        <v>44</v>
+      </c>
+      <c r="M6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>49</v>
+      </c>
+      <c r="C7">
+        <v>62</v>
+      </c>
+      <c r="D7">
+        <v>79</v>
+      </c>
+      <c r="E7">
+        <v>92</v>
+      </c>
+      <c r="F7">
+        <v>92</v>
+      </c>
+      <c r="G7">
+        <v>88</v>
+      </c>
+      <c r="H7">
+        <v>120</v>
+      </c>
+      <c r="I7">
+        <v>130</v>
+      </c>
+      <c r="J7">
+        <v>131</v>
+      </c>
+      <c r="K7">
+        <v>91</v>
+      </c>
+      <c r="L7">
+        <v>100</v>
+      </c>
+      <c r="M7">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -17308,10 +17296,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -17371,17 +17359,20 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
       <c r="F2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
       </c>
       <c r="I2">
         <v>2</v>
@@ -17390,135 +17381,127 @@
         <v>1</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>3</v>
-      </c>
-      <c r="M2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>13</v>
+      </c>
+      <c r="C4">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4">
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>6</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5">
         <v>4</v>
       </c>
       <c r="H5">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L5">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>11</v>
-      </c>
-      <c r="H6">
-        <v>13</v>
-      </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
-      </c>
-      <c r="K6">
-        <v>21</v>
-      </c>
-      <c r="L6">
-        <v>13</v>
-      </c>
-      <c r="M6">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -19124,42 +19107,98 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
     <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
         <v>2017</v>
       </c>
-      <c r="C1" s="1">
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
         <v>2019</v>
       </c>
-      <c r="D1" s="1">
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
         <v>2022</v>
       </c>
-      <c r="E1" s="1">
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -19169,33 +19208,116 @@
       <c r="E3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>3</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5">
+        <v>12</v>
+      </c>
+      <c r="I5">
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>16</v>
+      </c>
+      <c r="L5">
+        <v>8</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>13</v>
+      </c>
+      <c r="I6">
+        <v>12</v>
+      </c>
+      <c r="J6">
+        <v>10</v>
+      </c>
+      <c r="K6">
+        <v>21</v>
+      </c>
+      <c r="L6">
+        <v>13</v>
+      </c>
+      <c r="M6">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -20392,7 +20514,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -20400,189 +20522,70 @@
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
     <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="C1" s="1">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="D1" s="1">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>3</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
-      <c r="E4">
-        <v>7</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>3</v>
-      </c>
-      <c r="J4">
-        <v>7</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="M4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>7</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>6</v>
-      </c>
-      <c r="J5">
-        <v>10</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>3</v>
-      </c>
-      <c r="M5">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/cta-violent-crime-full-year.xlsx
+++ b/output/cta-violent-crime-full-year.xlsx
@@ -9,49 +9,49 @@
   <sheets>
     <sheet name="Citywide Totals" sheetId="1" r:id="rId1"/>
     <sheet name="By Neighborhood" sheetId="2" r:id="rId2"/>
-    <sheet name="Woodlawn" sheetId="3" r:id="rId3"/>
-    <sheet name="Roseland" sheetId="4" r:id="rId4"/>
-    <sheet name="Rush &amp; Division" sheetId="5" r:id="rId5"/>
-    <sheet name="Rogers Park" sheetId="6" r:id="rId6"/>
-    <sheet name="North Lawndale" sheetId="7" r:id="rId7"/>
-    <sheet name="Wrigleyville" sheetId="8" r:id="rId8"/>
-    <sheet name="Austin" sheetId="9" r:id="rId9"/>
-    <sheet name="Kenwood" sheetId="10" r:id="rId10"/>
-    <sheet name="Loop" sheetId="11" r:id="rId11"/>
-    <sheet name="South Chicago" sheetId="12" r:id="rId12"/>
-    <sheet name="Edgewater" sheetId="13" r:id="rId13"/>
-    <sheet name="West Lawn" sheetId="14" r:id="rId14"/>
-    <sheet name="Lower West Side" sheetId="15" r:id="rId15"/>
-    <sheet name="Old Town" sheetId="16" r:id="rId16"/>
-    <sheet name="Gage Park" sheetId="17" r:id="rId17"/>
-    <sheet name="Grand Boulevard" sheetId="18" r:id="rId18"/>
-    <sheet name="Englewood" sheetId="19" r:id="rId19"/>
-    <sheet name="Washington Park" sheetId="20" r:id="rId20"/>
-    <sheet name="Little Italy, UIC" sheetId="21" r:id="rId21"/>
-    <sheet name="West Town" sheetId="22" r:id="rId22"/>
-    <sheet name="Garfield Park" sheetId="23" r:id="rId23"/>
-    <sheet name="Uptown" sheetId="24" r:id="rId24"/>
-    <sheet name="Riverdale" sheetId="25" r:id="rId25"/>
-    <sheet name="Fuller Park" sheetId="26" r:id="rId26"/>
-    <sheet name="Little Village" sheetId="27" r:id="rId27"/>
-    <sheet name="Lake View" sheetId="28" r:id="rId28"/>
-    <sheet name="Albany Park" sheetId="29" r:id="rId29"/>
-    <sheet name="South Shore" sheetId="30" r:id="rId30"/>
-    <sheet name="O'Hare" sheetId="31" r:id="rId31"/>
-    <sheet name="Near South Side" sheetId="32" r:id="rId32"/>
-    <sheet name="Grand Crossing" sheetId="33" r:id="rId33"/>
-    <sheet name="Avondale" sheetId="34" r:id="rId34"/>
-    <sheet name="Oakland" sheetId="35" r:id="rId35"/>
-    <sheet name="Chatham" sheetId="36" r:id="rId36"/>
-    <sheet name="New City" sheetId="37" r:id="rId37"/>
-    <sheet name="Belmont Cragin" sheetId="38" r:id="rId38"/>
-    <sheet name="West Loop" sheetId="39" r:id="rId39"/>
-    <sheet name="Hegewisch" sheetId="40" r:id="rId40"/>
-    <sheet name="Greektown" sheetId="41" r:id="rId41"/>
-    <sheet name="Humboldt Park" sheetId="42" r:id="rId42"/>
-    <sheet name="Sheffield &amp; DePaul" sheetId="43" r:id="rId43"/>
-    <sheet name="Norwood Park" sheetId="44" r:id="rId44"/>
-    <sheet name="Auburn Gresham" sheetId="45" r:id="rId45"/>
+    <sheet name="Englewood" sheetId="3" r:id="rId3"/>
+    <sheet name="Auburn Gresham" sheetId="4" r:id="rId4"/>
+    <sheet name="Woodlawn" sheetId="5" r:id="rId5"/>
+    <sheet name="Roseland" sheetId="6" r:id="rId6"/>
+    <sheet name="Rush &amp; Division" sheetId="7" r:id="rId7"/>
+    <sheet name="Rogers Park" sheetId="8" r:id="rId8"/>
+    <sheet name="North Lawndale" sheetId="9" r:id="rId9"/>
+    <sheet name="Wrigleyville" sheetId="10" r:id="rId10"/>
+    <sheet name="Austin" sheetId="11" r:id="rId11"/>
+    <sheet name="Kenwood" sheetId="12" r:id="rId12"/>
+    <sheet name="Loop" sheetId="13" r:id="rId13"/>
+    <sheet name="South Chicago" sheetId="14" r:id="rId14"/>
+    <sheet name="Edgewater" sheetId="15" r:id="rId15"/>
+    <sheet name="West Lawn" sheetId="16" r:id="rId16"/>
+    <sheet name="Lower West Side" sheetId="17" r:id="rId17"/>
+    <sheet name="Old Town" sheetId="18" r:id="rId18"/>
+    <sheet name="Gage Park" sheetId="19" r:id="rId19"/>
+    <sheet name="Grand Boulevard" sheetId="20" r:id="rId20"/>
+    <sheet name="Washington Park" sheetId="21" r:id="rId21"/>
+    <sheet name="Little Italy, UIC" sheetId="22" r:id="rId22"/>
+    <sheet name="West Town" sheetId="23" r:id="rId23"/>
+    <sheet name="Garfield Park" sheetId="24" r:id="rId24"/>
+    <sheet name="Uptown" sheetId="25" r:id="rId25"/>
+    <sheet name="Riverdale" sheetId="26" r:id="rId26"/>
+    <sheet name="Fuller Park" sheetId="27" r:id="rId27"/>
+    <sheet name="Little Village" sheetId="28" r:id="rId28"/>
+    <sheet name="Lake View" sheetId="29" r:id="rId29"/>
+    <sheet name="Albany Park" sheetId="30" r:id="rId30"/>
+    <sheet name="South Shore" sheetId="31" r:id="rId31"/>
+    <sheet name="O'Hare" sheetId="32" r:id="rId32"/>
+    <sheet name="Near South Side" sheetId="33" r:id="rId33"/>
+    <sheet name="Grand Crossing" sheetId="34" r:id="rId34"/>
+    <sheet name="Avondale" sheetId="35" r:id="rId35"/>
+    <sheet name="Oakland" sheetId="36" r:id="rId36"/>
+    <sheet name="Chatham" sheetId="37" r:id="rId37"/>
+    <sheet name="New City" sheetId="38" r:id="rId38"/>
+    <sheet name="Belmont Cragin" sheetId="39" r:id="rId39"/>
+    <sheet name="West Loop" sheetId="40" r:id="rId40"/>
+    <sheet name="Hegewisch" sheetId="41" r:id="rId41"/>
+    <sheet name="Greektown" sheetId="42" r:id="rId42"/>
+    <sheet name="Humboldt Park" sheetId="43" r:id="rId43"/>
+    <sheet name="Sheffield &amp; DePaul" sheetId="44" r:id="rId44"/>
+    <sheet name="Norwood Park" sheetId="45" r:id="rId45"/>
     <sheet name="Chicago Lawn" sheetId="46" r:id="rId46"/>
     <sheet name="Calumet Heights" sheetId="47" r:id="rId47"/>
     <sheet name="Hyde Park" sheetId="48" r:id="rId48"/>
@@ -889,7 +889,7 @@
         <v>137</v>
       </c>
       <c r="M2">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -930,7 +930,7 @@
         <v>262</v>
       </c>
       <c r="M3">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1091,7 +1091,7 @@
         <v>896</v>
       </c>
       <c r="M7">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
   </sheetData>
@@ -1101,7 +1101,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -1114,102 +1114,162 @@
     <col min="8" max="8" width="4.7109375" customWidth="1"/>
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
         <v>2016</v>
       </c>
-      <c r="C1" s="1">
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
         <v>2018</v>
       </c>
-      <c r="D1" s="1">
+      <c r="F1" s="1">
         <v>2019</v>
       </c>
-      <c r="E1" s="1">
+      <c r="G1" s="1">
         <v>2020</v>
       </c>
-      <c r="F1" s="1">
+      <c r="H1" s="1">
         <v>2021</v>
       </c>
-      <c r="G1" s="1">
+      <c r="I1" s="1">
         <v>2022</v>
       </c>
-      <c r="H1" s="1">
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
         <v>2024</v>
       </c>
-      <c r="I1" s="1">
+      <c r="L1" s="1">
         <v>2025</v>
       </c>
-      <c r="J1" s="1">
+      <c r="M1" s="1">
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2">
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
         <v>1</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3">
-        <v>2</v>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
       </c>
       <c r="I3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
       </c>
       <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
         <v>1</v>
       </c>
       <c r="J5">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -1218,22 +1278,31 @@
         <v>2</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1307,40 +1376,40 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>5</v>
       </c>
       <c r="F2">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
         <v>8</v>
       </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>13</v>
-      </c>
-      <c r="I2">
-        <v>14</v>
-      </c>
-      <c r="J2">
-        <v>22</v>
-      </c>
       <c r="K2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -1348,72 +1417,60 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>7</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>6</v>
+      </c>
+      <c r="J3">
+        <v>10</v>
+      </c>
+      <c r="K3">
+        <v>12</v>
+      </c>
+      <c r="L3">
         <v>14</v>
       </c>
-      <c r="G3">
-        <v>26</v>
-      </c>
-      <c r="H3">
-        <v>23</v>
-      </c>
-      <c r="I3">
-        <v>32</v>
-      </c>
-      <c r="J3">
-        <v>40</v>
-      </c>
-      <c r="K3">
-        <v>26</v>
-      </c>
-      <c r="L3">
-        <v>34</v>
-      </c>
       <c r="M3">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>2</v>
+      <c r="B4">
+        <v>1</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>3</v>
       </c>
       <c r="K4">
         <v>2</v>
-      </c>
-      <c r="L4">
-        <v>5</v>
       </c>
       <c r="M4">
         <v>3</v>
@@ -1423,19 +1480,7 @@
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
+      <c r="K5">
         <v>1</v>
       </c>
     </row>
@@ -1444,40 +1489,40 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C6">
+        <v>31</v>
+      </c>
+      <c r="D6">
+        <v>22</v>
+      </c>
+      <c r="E6">
         <v>44</v>
       </c>
-      <c r="D6">
-        <v>49</v>
-      </c>
-      <c r="E6">
-        <v>67</v>
-      </c>
       <c r="F6">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="G6">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="H6">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="I6">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="J6">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="K6">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="L6">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="M6">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -1485,40 +1530,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C7">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="D7">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="E7">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="F7">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="G7">
-        <v>88</v>
+        <v>34</v>
       </c>
       <c r="H7">
-        <v>120</v>
+        <v>63</v>
       </c>
       <c r="I7">
-        <v>130</v>
+        <v>44</v>
       </c>
       <c r="J7">
-        <v>131</v>
+        <v>47</v>
       </c>
       <c r="K7">
-        <v>91</v>
+        <v>46</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="M7">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1527,6 +1572,433 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>12</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>8</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>13</v>
+      </c>
+      <c r="I2">
+        <v>14</v>
+      </c>
+      <c r="J2">
+        <v>22</v>
+      </c>
+      <c r="K2">
+        <v>15</v>
+      </c>
+      <c r="L2">
+        <v>15</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>13</v>
+      </c>
+      <c r="D3">
+        <v>17</v>
+      </c>
+      <c r="E3">
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <v>26</v>
+      </c>
+      <c r="H3">
+        <v>23</v>
+      </c>
+      <c r="I3">
+        <v>32</v>
+      </c>
+      <c r="J3">
+        <v>40</v>
+      </c>
+      <c r="K3">
+        <v>26</v>
+      </c>
+      <c r="L3">
+        <v>34</v>
+      </c>
+      <c r="M3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>4</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
+        <v>5</v>
+      </c>
+      <c r="M4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>30</v>
+      </c>
+      <c r="C6">
+        <v>44</v>
+      </c>
+      <c r="D6">
+        <v>49</v>
+      </c>
+      <c r="E6">
+        <v>67</v>
+      </c>
+      <c r="F6">
+        <v>69</v>
+      </c>
+      <c r="G6">
+        <v>57</v>
+      </c>
+      <c r="H6">
+        <v>80</v>
+      </c>
+      <c r="I6">
+        <v>80</v>
+      </c>
+      <c r="J6">
+        <v>64</v>
+      </c>
+      <c r="K6">
+        <v>48</v>
+      </c>
+      <c r="L6">
+        <v>44</v>
+      </c>
+      <c r="M6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>49</v>
+      </c>
+      <c r="C7">
+        <v>62</v>
+      </c>
+      <c r="D7">
+        <v>79</v>
+      </c>
+      <c r="E7">
+        <v>92</v>
+      </c>
+      <c r="F7">
+        <v>92</v>
+      </c>
+      <c r="G7">
+        <v>88</v>
+      </c>
+      <c r="H7">
+        <v>120</v>
+      </c>
+      <c r="I7">
+        <v>130</v>
+      </c>
+      <c r="J7">
+        <v>131</v>
+      </c>
+      <c r="K7">
+        <v>91</v>
+      </c>
+      <c r="L7">
+        <v>100</v>
+      </c>
+      <c r="M7">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1741,7 +2213,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1961,7 +2433,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2042,7 +2514,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2242,7 +2714,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2452,451 +2924,6 @@
       </c>
       <c r="M6">
         <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>8</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>6</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>11</v>
-      </c>
-      <c r="E7">
-        <v>9</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <v>15</v>
-      </c>
-      <c r="L7">
-        <v>13</v>
-      </c>
-      <c r="M7">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>4</v>
-      </c>
-      <c r="M3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>11</v>
-      </c>
-      <c r="D5">
-        <v>8</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-      <c r="J5">
-        <v>5</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>13</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>8</v>
-      </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>6</v>
-      </c>
-      <c r="J6">
-        <v>8</v>
-      </c>
-      <c r="K6">
-        <v>9</v>
-      </c>
-      <c r="L6">
-        <v>12</v>
-      </c>
-      <c r="M6">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2973,34 +3000,25 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>7</v>
-      </c>
-      <c r="H2">
-        <v>11</v>
-      </c>
-      <c r="I2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -3008,76 +3026,52 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>10</v>
-      </c>
-      <c r="F3">
-        <v>12</v>
-      </c>
-      <c r="G3">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
       <c r="D4">
         <v>1</v>
       </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
       <c r="L4">
         <v>1</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
+      <c r="G5">
         <v>1</v>
       </c>
     </row>
@@ -3086,40 +3080,37 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>32</v>
-      </c>
-      <c r="H6">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -3127,40 +3118,40 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="D7">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="E7">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="F7">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="G7">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="H7">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="L7">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="M7">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3418,7 +3409,7 @@
         <v>6</v>
       </c>
       <c r="M7">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -4093,7 +4084,7 @@
         <v>70</v>
       </c>
       <c r="M28">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -6534,7 +6525,7 @@
         <v>896</v>
       </c>
       <c r="M98">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
   </sheetData>
@@ -6646,7 +6637,7 @@
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" customWidth="1"/>
     <col min="4" max="4" width="4.7109375" customWidth="1"/>
@@ -6710,76 +6701,67 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
       <c r="C3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
       <c r="I3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
       <c r="L3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L4">
+        <v>4</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
     </row>
@@ -6791,37 +6773,34 @@
         <v>7</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5">
         <v>5</v>
       </c>
       <c r="G5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J5">
         <v>5</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -6829,40 +6808,40 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
         <v>7</v>
       </c>
-      <c r="C6">
-        <v>10</v>
-      </c>
-      <c r="D6">
-        <v>11</v>
-      </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>10</v>
-      </c>
       <c r="H6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I6">
+        <v>6</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>9</v>
+      </c>
+      <c r="L6">
         <v>12</v>
       </c>
-      <c r="J6">
-        <v>12</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>8</v>
-      </c>
       <c r="M6">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6936,39 +6915,42 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>4</v>
+      <c r="C3">
+        <v>2</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -6983,41 +6965,29 @@
         <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3">
         <v>4</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
       <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -7026,40 +6996,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C5">
         <v>7</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -7067,40 +7037,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C6">
         <v>10</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H6">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J6">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K6">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -7173,32 +7143,29 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
+      <c r="C2">
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M2">
         <v>4</v>
@@ -7208,14 +7175,14 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
+      <c r="B3">
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -7227,26 +7194,38 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J4">
-        <v>1</v>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
       </c>
       <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>
@@ -7255,40 +7234,40 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F5">
+        <v>25</v>
+      </c>
+      <c r="G5">
+        <v>15</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5">
+        <v>11</v>
+      </c>
+      <c r="K5">
+        <v>18</v>
+      </c>
+      <c r="L5">
+        <v>11</v>
+      </c>
+      <c r="M5">
         <v>7</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5">
-        <v>6</v>
-      </c>
-      <c r="I5">
-        <v>7</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5">
-        <v>5</v>
-      </c>
-      <c r="M5">
-        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -7296,40 +7275,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K6">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="L6">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="M6">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -7338,6 +7317,235 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="4.7109375" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C1" s="1">
+        <v>2016</v>
+      </c>
+      <c r="D1" s="1">
+        <v>2017</v>
+      </c>
+      <c r="E1" s="1">
+        <v>2018</v>
+      </c>
+      <c r="F1" s="1">
+        <v>2019</v>
+      </c>
+      <c r="G1" s="1">
+        <v>2020</v>
+      </c>
+      <c r="H1" s="1">
+        <v>2021</v>
+      </c>
+      <c r="I1" s="1">
+        <v>2022</v>
+      </c>
+      <c r="J1" s="1">
+        <v>2023</v>
+      </c>
+      <c r="K1" s="1">
+        <v>2024</v>
+      </c>
+      <c r="L1" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>3</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>7</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="I5">
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>12</v>
+      </c>
+      <c r="E6">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+      <c r="K6">
+        <v>9</v>
+      </c>
+      <c r="L6">
+        <v>15</v>
+      </c>
+      <c r="M6">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7601,7 +7809,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7836,7 +8044,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7999,7 +8207,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -8215,208 +8423,6 @@
       </c>
       <c r="M6">
         <v>11</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2021</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="L1" s="1">
-        <v>2025</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>2</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>7</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>4</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -8489,38 +8495,17 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2">
-        <v>2</v>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>6</v>
-      </c>
-      <c r="L2">
-        <v>5</v>
-      </c>
-      <c r="M2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -8528,37 +8513,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>11</v>
-      </c>
-      <c r="K3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M3">
         <v>4</v>
@@ -8568,61 +8544,46 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
       <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
       <c r="C5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>17</v>
-      </c>
-      <c r="I5">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -8630,40 +8591,40 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G6">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="K6">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -8672,207 +8633,6 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" customWidth="1"/>
-    <col min="3" max="3" width="4.7109375" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" customWidth="1"/>
-    <col min="7" max="7" width="4.7109375" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" customWidth="1"/>
-    <col min="12" max="12" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1">
-        <v>2015</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E1" s="1">
-        <v>2018</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G1" s="1">
-        <v>2020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>2022</v>
-      </c>
-      <c r="I1" s="1">
-        <v>2023</v>
-      </c>
-      <c r="J1" s="1">
-        <v>2024</v>
-      </c>
-      <c r="K1" s="1">
-        <v>2025